--- a/data/k-props/2026-08-11.xlsx
+++ b/data/k-props/2026-08-11.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="101">
   <si>
     <t>date</t>
   </si>
@@ -193,15 +193,15 @@
     <t>Jake Irvin</t>
   </si>
   <si>
+    <t>Ryan Weathers</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ New York Yankees</t>
+  </si>
+  <si>
     <t>Bryan Woo</t>
   </si>
   <si>
-    <t>Seattle Mariners @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Ryan Weathers</t>
-  </si>
-  <si>
     <t>Dylan Cease</t>
   </si>
   <si>
@@ -265,15 +265,15 @@
     <t>Mitch Bratt</t>
   </si>
   <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Athletics</t>
+  </si>
+  <si>
     <t>Mason Barnett</t>
   </si>
   <si>
-    <t>Tampa Bay Rays @ Athletics</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
     <t>Kyle Harrison</t>
   </si>
   <si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>Houston Astros @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Carson Whisenhunt</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
   </si>
   <si>
     <t>Blake Snell</t>
@@ -688,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ33"/>
+  <dimension ref="A1:AQ34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="43" width="16" customWidth="1"/>
@@ -839,7 +845,7 @@
         <v>-108</v>
       </c>
       <c r="E2">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="F2">
         <v>4.09</v>
@@ -949,7 +955,7 @@
         <v>3.5</v>
       </c>
       <c r="D3">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E3">
         <v>-142</v>
@@ -1065,7 +1071,7 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>-123</v>
+        <v>-120</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1112,7 +1118,7 @@
         <v>6.5</v>
       </c>
       <c r="D5">
-        <v>-141</v>
+        <v>-140</v>
       </c>
       <c r="E5">
         <v>118</v>
@@ -1338,7 +1344,7 @@
         <v>4.5</v>
       </c>
       <c r="D7">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E7">
         <v>-155</v>
@@ -1388,13 +1394,13 @@
         <v>6.5</v>
       </c>
       <c r="D8">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E8">
-        <v>-140</v>
+        <v>-155</v>
       </c>
       <c r="F8">
-        <v>7.06</v>
+        <v>5.1</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1403,10 +1409,10 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>7.06</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M8" t="s">
         <v>61</v>
@@ -1418,7 +1424,7 @@
         <v>48</v>
       </c>
       <c r="P8">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1430,52 +1436,52 @@
         <v>6</v>
       </c>
       <c r="T8">
-        <v>0.2428</v>
+        <v>0.2624</v>
       </c>
       <c r="U8">
-        <v>0.2425</v>
+        <v>0.2539</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="X8">
-        <v>0.2419</v>
+        <v>0.2393</v>
       </c>
       <c r="Y8">
-        <v>0.383</v>
+        <v>0.369</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
       <c r="AB8">
-        <v>1.2223</v>
+        <v>0.8992</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
       </c>
       <c r="AD8">
-        <v>0.2681</v>
+        <v>0.1972</v>
       </c>
       <c r="AE8">
-        <v>0.268</v>
+        <v>0.1872</v>
       </c>
       <c r="AF8">
         <v>9</v>
       </c>
       <c r="AG8">
-        <v>0.2439</v>
+        <v>0.2371</v>
       </c>
       <c r="AH8">
         <v>0.2193</v>
       </c>
       <c r="AI8">
-        <v>1.0015</v>
+        <v>0.9779</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
@@ -1501,13 +1507,13 @@
         <v>6.5</v>
       </c>
       <c r="D9">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E9">
-        <v>-155</v>
+        <v>-135</v>
       </c>
       <c r="F9">
-        <v>5.1</v>
+        <v>7.06</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1516,10 +1522,10 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>5.1</v>
+        <v>7.06</v>
       </c>
       <c r="L9" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="M9" t="s">
         <v>61</v>
@@ -1531,7 +1537,7 @@
         <v>48</v>
       </c>
       <c r="P9">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -1543,52 +1549,52 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>0.2624</v>
+        <v>0.2428</v>
       </c>
       <c r="U9">
-        <v>0.2539</v>
+        <v>0.2425</v>
       </c>
       <c r="V9">
         <v>5</v>
       </c>
       <c r="W9">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="X9">
-        <v>0.2393</v>
+        <v>0.2419</v>
       </c>
       <c r="Y9">
-        <v>0.369</v>
+        <v>0.383</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>4.16</v>
+        <v>4.11</v>
       </c>
       <c r="AB9">
-        <v>0.8992</v>
+        <v>1.2223</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
       </c>
       <c r="AD9">
-        <v>0.1972</v>
+        <v>0.2681</v>
       </c>
       <c r="AE9">
-        <v>0.1872</v>
+        <v>0.268</v>
       </c>
       <c r="AF9">
         <v>9</v>
       </c>
       <c r="AG9">
-        <v>0.2371</v>
+        <v>0.2439</v>
       </c>
       <c r="AH9">
         <v>0.2193</v>
       </c>
       <c r="AI9">
-        <v>0.9779</v>
+        <v>1.0015</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
@@ -1614,10 +1620,10 @@
         <v>7.5</v>
       </c>
       <c r="D10">
-        <v>-132</v>
+        <v>-140</v>
       </c>
       <c r="E10">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F10">
         <v>7.39</v>
@@ -1730,7 +1736,7 @@
         <v>124</v>
       </c>
       <c r="E11">
-        <v>-145</v>
+        <v>-143</v>
       </c>
       <c r="F11">
         <v>4.36</v>
@@ -1840,10 +1846,10 @@
         <v>3.5</v>
       </c>
       <c r="D12">
-        <v>-145</v>
+        <v>-140</v>
       </c>
       <c r="E12">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1890,10 +1896,10 @@
         <v>5.5</v>
       </c>
       <c r="D13">
-        <v>-153</v>
+        <v>-155</v>
       </c>
       <c r="E13">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F13">
         <v>7.38</v>
@@ -2006,7 +2012,7 @@
         <v>128</v>
       </c>
       <c r="E14">
-        <v>-157</v>
+        <v>-152</v>
       </c>
       <c r="F14">
         <v>4.33</v>
@@ -2229,7 +2235,7 @@
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>-111</v>
+        <v>-113</v>
       </c>
       <c r="E16">
         <v>-105</v>
@@ -2339,13 +2345,13 @@
         <v>74</v>
       </c>
       <c r="C17">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D17">
-        <v>-158</v>
+        <v>120</v>
       </c>
       <c r="E17">
-        <v>124</v>
+        <v>-141</v>
       </c>
       <c r="F17">
         <v>7.96</v>
@@ -2455,10 +2461,10 @@
         <v>5.5</v>
       </c>
       <c r="D18">
-        <v>-142</v>
+        <v>-146</v>
       </c>
       <c r="E18">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2505,7 +2511,7 @@
         <v>3.5</v>
       </c>
       <c r="D19">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>-121</v>
@@ -2618,10 +2624,10 @@
         <v>4.5</v>
       </c>
       <c r="D20">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20">
-        <v>-161</v>
+        <v>-160</v>
       </c>
       <c r="F20">
         <v>3.42</v>
@@ -2731,10 +2737,10 @@
         <v>4.5</v>
       </c>
       <c r="D21">
-        <v>-143</v>
+        <v>-148</v>
       </c>
       <c r="E21">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -2781,10 +2787,10 @@
         <v>2.5</v>
       </c>
       <c r="D22">
-        <v>-132</v>
+        <v>-130</v>
       </c>
       <c r="E22">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F22">
         <v>2.28</v>
@@ -2894,7 +2900,7 @@
         <v>4.5</v>
       </c>
       <c r="D23">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E23">
         <v>-146</v>
@@ -3007,13 +3013,13 @@
         <v>3.5</v>
       </c>
       <c r="D24">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E24">
-        <v>-125</v>
+        <v>-141</v>
       </c>
       <c r="F24">
-        <v>3.78</v>
+        <v>3.67</v>
       </c>
       <c r="H24" t="s">
         <v>45</v>
@@ -3022,7 +3028,7 @@
         <v>45</v>
       </c>
       <c r="K24">
-        <v>3.78</v>
+        <v>3.67</v>
       </c>
       <c r="L24" t="s">
         <v>46</v>
@@ -3037,7 +3043,7 @@
         <v>48</v>
       </c>
       <c r="P24">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -3049,52 +3055,52 @@
         <v>6</v>
       </c>
       <c r="T24">
-        <v>0.2449</v>
+        <v>0.1407</v>
       </c>
       <c r="U24">
-        <v>0.2561</v>
+        <v>0.129</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="X24">
-        <v>0.3095</v>
+        <v>0.1081</v>
       </c>
       <c r="Y24">
-        <v>0.174</v>
+        <v>0.357</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>4.32</v>
+        <v>4.02</v>
       </c>
       <c r="AB24">
-        <v>0.815</v>
+        <v>1.1833</v>
       </c>
       <c r="AC24" t="s">
         <v>49</v>
       </c>
       <c r="AD24">
-        <v>0.1787</v>
+        <v>0.2595</v>
       </c>
       <c r="AE24">
-        <v>0.1753</v>
+        <v>0.2292</v>
       </c>
       <c r="AF24">
         <v>9</v>
       </c>
       <c r="AG24">
-        <v>0.1929</v>
+        <v>0.2179</v>
       </c>
       <c r="AH24">
         <v>0.2193</v>
       </c>
       <c r="AI24">
-        <v>0.8983</v>
+        <v>1.0198</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
@@ -3120,13 +3126,13 @@
         <v>3.5</v>
       </c>
       <c r="D25">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E25">
-        <v>-141</v>
+        <v>-124</v>
       </c>
       <c r="F25">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3135,7 +3141,7 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
@@ -3150,7 +3156,7 @@
         <v>48</v>
       </c>
       <c r="P25">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -3162,52 +3168,52 @@
         <v>6</v>
       </c>
       <c r="T25">
-        <v>0.1407</v>
+        <v>0.2449</v>
       </c>
       <c r="U25">
-        <v>0.129</v>
+        <v>0.2561</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W25">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="X25">
-        <v>0.1081</v>
+        <v>0.3095</v>
       </c>
       <c r="Y25">
-        <v>0.357</v>
+        <v>0.174</v>
       </c>
       <c r="Z25" t="b">
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>4.02</v>
+        <v>4.32</v>
       </c>
       <c r="AB25">
-        <v>1.1833</v>
+        <v>0.815</v>
       </c>
       <c r="AC25" t="s">
         <v>49</v>
       </c>
       <c r="AD25">
-        <v>0.2595</v>
+        <v>0.1787</v>
       </c>
       <c r="AE25">
-        <v>0.2292</v>
+        <v>0.1753</v>
       </c>
       <c r="AF25">
         <v>9</v>
       </c>
       <c r="AG25">
-        <v>0.2179</v>
+        <v>0.1929</v>
       </c>
       <c r="AH25">
         <v>0.2193</v>
       </c>
       <c r="AI25">
-        <v>1.0198</v>
+        <v>0.8983</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
@@ -3233,10 +3239,10 @@
         <v>5.5</v>
       </c>
       <c r="D26">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="E26">
-        <v>-142</v>
+        <v>-145</v>
       </c>
       <c r="F26">
         <v>4.5</v>
@@ -3346,10 +3352,10 @@
         <v>4.5</v>
       </c>
       <c r="D27">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E27">
-        <v>-127</v>
+        <v>-150</v>
       </c>
       <c r="F27">
         <v>4.06</v>
@@ -3459,10 +3465,10 @@
         <v>5.5</v>
       </c>
       <c r="D28">
-        <v>-127</v>
+        <v>-130</v>
       </c>
       <c r="E28">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F28">
         <v>5.47</v>
@@ -3569,13 +3575,16 @@
         <v>92</v>
       </c>
       <c r="C29">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D29">
-        <v>124</v>
+        <v>-141</v>
       </c>
       <c r="E29">
-        <v>-155</v>
+        <v>111</v>
+      </c>
+      <c r="F29">
+        <v>3.78</v>
       </c>
       <c r="H29" t="s">
         <v>45</v>
@@ -3583,32 +3592,92 @@
       <c r="J29" t="s">
         <v>45</v>
       </c>
+      <c r="K29">
+        <v>3.78</v>
+      </c>
       <c r="L29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M29" t="s">
+        <v>91</v>
+      </c>
+      <c r="N29">
+        <v>823186</v>
+      </c>
+      <c r="O29" t="s">
         <v>93</v>
       </c>
-      <c r="N29" t="s">
-        <v>45</v>
-      </c>
-      <c r="O29" t="s">
-        <v>45</v>
+      <c r="P29">
+        <v>4.5</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="T29">
+        <v>0.1905</v>
+      </c>
+      <c r="U29">
+        <v>0.1905</v>
+      </c>
+      <c r="V29">
+        <v>5</v>
+      </c>
+      <c r="W29">
+        <v>105</v>
+      </c>
+      <c r="X29">
+        <v>0.1905</v>
+      </c>
+      <c r="Y29">
+        <v>0.344</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>4.7</v>
+      </c>
+      <c r="AB29">
+        <v>0.9647</v>
       </c>
       <c r="AC29" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="AD29">
+        <v>0.2116</v>
+      </c>
+      <c r="AE29">
+        <v>0.2017</v>
+      </c>
+      <c r="AF29">
+        <v>8</v>
+      </c>
+      <c r="AG29">
+        <v>0.2071</v>
+      </c>
+      <c r="AH29">
+        <v>0.2193</v>
+      </c>
+      <c r="AI29">
+        <v>0.9797</v>
+      </c>
+      <c r="AJ29" t="b">
+        <v>1</v>
       </c>
       <c r="AK29" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AL29" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
@@ -3619,16 +3688,13 @@
         <v>94</v>
       </c>
       <c r="C30">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D30">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="E30">
-        <v>-128</v>
-      </c>
-      <c r="F30">
-        <v>6.53</v>
+        <v>-155</v>
       </c>
       <c r="H30" t="s">
         <v>45</v>
@@ -3636,92 +3702,32 @@
       <c r="J30" t="s">
         <v>45</v>
       </c>
-      <c r="K30">
-        <v>6.2</v>
-      </c>
       <c r="L30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M30" t="s">
         <v>95</v>
       </c>
-      <c r="M30" t="s">
-        <v>93</v>
-      </c>
-      <c r="N30">
-        <v>823917</v>
+      <c r="N30" t="s">
+        <v>45</v>
       </c>
       <c r="O30" t="s">
-        <v>48</v>
-      </c>
-      <c r="P30">
-        <v>6.3</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S30">
         <v>6</v>
       </c>
-      <c r="T30">
-        <v>0.1915</v>
-      </c>
-      <c r="U30">
-        <v>0.1847</v>
-      </c>
-      <c r="V30">
-        <v>5</v>
-      </c>
-      <c r="W30">
-        <v>121</v>
-      </c>
-      <c r="X30">
-        <v>0.1736</v>
-      </c>
-      <c r="Y30">
-        <v>0.377</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>4.06</v>
-      </c>
-      <c r="AB30">
-        <v>1.3202</v>
-      </c>
       <c r="AC30" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD30">
-        <v>0.2895</v>
-      </c>
-      <c r="AE30">
-        <v>0.2205</v>
-      </c>
-      <c r="AF30">
-        <v>9</v>
-      </c>
-      <c r="AG30">
-        <v>0.207</v>
-      </c>
-      <c r="AH30">
-        <v>0.2193</v>
-      </c>
-      <c r="AI30">
-        <v>0.9998</v>
-      </c>
-      <c r="AJ30" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>45</v>
       </c>
       <c r="AK30" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AL30" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM30">
-        <v>0.33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.25">
@@ -3731,8 +3737,17 @@
       <c r="B31" t="s">
         <v>96</v>
       </c>
+      <c r="C31">
+        <v>4.5</v>
+      </c>
+      <c r="D31">
+        <v>111</v>
+      </c>
+      <c r="E31">
+        <v>-128</v>
+      </c>
       <c r="F31">
-        <v>6.44</v>
+        <v>6.53</v>
       </c>
       <c r="H31" t="s">
         <v>45</v>
@@ -3741,22 +3756,22 @@
         <v>45</v>
       </c>
       <c r="K31">
-        <v>6.11</v>
+        <v>6.2</v>
       </c>
       <c r="L31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M31" t="s">
         <v>95</v>
       </c>
-      <c r="M31" t="s">
-        <v>54</v>
-      </c>
       <c r="N31">
-        <v>823832</v>
+        <v>823917</v>
       </c>
       <c r="O31" t="s">
         <v>48</v>
       </c>
       <c r="P31">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="Q31" t="b">
         <v>0</v>
@@ -3765,55 +3780,55 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T31">
-        <v>0.2707</v>
+        <v>0.1915</v>
       </c>
       <c r="U31">
-        <v>0.2659</v>
+        <v>0.1847</v>
       </c>
       <c r="V31">
         <v>5</v>
       </c>
       <c r="W31">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="X31">
-        <v>0.2581</v>
+        <v>0.1736</v>
       </c>
       <c r="Y31">
-        <v>0.383</v>
+        <v>0.377</v>
       </c>
       <c r="Z31" t="b">
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="AB31">
-        <v>1.0142</v>
+        <v>1.3202</v>
       </c>
       <c r="AC31" t="s">
         <v>49</v>
       </c>
       <c r="AD31">
-        <v>0.2224</v>
+        <v>0.2895</v>
       </c>
       <c r="AE31">
-        <v>0.2376</v>
+        <v>0.2205</v>
       </c>
       <c r="AF31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG31">
-        <v>0.2359</v>
+        <v>0.207</v>
       </c>
       <c r="AH31">
         <v>0.2193</v>
       </c>
       <c r="AI31">
-        <v>1.0138</v>
+        <v>0.9998</v>
       </c>
       <c r="AJ31" t="b">
         <v>1</v>
@@ -3833,34 +3848,34 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32">
+        <v>6.44</v>
+      </c>
+      <c r="H32" t="s">
+        <v>45</v>
+      </c>
+      <c r="J32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K32">
+        <v>6.11</v>
+      </c>
+      <c r="L32" t="s">
         <v>97</v>
       </c>
-      <c r="F32">
-        <v>4.34</v>
-      </c>
-      <c r="H32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J32" t="s">
-        <v>45</v>
-      </c>
-      <c r="K32">
-        <v>4.34</v>
-      </c>
-      <c r="L32" t="s">
-        <v>46</v>
-      </c>
       <c r="M32" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="N32">
-        <v>824886</v>
+        <v>823832</v>
       </c>
       <c r="O32" t="s">
         <v>48</v>
       </c>
       <c r="P32">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q32" t="b">
         <v>0</v>
@@ -3872,52 +3887,52 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>0.1916</v>
+        <v>0.2707</v>
       </c>
       <c r="U32">
-        <v>0.1882</v>
+        <v>0.2659</v>
       </c>
       <c r="V32">
         <v>5</v>
       </c>
       <c r="W32">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="X32">
-        <v>0.1809</v>
+        <v>0.2581</v>
       </c>
       <c r="Y32">
-        <v>0.32</v>
+        <v>0.383</v>
       </c>
       <c r="Z32" t="b">
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="AB32">
-        <v>1.1556</v>
+        <v>1.0142</v>
       </c>
       <c r="AC32" t="s">
         <v>49</v>
       </c>
       <c r="AD32">
-        <v>0.2534</v>
+        <v>0.2224</v>
       </c>
       <c r="AE32">
-        <v>0.2541</v>
+        <v>0.2376</v>
       </c>
       <c r="AF32">
         <v>8</v>
       </c>
       <c r="AG32">
-        <v>0.2315</v>
+        <v>0.2359</v>
       </c>
       <c r="AH32">
         <v>0.2193</v>
       </c>
       <c r="AI32">
-        <v>0.9722</v>
+        <v>1.0138</v>
       </c>
       <c r="AJ32" t="b">
         <v>1</v>
@@ -3929,7 +3944,7 @@
         <v>50</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
@@ -3937,10 +3952,10 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F33">
-        <v>6.88</v>
+        <v>4.34</v>
       </c>
       <c r="H33" t="s">
         <v>45</v>
@@ -3949,22 +3964,22 @@
         <v>45</v>
       </c>
       <c r="K33">
-        <v>6.55</v>
+        <v>4.34</v>
       </c>
       <c r="L33" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="M33" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="N33">
-        <v>823019</v>
+        <v>824886</v>
       </c>
       <c r="O33" t="s">
         <v>48</v>
       </c>
       <c r="P33">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="Q33" t="b">
         <v>0</v>
@@ -3976,52 +3991,52 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>0.278</v>
+        <v>0.1916</v>
       </c>
       <c r="U33">
-        <v>0.2806</v>
+        <v>0.1882</v>
       </c>
       <c r="V33">
         <v>5</v>
       </c>
       <c r="W33">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="X33">
-        <v>0.2846</v>
+        <v>0.1809</v>
       </c>
       <c r="Y33">
-        <v>0.394</v>
+        <v>0.32</v>
       </c>
       <c r="Z33" t="b">
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="AB33">
-        <v>0.915</v>
+        <v>1.1556</v>
       </c>
       <c r="AC33" t="s">
         <v>49</v>
       </c>
       <c r="AD33">
-        <v>0.2007</v>
+        <v>0.2534</v>
       </c>
       <c r="AE33">
-        <v>0.1844</v>
+        <v>0.2541</v>
       </c>
       <c r="AF33">
         <v>8</v>
       </c>
       <c r="AG33">
-        <v>0.1805</v>
+        <v>0.2315</v>
       </c>
       <c r="AH33">
         <v>0.2193</v>
       </c>
       <c r="AI33">
-        <v>0.9783</v>
+        <v>0.9722</v>
       </c>
       <c r="AJ33" t="b">
         <v>1</v>
@@ -4033,6 +4048,110 @@
         <v>50</v>
       </c>
       <c r="AM33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34">
+        <v>6.88</v>
+      </c>
+      <c r="H34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" t="s">
+        <v>45</v>
+      </c>
+      <c r="K34">
+        <v>6.55</v>
+      </c>
+      <c r="L34" t="s">
+        <v>97</v>
+      </c>
+      <c r="M34" t="s">
+        <v>76</v>
+      </c>
+      <c r="N34">
+        <v>823019</v>
+      </c>
+      <c r="O34" t="s">
+        <v>48</v>
+      </c>
+      <c r="P34">
+        <v>6.2</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0.278</v>
+      </c>
+      <c r="U34">
+        <v>0.2806</v>
+      </c>
+      <c r="V34">
+        <v>5</v>
+      </c>
+      <c r="W34">
+        <v>130</v>
+      </c>
+      <c r="X34">
+        <v>0.2846</v>
+      </c>
+      <c r="Y34">
+        <v>0.394</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>4.18</v>
+      </c>
+      <c r="AB34">
+        <v>0.915</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD34">
+        <v>0.2007</v>
+      </c>
+      <c r="AE34">
+        <v>0.1844</v>
+      </c>
+      <c r="AF34">
+        <v>8</v>
+      </c>
+      <c r="AG34">
+        <v>0.1805</v>
+      </c>
+      <c r="AH34">
+        <v>0.2193</v>
+      </c>
+      <c r="AI34">
+        <v>0.9783</v>
+      </c>
+      <c r="AJ34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM34">
         <v>0.33</v>
       </c>
     </row>

--- a/data/k-props/2026-08-11.xlsx
+++ b/data/k-props/2026-08-11.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="103">
   <si>
     <t>date</t>
   </si>
@@ -160,54 +160,63 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>posted</t>
+  </si>
+  <si>
+    <t>Drew Anderson</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Eury Perez</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Paul Skenes</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Shota Imanaga</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
+    <t>Bryan Woo</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Ryan Weathers</t>
+  </si>
+  <si>
+    <t>Dylan Cease</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Toronto Blue Jays</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
   </si>
   <si>
-    <t>Drew Anderson</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Eury Perez</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Paul Skenes</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Shota Imanaga</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Jake Irvin</t>
-  </si>
-  <si>
-    <t>Ryan Weathers</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Bryan Woo</t>
-  </si>
-  <si>
-    <t>Dylan Cease</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Toronto Blue Jays</t>
-  </si>
-  <si>
     <t>Patrick Sandoval</t>
   </si>
   <si>
@@ -283,18 +292,18 @@
     <t>Walker Buehler</t>
   </si>
   <si>
+    <t>Carson Whisenhunt</t>
+  </si>
+  <si>
+    <t>Houston Astros @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
     <t>Hunter Brown</t>
   </si>
   <si>
-    <t>Houston Astros @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Carson Whisenhunt</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
     <t>Blake Snell</t>
   </si>
   <si>
@@ -302,9 +311,6 @@
   </si>
   <si>
     <t>Michael Wacha</t>
-  </si>
-  <si>
-    <t>6-7</t>
   </si>
   <si>
     <t>Eury Pérez</t>
@@ -848,7 +854,7 @@
         <v>-108</v>
       </c>
       <c r="F2">
-        <v>4.09</v>
+        <v>4.32</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -857,7 +863,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>4.09</v>
+        <v>4.16</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -908,16 +914,16 @@
         <v>4.05</v>
       </c>
       <c r="AB2">
-        <v>0.9013</v>
+        <v>0.9337</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
       </c>
       <c r="AD2">
-        <v>0.1977</v>
+        <v>0.2045</v>
       </c>
       <c r="AE2">
-        <v>0.2017</v>
+        <v>0.2052</v>
       </c>
       <c r="AF2">
         <v>9</v>
@@ -926,10 +932,10 @@
         <v>0.2261</v>
       </c>
       <c r="AH2">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI2">
-        <v>0.9799</v>
+        <v>0.9619</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -941,7 +947,7 @@
         <v>50</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
@@ -955,13 +961,13 @@
         <v>3.5</v>
       </c>
       <c r="D3">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E3">
-        <v>-142</v>
+        <v>-150</v>
       </c>
       <c r="F3">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -970,7 +976,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -1021,16 +1027,16 @@
         <v>4.29</v>
       </c>
       <c r="AB3">
-        <v>0.9867</v>
+        <v>0.8976</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
       </c>
       <c r="AD3">
-        <v>0.2164</v>
+        <v>0.1966</v>
       </c>
       <c r="AE3">
-        <v>0.2085</v>
+        <v>0.1965</v>
       </c>
       <c r="AF3">
         <v>9</v>
@@ -1039,10 +1045,10 @@
         <v>0.2176</v>
       </c>
       <c r="AH3">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI3">
-        <v>0.9426</v>
+        <v>0.88</v>
       </c>
       <c r="AJ3" t="b">
         <v>1</v>
@@ -1054,7 +1060,7 @@
         <v>50</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
@@ -1068,10 +1074,10 @@
         <v>6.5</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E4">
-        <v>-120</v>
+        <v>-125</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1118,13 +1124,13 @@
         <v>6.5</v>
       </c>
       <c r="D5">
-        <v>-140</v>
+        <v>-146</v>
       </c>
       <c r="E5">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F5">
-        <v>7.26</v>
+        <v>7.16</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1133,7 +1139,7 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>7.26</v>
+        <v>7.16</v>
       </c>
       <c r="L5" t="s">
         <v>56</v>
@@ -1184,28 +1190,28 @@
         <v>4.1</v>
       </c>
       <c r="AB5">
-        <v>1.0403</v>
+        <v>1.1053</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
       </c>
       <c r="AD5">
-        <v>0.2281</v>
+        <v>0.242</v>
       </c>
       <c r="AE5">
-        <v>0.2265</v>
+        <v>0.2322</v>
       </c>
       <c r="AF5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG5">
         <v>0.2096</v>
       </c>
       <c r="AH5">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI5">
-        <v>0.9827</v>
+        <v>0.9124</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
@@ -1231,13 +1237,13 @@
         <v>5.5</v>
       </c>
       <c r="D6">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E6">
-        <v>-125</v>
+        <v>-143</v>
       </c>
       <c r="F6">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1246,7 +1252,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
@@ -1297,16 +1303,16 @@
         <v>4.02</v>
       </c>
       <c r="AB6">
-        <v>0.9273</v>
+        <v>0.9045</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
       </c>
       <c r="AD6">
-        <v>0.2034</v>
+        <v>0.1981</v>
       </c>
       <c r="AE6">
-        <v>0.2138</v>
+        <v>0.2224</v>
       </c>
       <c r="AF6">
         <v>9</v>
@@ -1315,10 +1321,10 @@
         <v>0.2352</v>
       </c>
       <c r="AH6">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI6">
-        <v>1.0081</v>
+        <v>1.0324</v>
       </c>
       <c r="AJ6" t="b">
         <v>1</v>
@@ -1330,7 +1336,7 @@
         <v>50</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
@@ -1344,43 +1350,106 @@
         <v>4.5</v>
       </c>
       <c r="D7">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E7">
         <v>-155</v>
       </c>
+      <c r="F7">
+        <v>4.87</v>
+      </c>
       <c r="H7" t="s">
         <v>45</v>
       </c>
       <c r="J7" t="s">
         <v>45</v>
       </c>
+      <c r="K7">
+        <v>4.71</v>
+      </c>
       <c r="L7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M7" t="s">
         <v>58</v>
       </c>
-      <c r="N7" t="s">
-        <v>45</v>
+      <c r="N7">
+        <v>822697</v>
       </c>
       <c r="O7" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P7">
+        <v>4.8</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
       </c>
       <c r="S7">
         <v>5</v>
       </c>
+      <c r="T7">
+        <v>0.2313</v>
+      </c>
+      <c r="U7">
+        <v>0.2304</v>
+      </c>
+      <c r="V7">
+        <v>5</v>
+      </c>
+      <c r="W7">
+        <v>92</v>
+      </c>
+      <c r="X7">
+        <v>0.2283</v>
+      </c>
+      <c r="Y7">
+        <v>0.315</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>4.32</v>
+      </c>
+      <c r="AB7">
+        <v>1.0212</v>
+      </c>
       <c r="AC7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="AD7">
+        <v>0.2236</v>
+      </c>
+      <c r="AE7">
+        <v>0.2226</v>
+      </c>
+      <c r="AF7">
+        <v>9</v>
+      </c>
+      <c r="AG7">
+        <v>0.218</v>
+      </c>
+      <c r="AH7">
+        <v>0.219</v>
+      </c>
+      <c r="AI7">
+        <v>0.9719</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="AM7">
+        <v>0.16</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
@@ -1394,13 +1463,13 @@
         <v>6.5</v>
       </c>
       <c r="D8">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>-155</v>
+        <v>-134</v>
       </c>
       <c r="F8">
-        <v>5.1</v>
+        <v>6.87</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1409,13 +1478,13 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>5.1</v>
+        <v>6.87</v>
       </c>
       <c r="L8" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="M8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N8">
         <v>823512</v>
@@ -1424,7 +1493,7 @@
         <v>48</v>
       </c>
       <c r="P8">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1436,52 +1505,52 @@
         <v>6</v>
       </c>
       <c r="T8">
-        <v>0.2624</v>
+        <v>0.2428</v>
       </c>
       <c r="U8">
-        <v>0.2539</v>
+        <v>0.2425</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="X8">
-        <v>0.2393</v>
+        <v>0.2419</v>
       </c>
       <c r="Y8">
-        <v>0.369</v>
+        <v>0.383</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>4.16</v>
+        <v>4.11</v>
       </c>
       <c r="AB8">
-        <v>0.8992</v>
+        <v>1.1701</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
       </c>
       <c r="AD8">
-        <v>0.1972</v>
+        <v>0.2562</v>
       </c>
       <c r="AE8">
-        <v>0.1872</v>
+        <v>0.2601</v>
       </c>
       <c r="AF8">
         <v>9</v>
       </c>
       <c r="AG8">
-        <v>0.2371</v>
+        <v>0.2439</v>
       </c>
       <c r="AH8">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI8">
-        <v>0.9779</v>
+        <v>1.018</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
@@ -1501,19 +1570,19 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9">
         <v>6.5</v>
       </c>
       <c r="D9">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E9">
-        <v>-135</v>
+        <v>-145</v>
       </c>
       <c r="F9">
-        <v>7.06</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1522,13 +1591,13 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>7.06</v>
+        <v>5.85</v>
       </c>
       <c r="L9" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N9">
         <v>823512</v>
@@ -1537,7 +1606,7 @@
         <v>48</v>
       </c>
       <c r="P9">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -1546,55 +1615,55 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>0.2428</v>
+        <v>0.2624</v>
       </c>
       <c r="U9">
-        <v>0.2425</v>
+        <v>0.2539</v>
       </c>
       <c r="V9">
         <v>5</v>
       </c>
       <c r="W9">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="X9">
-        <v>0.2419</v>
+        <v>0.2393</v>
       </c>
       <c r="Y9">
-        <v>0.383</v>
+        <v>0.369</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
       <c r="AB9">
-        <v>1.2223</v>
+        <v>1.042</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
       </c>
       <c r="AD9">
-        <v>0.2681</v>
+        <v>0.2282</v>
       </c>
       <c r="AE9">
-        <v>0.268</v>
+        <v>0.2152</v>
       </c>
       <c r="AF9">
         <v>9</v>
       </c>
       <c r="AG9">
-        <v>0.2439</v>
+        <v>0.2371</v>
       </c>
       <c r="AH9">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI9">
-        <v>1.0015</v>
+        <v>0.9673</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
@@ -1606,7 +1675,7 @@
         <v>50</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
@@ -1614,19 +1683,19 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10">
         <v>7.5</v>
       </c>
       <c r="D10">
-        <v>-140</v>
+        <v>-143</v>
       </c>
       <c r="E10">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F10">
-        <v>7.39</v>
+        <v>7.4</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1635,13 +1704,13 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>7.39</v>
+        <v>7.4</v>
       </c>
       <c r="L10" t="s">
         <v>56</v>
       </c>
       <c r="M10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N10">
         <v>822778</v>
@@ -1686,10 +1755,10 @@
         <v>4</v>
       </c>
       <c r="AB10">
-        <v>0.8588</v>
+        <v>0.8601</v>
       </c>
       <c r="AC10" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD10">
         <v>0.1884</v>
@@ -1704,7 +1773,7 @@
         <v>0.2185</v>
       </c>
       <c r="AH10">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI10">
         <v>0.9912</v>
@@ -1713,10 +1782,10 @@
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL10" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -1727,7 +1796,7 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C11">
         <v>4.5</v>
@@ -1736,10 +1805,10 @@
         <v>124</v>
       </c>
       <c r="E11">
-        <v>-143</v>
+        <v>-134</v>
       </c>
       <c r="F11">
-        <v>4.36</v>
+        <v>3.69</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1748,13 +1817,13 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>4.36</v>
+        <v>3.53</v>
       </c>
       <c r="L11" t="s">
         <v>46</v>
       </c>
       <c r="M11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N11">
         <v>822778</v>
@@ -1799,16 +1868,16 @@
         <v>4.54</v>
       </c>
       <c r="AB11">
-        <v>0.8862</v>
+        <v>0.7321</v>
       </c>
       <c r="AC11" t="s">
         <v>49</v>
       </c>
       <c r="AD11">
-        <v>0.1944</v>
+        <v>0.1603</v>
       </c>
       <c r="AE11">
-        <v>0.1853</v>
+        <v>0.175</v>
       </c>
       <c r="AF11">
         <v>9</v>
@@ -1817,10 +1886,10 @@
         <v>0.2164</v>
       </c>
       <c r="AH11">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI11">
-        <v>0.9829</v>
+        <v>0.9645</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
@@ -1832,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
@@ -1840,16 +1909,16 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C12">
         <v>3.5</v>
       </c>
       <c r="D12">
-        <v>-140</v>
+        <v>-131</v>
       </c>
       <c r="E12">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1861,7 +1930,7 @@
         <v>45</v>
       </c>
       <c r="M12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N12" t="s">
         <v>45</v>
@@ -1890,7 +1959,7 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C13">
         <v>5.5</v>
@@ -1899,10 +1968,10 @@
         <v>-155</v>
       </c>
       <c r="E13">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F13">
-        <v>7.38</v>
+        <v>7.39</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -1911,13 +1980,13 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>7.38</v>
+        <v>7.39</v>
       </c>
       <c r="L13" t="s">
         <v>56</v>
       </c>
       <c r="M13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N13">
         <v>824886</v>
@@ -1962,10 +2031,10 @@
         <v>4.19</v>
       </c>
       <c r="AB13">
-        <v>1.0713</v>
+        <v>1.073</v>
       </c>
       <c r="AC13" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD13">
         <v>0.235</v>
@@ -1980,7 +2049,7 @@
         <v>0.2179</v>
       </c>
       <c r="AH13">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI13">
         <v>0.9931</v>
@@ -1989,10 +2058,10 @@
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL13" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2003,7 +2072,7 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C14">
         <v>4.5</v>
@@ -2015,7 +2084,7 @@
         <v>-152</v>
       </c>
       <c r="F14">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2024,13 +2093,13 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.33</v>
+        <v>4.44</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N14">
         <v>823673</v>
@@ -2075,16 +2144,16 @@
         <v>4.26</v>
       </c>
       <c r="AB14">
-        <v>0.8917</v>
+        <v>0.9354</v>
       </c>
       <c r="AC14" t="s">
         <v>49</v>
       </c>
       <c r="AD14">
-        <v>0.1956</v>
+        <v>0.2048</v>
       </c>
       <c r="AE14">
-        <v>0.1959</v>
+        <v>0.1903</v>
       </c>
       <c r="AF14">
         <v>9</v>
@@ -2093,10 +2162,10 @@
         <v>0.2106</v>
       </c>
       <c r="AH14">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI14">
-        <v>0.9877</v>
+        <v>0.9652</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
@@ -2108,7 +2177,7 @@
         <v>50</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
@@ -2116,19 +2185,19 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C15">
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E15">
-        <v>-127</v>
+        <v>-123</v>
       </c>
       <c r="F15">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2143,7 +2212,7 @@
         <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N15">
         <v>823673</v>
@@ -2188,10 +2257,10 @@
         <v>4.18</v>
       </c>
       <c r="AB15">
-        <v>1.0673</v>
+        <v>1.0689</v>
       </c>
       <c r="AC15" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD15">
         <v>0.2341</v>
@@ -2206,7 +2275,7 @@
         <v>0.2383</v>
       </c>
       <c r="AH15">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI15">
         <v>0.9949</v>
@@ -2215,13 +2284,13 @@
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL15" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
@@ -2229,7 +2298,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2241,7 +2310,7 @@
         <v>-105</v>
       </c>
       <c r="F16">
-        <v>4.17</v>
+        <v>4.34</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2250,13 +2319,13 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N16">
         <v>824563</v>
@@ -2301,10 +2370,10 @@
         <v>4.45</v>
       </c>
       <c r="AB16">
-        <v>0.9859</v>
+        <v>0.9875</v>
       </c>
       <c r="AC16" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD16">
         <v>0.2162</v>
@@ -2319,7 +2388,7 @@
         <v>0.2463</v>
       </c>
       <c r="AH16">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI16">
         <v>1.0041</v>
@@ -2328,13 +2397,13 @@
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL16" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
@@ -2342,19 +2411,19 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C17">
         <v>7.5</v>
       </c>
       <c r="D17">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E17">
-        <v>-141</v>
+        <v>-137</v>
       </c>
       <c r="F17">
-        <v>7.96</v>
+        <v>7.97</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2363,13 +2432,13 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>7.96</v>
+        <v>7.97</v>
       </c>
       <c r="L17" t="s">
         <v>56</v>
       </c>
       <c r="M17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N17">
         <v>824563</v>
@@ -2414,10 +2483,10 @@
         <v>4.08</v>
       </c>
       <c r="AB17">
-        <v>1.1618</v>
+        <v>1.1636</v>
       </c>
       <c r="AC17" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD17">
         <v>0.2548</v>
@@ -2432,7 +2501,7 @@
         <v>0.2549</v>
       </c>
       <c r="AH17">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI17">
         <v>1.0408</v>
@@ -2441,10 +2510,10 @@
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL17" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2455,7 +2524,7 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C18">
         <v>5.5</v>
@@ -2476,7 +2545,7 @@
         <v>45</v>
       </c>
       <c r="M18" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N18" t="s">
         <v>45</v>
@@ -2505,7 +2574,7 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C19">
         <v>3.5</v>
@@ -2514,10 +2583,10 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>-121</v>
+        <v>-115</v>
       </c>
       <c r="F19">
-        <v>3.31</v>
+        <v>3.47</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2532,7 +2601,7 @@
         <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N19">
         <v>823019</v>
@@ -2577,10 +2646,10 @@
         <v>4.17</v>
       </c>
       <c r="AB19">
-        <v>0.8495</v>
+        <v>0.8509</v>
       </c>
       <c r="AC19" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD19">
         <v>0.1863</v>
@@ -2595,7 +2664,7 @@
         <v>0.2267</v>
       </c>
       <c r="AH19">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI19">
         <v>0.9637</v>
@@ -2604,13 +2673,13 @@
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL19" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
@@ -2618,19 +2687,19 @@
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C20">
         <v>4.5</v>
       </c>
       <c r="D20">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E20">
-        <v>-160</v>
+        <v>-145</v>
       </c>
       <c r="F20">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2645,7 +2714,7 @@
         <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N20">
         <v>823997</v>
@@ -2690,10 +2759,10 @@
         <v>4.56</v>
       </c>
       <c r="AB20">
-        <v>1.0347</v>
+        <v>1.0363</v>
       </c>
       <c r="AC20" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD20">
         <v>0.2269</v>
@@ -2708,7 +2777,7 @@
         <v>0.2197</v>
       </c>
       <c r="AH20">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI20">
         <v>1.0152</v>
@@ -2717,13 +2786,13 @@
         <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL20" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.25">
@@ -2731,7 +2800,7 @@
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C21">
         <v>4.5</v>
@@ -2752,7 +2821,7 @@
         <v>45</v>
       </c>
       <c r="M21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N21" t="s">
         <v>45</v>
@@ -2781,7 +2850,7 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C22">
         <v>2.5</v>
@@ -2790,10 +2859,10 @@
         <v>-130</v>
       </c>
       <c r="E22">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F22">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
@@ -2802,13 +2871,13 @@
         <v>45</v>
       </c>
       <c r="K22">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
       </c>
       <c r="M22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N22">
         <v>825046</v>
@@ -2853,10 +2922,10 @@
         <v>4.19</v>
       </c>
       <c r="AB22">
-        <v>0.8047</v>
+        <v>0.8059</v>
       </c>
       <c r="AC22" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD22">
         <v>0.1765</v>
@@ -2871,7 +2940,7 @@
         <v>0.2003</v>
       </c>
       <c r="AH22">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI22">
         <v>0.9452</v>
@@ -2880,13 +2949,13 @@
         <v>1</v>
       </c>
       <c r="AK22" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL22" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.25">
@@ -2894,19 +2963,19 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23">
         <v>4.5</v>
       </c>
       <c r="D23">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="E23">
-        <v>-146</v>
+        <v>-125</v>
       </c>
       <c r="F23">
-        <v>3.66</v>
+        <v>3.83</v>
       </c>
       <c r="H23" t="s">
         <v>45</v>
@@ -2915,13 +2984,13 @@
         <v>45</v>
       </c>
       <c r="K23">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="L23" t="s">
         <v>46</v>
       </c>
       <c r="M23" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N23">
         <v>825046</v>
@@ -2966,10 +3035,10 @@
         <v>4.41</v>
       </c>
       <c r="AB23">
-        <v>1.0505</v>
+        <v>1.0522</v>
       </c>
       <c r="AC23" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD23">
         <v>0.2304</v>
@@ -2984,7 +3053,7 @@
         <v>0.2504</v>
       </c>
       <c r="AH23">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI23">
         <v>1.0109</v>
@@ -2993,13 +3062,13 @@
         <v>1</v>
       </c>
       <c r="AK23" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL23" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.25">
@@ -3007,7 +3076,7 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C24">
         <v>3.5</v>
@@ -3016,10 +3085,10 @@
         <v>121</v>
       </c>
       <c r="E24">
-        <v>-141</v>
+        <v>-143</v>
       </c>
       <c r="F24">
-        <v>3.67</v>
+        <v>3.84</v>
       </c>
       <c r="H24" t="s">
         <v>45</v>
@@ -3028,13 +3097,13 @@
         <v>45</v>
       </c>
       <c r="K24">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="L24" t="s">
         <v>46</v>
       </c>
       <c r="M24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N24">
         <v>824970</v>
@@ -3079,10 +3148,10 @@
         <v>4.02</v>
       </c>
       <c r="AB24">
-        <v>1.1833</v>
+        <v>1.1852</v>
       </c>
       <c r="AC24" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD24">
         <v>0.2595</v>
@@ -3097,7 +3166,7 @@
         <v>0.2179</v>
       </c>
       <c r="AH24">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI24">
         <v>1.0198</v>
@@ -3106,13 +3175,13 @@
         <v>1</v>
       </c>
       <c r="AK24" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL24" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.25">
@@ -3120,19 +3189,19 @@
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C25">
         <v>3.5</v>
       </c>
       <c r="D25">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E25">
-        <v>-124</v>
+        <v>-125</v>
       </c>
       <c r="F25">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3141,13 +3210,13 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N25">
         <v>824970</v>
@@ -3192,10 +3261,10 @@
         <v>4.32</v>
       </c>
       <c r="AB25">
-        <v>0.815</v>
+        <v>0.8163</v>
       </c>
       <c r="AC25" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD25">
         <v>0.1787</v>
@@ -3210,7 +3279,7 @@
         <v>0.1929</v>
       </c>
       <c r="AH25">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI25">
         <v>0.8983</v>
@@ -3219,13 +3288,13 @@
         <v>1</v>
       </c>
       <c r="AK25" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL25" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="26" spans="1:43" x14ac:dyDescent="0.25">
@@ -3233,19 +3302,19 @@
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C26">
         <v>5.5</v>
       </c>
       <c r="D26">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E26">
-        <v>-145</v>
+        <v>-143</v>
       </c>
       <c r="F26">
-        <v>4.5</v>
+        <v>4.66</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -3260,7 +3329,7 @@
         <v>46</v>
       </c>
       <c r="M26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N26">
         <v>823264</v>
@@ -3305,10 +3374,10 @@
         <v>4.03</v>
       </c>
       <c r="AB26">
-        <v>0.7123</v>
+        <v>0.7134</v>
       </c>
       <c r="AC26" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD26">
         <v>0.1562</v>
@@ -3323,7 +3392,7 @@
         <v>0.2175</v>
       </c>
       <c r="AH26">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI26">
         <v>0.9905</v>
@@ -3332,13 +3401,13 @@
         <v>1</v>
       </c>
       <c r="AK26" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL26" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.25">
@@ -3346,19 +3415,19 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C27">
         <v>4.5</v>
       </c>
       <c r="D27">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E27">
         <v>-150</v>
       </c>
       <c r="F27">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3367,13 +3436,13 @@
         <v>45</v>
       </c>
       <c r="K27">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="L27" t="s">
         <v>46</v>
       </c>
       <c r="M27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N27">
         <v>823264</v>
@@ -3418,10 +3487,10 @@
         <v>4.37</v>
       </c>
       <c r="AB27">
-        <v>1.062</v>
+        <v>1.0636</v>
       </c>
       <c r="AC27" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD27">
         <v>0.2329</v>
@@ -3436,7 +3505,7 @@
         <v>0.2141</v>
       </c>
       <c r="AH27">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI27">
         <v>1.004</v>
@@ -3445,13 +3514,13 @@
         <v>1</v>
       </c>
       <c r="AK27" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL27" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
@@ -3459,19 +3528,19 @@
         <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C28">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D28">
-        <v>-130</v>
+        <v>-115</v>
       </c>
       <c r="E28">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F28">
-        <v>5.47</v>
+        <v>3.95</v>
       </c>
       <c r="H28" t="s">
         <v>45</v>
@@ -3480,22 +3549,22 @@
         <v>45</v>
       </c>
       <c r="K28">
-        <v>5.47</v>
+        <v>3.79</v>
       </c>
       <c r="L28" t="s">
         <v>46</v>
       </c>
       <c r="M28" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N28">
         <v>823186</v>
       </c>
       <c r="O28" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="P28">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
@@ -3504,67 +3573,67 @@
         <v>0</v>
       </c>
       <c r="S28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28">
-        <v>0.2561</v>
+        <v>0.1905</v>
       </c>
       <c r="U28">
-        <v>0.2491</v>
+        <v>0.1905</v>
       </c>
       <c r="V28">
         <v>5</v>
       </c>
       <c r="W28">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="X28">
-        <v>0.2373</v>
+        <v>0.1905</v>
       </c>
       <c r="Y28">
-        <v>0.371</v>
+        <v>0.344</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>4.19</v>
+        <v>4.7</v>
       </c>
       <c r="AB28">
-        <v>0.9878</v>
+        <v>0.9662</v>
       </c>
       <c r="AC28" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD28">
-        <v>0.2166</v>
+        <v>0.2116</v>
       </c>
       <c r="AE28">
-        <v>0.2222</v>
+        <v>0.2017</v>
       </c>
       <c r="AF28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG28">
-        <v>0.2019</v>
+        <v>0.2071</v>
       </c>
       <c r="AH28">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI28">
-        <v>0.9933</v>
+        <v>0.9797</v>
       </c>
       <c r="AJ28" t="b">
         <v>1</v>
       </c>
       <c r="AK28" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL28" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.25">
@@ -3572,19 +3641,19 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C29">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D29">
-        <v>-141</v>
+        <v>-143</v>
       </c>
       <c r="E29">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F29">
-        <v>3.78</v>
+        <v>5.63</v>
       </c>
       <c r="H29" t="s">
         <v>45</v>
@@ -3593,22 +3662,22 @@
         <v>45</v>
       </c>
       <c r="K29">
-        <v>3.78</v>
+        <v>5.47</v>
       </c>
       <c r="L29" t="s">
         <v>46</v>
       </c>
       <c r="M29" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N29">
         <v>823186</v>
       </c>
       <c r="O29" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="P29">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
@@ -3617,67 +3686,67 @@
         <v>0</v>
       </c>
       <c r="S29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>0.1905</v>
+        <v>0.2561</v>
       </c>
       <c r="U29">
-        <v>0.1905</v>
+        <v>0.2491</v>
       </c>
       <c r="V29">
         <v>5</v>
       </c>
       <c r="W29">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="X29">
-        <v>0.1905</v>
+        <v>0.2373</v>
       </c>
       <c r="Y29">
-        <v>0.344</v>
+        <v>0.371</v>
       </c>
       <c r="Z29" t="b">
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>4.7</v>
+        <v>4.19</v>
       </c>
       <c r="AB29">
-        <v>0.9647</v>
+        <v>0.9893</v>
       </c>
       <c r="AC29" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD29">
-        <v>0.2116</v>
+        <v>0.2166</v>
       </c>
       <c r="AE29">
-        <v>0.2017</v>
+        <v>0.2222</v>
       </c>
       <c r="AF29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG29">
-        <v>0.2071</v>
+        <v>0.2019</v>
       </c>
       <c r="AH29">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI29">
-        <v>0.9797</v>
+        <v>0.9933</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
       </c>
       <c r="AK29" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL29" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
@@ -3685,7 +3754,7 @@
         <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C30">
         <v>6.5</v>
@@ -3694,7 +3763,7 @@
         <v>126</v>
       </c>
       <c r="E30">
-        <v>-155</v>
+        <v>-154</v>
       </c>
       <c r="H30" t="s">
         <v>45</v>
@@ -3706,7 +3775,7 @@
         <v>45</v>
       </c>
       <c r="M30" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N30" t="s">
         <v>45</v>
@@ -3735,7 +3804,7 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C31">
         <v>4.5</v>
@@ -3747,7 +3816,7 @@
         <v>-128</v>
       </c>
       <c r="F31">
-        <v>6.53</v>
+        <v>6.21</v>
       </c>
       <c r="H31" t="s">
         <v>45</v>
@@ -3756,13 +3825,13 @@
         <v>45</v>
       </c>
       <c r="K31">
-        <v>6.2</v>
+        <v>6.21</v>
       </c>
       <c r="L31" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="M31" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N31">
         <v>823917</v>
@@ -3807,10 +3876,10 @@
         <v>4.06</v>
       </c>
       <c r="AB31">
-        <v>1.3202</v>
+        <v>1.3222</v>
       </c>
       <c r="AC31" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD31">
         <v>0.2895</v>
@@ -3825,7 +3894,7 @@
         <v>0.207</v>
       </c>
       <c r="AH31">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI31">
         <v>0.9998</v>
@@ -3834,13 +3903,13 @@
         <v>1</v>
       </c>
       <c r="AK31" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL31" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM31">
-        <v>0.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.25">
@@ -3848,10 +3917,10 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>6.44</v>
+        <v>6.37</v>
       </c>
       <c r="H32" t="s">
         <v>45</v>
@@ -3860,10 +3929,10 @@
         <v>45</v>
       </c>
       <c r="K32">
-        <v>6.11</v>
+        <v>6.37</v>
       </c>
       <c r="L32" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="M32" t="s">
         <v>54</v>
@@ -3911,28 +3980,28 @@
         <v>4.08</v>
       </c>
       <c r="AB32">
-        <v>1.0142</v>
+        <v>1.0153</v>
       </c>
       <c r="AC32" t="s">
         <v>49</v>
       </c>
       <c r="AD32">
-        <v>0.2224</v>
+        <v>0.2223</v>
       </c>
       <c r="AE32">
-        <v>0.2376</v>
+        <v>0.2583</v>
       </c>
       <c r="AF32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG32">
         <v>0.2359</v>
       </c>
       <c r="AH32">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI32">
-        <v>1.0138</v>
+        <v>1.0563</v>
       </c>
       <c r="AJ32" t="b">
         <v>1</v>
@@ -3944,7 +4013,7 @@
         <v>50</v>
       </c>
       <c r="AM32">
-        <v>0.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
@@ -3952,10 +4021,10 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F33">
-        <v>4.34</v>
+        <v>4.5</v>
       </c>
       <c r="H33" t="s">
         <v>45</v>
@@ -3970,7 +4039,7 @@
         <v>46</v>
       </c>
       <c r="M33" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N33">
         <v>824886</v>
@@ -4015,10 +4084,10 @@
         <v>4.06</v>
       </c>
       <c r="AB33">
-        <v>1.1556</v>
+        <v>1.1574</v>
       </c>
       <c r="AC33" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD33">
         <v>0.2534</v>
@@ -4033,7 +4102,7 @@
         <v>0.2315</v>
       </c>
       <c r="AH33">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI33">
         <v>0.9722</v>
@@ -4042,13 +4111,13 @@
         <v>1</v>
       </c>
       <c r="AK33" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL33" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.25">
@@ -4056,10 +4125,10 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F34">
-        <v>6.88</v>
+        <v>6.56</v>
       </c>
       <c r="H34" t="s">
         <v>45</v>
@@ -4068,13 +4137,13 @@
         <v>45</v>
       </c>
       <c r="K34">
-        <v>6.55</v>
+        <v>6.56</v>
       </c>
       <c r="L34" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="M34" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N34">
         <v>823019</v>
@@ -4119,10 +4188,10 @@
         <v>4.18</v>
       </c>
       <c r="AB34">
-        <v>0.915</v>
+        <v>0.9164</v>
       </c>
       <c r="AC34" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="AD34">
         <v>0.2007</v>
@@ -4137,7 +4206,7 @@
         <v>0.1805</v>
       </c>
       <c r="AH34">
-        <v>0.2193</v>
+        <v>0.219</v>
       </c>
       <c r="AI34">
         <v>0.9783</v>
@@ -4146,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="AK34" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AL34" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="AM34">
-        <v>0.33</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-11.xlsx
+++ b/data/k-props/2026-08-11.xlsx
@@ -172,154 +172,154 @@
     <t>Opener / bullpen game</t>
   </si>
   <si>
+    <t>Paul Skenes</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Eury Pérez</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Shota Imanaga</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
+    <t>Bryan Woo</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Ryan Weathers</t>
+  </si>
+  <si>
+    <t>Patrick Sandoval</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Dylan Cease</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>projected_regulars</t>
+  </si>
+  <si>
+    <t>Nolan McLean</t>
+  </si>
+  <si>
+    <t>New York Mets @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Bailey Ober</t>
+  </si>
+  <si>
+    <t>Nick Lodolo</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Andre Pallante</t>
+  </si>
+  <si>
+    <t>Ryan Johnson</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Athletics</t>
+  </si>
+  <si>
+    <t>Mason Barnett</t>
+  </si>
+  <si>
+    <t>Kyle Harrison</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Walker Buehler</t>
+  </si>
+  <si>
+    <t>Hunter Brown</t>
+  </si>
+  <si>
+    <t>Houston Astros @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Carson Whisenhunt</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Dodgers</t>
+  </si>
+  <si>
     <t>Eury Perez</t>
   </si>
   <si>
-    <t>Pittsburgh Pirates @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Paul Skenes</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Shota Imanaga</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Jake Irvin</t>
-  </si>
-  <si>
-    <t>Bryan Woo</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Ryan Weathers</t>
-  </si>
-  <si>
-    <t>Dylan Cease</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>projected_regulars</t>
-  </si>
-  <si>
-    <t>Patrick Sandoval</t>
-  </si>
-  <si>
     <t>Martin Perez</t>
   </si>
   <si>
-    <t>New York Mets @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Nolan McLean</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Bailey Ober</t>
-  </si>
-  <si>
-    <t>Nick Lodolo</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
     <t>Cristopher Sanchez</t>
   </si>
   <si>
-    <t>Philadelphia Phillies @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Andre Pallante</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Los Angeles Angels</t>
-  </si>
-  <si>
     <t>Cody Bradford</t>
   </si>
   <si>
-    <t>Tomoyuki Sugano</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Athletics</t>
-  </si>
-  <si>
-    <t>Mason Barnett</t>
-  </si>
-  <si>
-    <t>Kyle Harrison</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Walker Buehler</t>
-  </si>
-  <si>
-    <t>Carson Whisenhunt</t>
-  </si>
-  <si>
-    <t>Houston Astros @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Hunter Brown</t>
-  </si>
-  <si>
     <t>Blake Snell</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Michael Wacha</t>
-  </si>
-  <si>
-    <t>Eury Pérez</t>
-  </si>
-  <si>
-    <t>Martín Pérez</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
   </si>
 </sst>
 </file>
@@ -854,7 +854,7 @@
         <v>-108</v>
       </c>
       <c r="F2">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -863,7 +863,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -914,7 +914,7 @@
         <v>4.05</v>
       </c>
       <c r="AB2">
-        <v>0.9337</v>
+        <v>0.9307</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
@@ -932,7 +932,7 @@
         <v>0.2261</v>
       </c>
       <c r="AH2">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI2">
         <v>0.9619</v>
@@ -947,7 +947,7 @@
         <v>50</v>
       </c>
       <c r="AM2">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
@@ -967,7 +967,7 @@
         <v>-150</v>
       </c>
       <c r="F3">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -976,7 +976,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -1027,7 +1027,7 @@
         <v>4.29</v>
       </c>
       <c r="AB3">
-        <v>0.8976</v>
+        <v>0.8947</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
@@ -1045,7 +1045,7 @@
         <v>0.2176</v>
       </c>
       <c r="AH3">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI3">
         <v>0.88</v>
@@ -1060,7 +1060,7 @@
         <v>50</v>
       </c>
       <c r="AM3">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
@@ -1074,10 +1074,13 @@
         <v>6.5</v>
       </c>
       <c r="D4">
-        <v>102</v>
+        <v>-146</v>
       </c>
       <c r="E4">
-        <v>-125</v>
+        <v>120</v>
+      </c>
+      <c r="F4">
+        <v>6.74</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1085,32 +1088,92 @@
       <c r="J4" t="s">
         <v>45</v>
       </c>
+      <c r="K4">
+        <v>7.13</v>
+      </c>
       <c r="L4" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N4" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="N4">
+        <v>823832</v>
       </c>
       <c r="O4" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P4">
+        <v>5.4</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
       </c>
       <c r="S4">
         <v>6</v>
       </c>
+      <c r="T4">
+        <v>0.3045</v>
+      </c>
+      <c r="U4">
+        <v>0.3202</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="W4">
+        <v>112</v>
+      </c>
+      <c r="X4">
+        <v>0.3482</v>
+      </c>
+      <c r="Y4">
+        <v>0.359</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>4.1</v>
+      </c>
+      <c r="AB4">
+        <v>1.1017</v>
+      </c>
       <c r="AC4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="AD4">
+        <v>0.242</v>
+      </c>
+      <c r="AE4">
+        <v>0.2322</v>
+      </c>
+      <c r="AF4">
+        <v>9</v>
+      </c>
+      <c r="AG4">
+        <v>0.2096</v>
+      </c>
+      <c r="AH4">
+        <v>0.2197</v>
+      </c>
+      <c r="AI4">
+        <v>0.9124</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="AM4">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
@@ -1118,34 +1181,25 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5">
+        <v>6.35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5">
+        <v>6.35</v>
+      </c>
+      <c r="L5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" t="s">
         <v>55</v>
-      </c>
-      <c r="C5">
-        <v>6.5</v>
-      </c>
-      <c r="D5">
-        <v>-146</v>
-      </c>
-      <c r="E5">
-        <v>120</v>
-      </c>
-      <c r="F5">
-        <v>7.16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5">
-        <v>7.16</v>
-      </c>
-      <c r="L5" t="s">
-        <v>56</v>
-      </c>
-      <c r="M5" t="s">
-        <v>54</v>
       </c>
       <c r="N5">
         <v>823832</v>
@@ -1154,7 +1208,7 @@
         <v>48</v>
       </c>
       <c r="P5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1163,55 +1217,55 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.3045</v>
+        <v>0.2707</v>
       </c>
       <c r="U5">
-        <v>0.3202</v>
+        <v>0.2659</v>
       </c>
       <c r="V5">
         <v>5</v>
       </c>
       <c r="W5">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="X5">
-        <v>0.3482</v>
+        <v>0.2581</v>
       </c>
       <c r="Y5">
-        <v>0.359</v>
+        <v>0.383</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="AB5">
-        <v>1.1053</v>
+        <v>1.012</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
       </c>
       <c r="AD5">
-        <v>0.242</v>
+        <v>0.2223</v>
       </c>
       <c r="AE5">
-        <v>0.2322</v>
+        <v>0.2583</v>
       </c>
       <c r="AF5">
         <v>9</v>
       </c>
       <c r="AG5">
-        <v>0.2096</v>
+        <v>0.2359</v>
       </c>
       <c r="AH5">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI5">
-        <v>0.9124</v>
+        <v>1.0563</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
@@ -1231,7 +1285,7 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>5.5</v>
@@ -1243,7 +1297,7 @@
         <v>-143</v>
       </c>
       <c r="F6">
-        <v>5.05</v>
+        <v>4.88</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1252,13 +1306,13 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N6">
         <v>822697</v>
@@ -1303,7 +1357,7 @@
         <v>4.02</v>
       </c>
       <c r="AB6">
-        <v>0.9045</v>
+        <v>0.9016</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
@@ -1321,7 +1375,7 @@
         <v>0.2352</v>
       </c>
       <c r="AH6">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI6">
         <v>1.0324</v>
@@ -1336,7 +1390,7 @@
         <v>50</v>
       </c>
       <c r="AM6">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
@@ -1344,7 +1398,7 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>4.5</v>
@@ -1356,7 +1410,7 @@
         <v>-155</v>
       </c>
       <c r="F7">
-        <v>4.87</v>
+        <v>4.7</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1365,13 +1419,13 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>4.71</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
       </c>
       <c r="M7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N7">
         <v>822697</v>
@@ -1416,7 +1470,7 @@
         <v>4.32</v>
       </c>
       <c r="AB7">
-        <v>1.0212</v>
+        <v>1.0179</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
@@ -1434,7 +1488,7 @@
         <v>0.218</v>
       </c>
       <c r="AH7">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI7">
         <v>0.9719</v>
@@ -1449,7 +1503,7 @@
         <v>50</v>
       </c>
       <c r="AM7">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
@@ -1457,7 +1511,7 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>6.5</v>
@@ -1469,7 +1523,7 @@
         <v>-134</v>
       </c>
       <c r="F8">
-        <v>6.87</v>
+        <v>6.84</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1478,10 +1532,10 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>6.87</v>
+        <v>6.84</v>
       </c>
       <c r="L8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M8" t="s">
         <v>62</v>
@@ -1529,7 +1583,7 @@
         <v>4.11</v>
       </c>
       <c r="AB8">
-        <v>1.1701</v>
+        <v>1.1664</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
@@ -1547,7 +1601,7 @@
         <v>0.2439</v>
       </c>
       <c r="AH8">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI8">
         <v>1.018</v>
@@ -1582,7 +1636,7 @@
         <v>-145</v>
       </c>
       <c r="F9">
-        <v>6.01</v>
+        <v>5.83</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1591,7 +1645,7 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>5.85</v>
+        <v>5.83</v>
       </c>
       <c r="L9" t="s">
         <v>46</v>
@@ -1642,7 +1696,7 @@
         <v>4.16</v>
       </c>
       <c r="AB9">
-        <v>1.042</v>
+        <v>1.0387</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
@@ -1660,7 +1714,7 @@
         <v>0.2371</v>
       </c>
       <c r="AH9">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI9">
         <v>0.9673</v>
@@ -1675,7 +1729,7 @@
         <v>50</v>
       </c>
       <c r="AM9">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
@@ -1686,16 +1740,16 @@
         <v>64</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="D10">
-        <v>-143</v>
+        <v>124</v>
       </c>
       <c r="E10">
-        <v>124</v>
+        <v>-134</v>
       </c>
       <c r="F10">
-        <v>7.4</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1704,10 +1758,10 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>7.4</v>
+        <v>2.82</v>
       </c>
       <c r="L10" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M10" t="s">
         <v>65</v>
@@ -1719,7 +1773,7 @@
         <v>48</v>
       </c>
       <c r="P10">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1731,61 +1785,61 @@
         <v>6</v>
       </c>
       <c r="T10">
-        <v>0.3644</v>
+        <v>0.2294</v>
       </c>
       <c r="U10">
-        <v>0.3611</v>
+        <v>0.2294</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="X10">
-        <v>0.3561</v>
+        <v>0.2294</v>
       </c>
       <c r="Y10">
-        <v>0.398</v>
+        <v>0.353</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>4</v>
+        <v>4.54</v>
       </c>
       <c r="AB10">
-        <v>0.8601</v>
+        <v>0.6417</v>
       </c>
       <c r="AC10" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="AD10">
-        <v>0.1884</v>
+        <v>0.141</v>
       </c>
       <c r="AE10">
-        <v>0.1881</v>
+        <v>0.1474</v>
       </c>
       <c r="AF10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG10">
-        <v>0.2185</v>
+        <v>0.2164</v>
       </c>
       <c r="AH10">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI10">
-        <v>0.9912</v>
+        <v>0.88</v>
       </c>
       <c r="AJ10" t="b">
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -1796,19 +1850,19 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="D11">
+        <v>-143</v>
+      </c>
+      <c r="E11">
         <v>124</v>
       </c>
-      <c r="E11">
-        <v>-134</v>
-      </c>
       <c r="F11">
-        <v>3.69</v>
+        <v>6.99</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1817,10 +1871,10 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>3.53</v>
+        <v>7.38</v>
       </c>
       <c r="L11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M11" t="s">
         <v>65</v>
@@ -1832,7 +1886,7 @@
         <v>48</v>
       </c>
       <c r="P11">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
@@ -1844,64 +1898,64 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>0.2294</v>
+        <v>0.3644</v>
       </c>
       <c r="U11">
-        <v>0.2294</v>
+        <v>0.3611</v>
       </c>
       <c r="V11">
         <v>5</v>
       </c>
       <c r="W11">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="X11">
-        <v>0.2294</v>
+        <v>0.3561</v>
       </c>
       <c r="Y11">
-        <v>0.353</v>
+        <v>0.398</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="AB11">
-        <v>0.7321</v>
+        <v>0.8574</v>
       </c>
       <c r="AC11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="AD11">
-        <v>0.1603</v>
+        <v>0.1884</v>
       </c>
       <c r="AE11">
-        <v>0.175</v>
+        <v>0.1881</v>
       </c>
       <c r="AF11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG11">
-        <v>0.2164</v>
+        <v>0.2185</v>
       </c>
       <c r="AH11">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI11">
-        <v>0.9645</v>
+        <v>0.9912</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AL11" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AM11">
-        <v>0.16</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
@@ -1912,13 +1966,16 @@
         <v>69</v>
       </c>
       <c r="C12">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D12">
-        <v>-131</v>
+        <v>-155</v>
       </c>
       <c r="E12">
-        <v>106</v>
+        <v>122</v>
+      </c>
+      <c r="F12">
+        <v>6.61</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1926,32 +1983,92 @@
       <c r="J12" t="s">
         <v>45</v>
       </c>
+      <c r="K12">
+        <v>7</v>
+      </c>
       <c r="L12" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="M12" t="s">
         <v>70</v>
       </c>
-      <c r="N12" t="s">
-        <v>45</v>
+      <c r="N12">
+        <v>824886</v>
       </c>
       <c r="O12" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P12">
+        <v>5.7</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
       </c>
       <c r="S12">
+        <v>6</v>
+      </c>
+      <c r="T12">
+        <v>0.2847</v>
+      </c>
+      <c r="U12">
+        <v>0.2912</v>
+      </c>
+      <c r="V12">
         <v>5</v>
       </c>
+      <c r="W12">
+        <v>126</v>
+      </c>
+      <c r="X12">
+        <v>0.3016</v>
+      </c>
+      <c r="Y12">
+        <v>0.387</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>4.19</v>
+      </c>
+      <c r="AB12">
+        <v>1.0081</v>
+      </c>
       <c r="AC12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="AD12">
+        <v>0.2215</v>
+      </c>
+      <c r="AE12">
+        <v>0.2152</v>
+      </c>
+      <c r="AF12">
+        <v>9</v>
+      </c>
+      <c r="AG12">
+        <v>0.2179</v>
+      </c>
+      <c r="AH12">
+        <v>0.2197</v>
+      </c>
+      <c r="AI12">
+        <v>1.001</v>
+      </c>
+      <c r="AJ12" t="b">
+        <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="AM12">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
@@ -1961,17 +2078,8 @@
       <c r="B13" t="s">
         <v>71</v>
       </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-      <c r="D13">
-        <v>-155</v>
-      </c>
-      <c r="E13">
-        <v>122</v>
-      </c>
       <c r="F13">
-        <v>7.39</v>
+        <v>5.04</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -1980,10 +2088,10 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>7.39</v>
+        <v>5.04</v>
       </c>
       <c r="L13" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M13" t="s">
         <v>70</v>
@@ -1995,7 +2103,7 @@
         <v>48</v>
       </c>
       <c r="P13">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -2004,64 +2112,64 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>0.2847</v>
+        <v>0.1916</v>
       </c>
       <c r="U13">
-        <v>0.2912</v>
+        <v>0.1882</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="X13">
-        <v>0.3016</v>
+        <v>0.1809</v>
       </c>
       <c r="Y13">
-        <v>0.387</v>
+        <v>0.32</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="AB13">
-        <v>1.073</v>
+        <v>1.3565</v>
       </c>
       <c r="AC13" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="AD13">
-        <v>0.235</v>
+        <v>0.298</v>
       </c>
       <c r="AE13">
-        <v>0.2267</v>
+        <v>0.2803</v>
       </c>
       <c r="AF13">
         <v>9</v>
       </c>
       <c r="AG13">
-        <v>0.2179</v>
+        <v>0.2315</v>
       </c>
       <c r="AH13">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI13">
-        <v>0.9931</v>
+        <v>0.9621</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AL13" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2084,7 +2192,7 @@
         <v>-152</v>
       </c>
       <c r="F14">
-        <v>4.6</v>
+        <v>4.43</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2093,7 +2201,7 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
@@ -2144,7 +2252,7 @@
         <v>4.26</v>
       </c>
       <c r="AB14">
-        <v>0.9354</v>
+        <v>0.9324</v>
       </c>
       <c r="AC14" t="s">
         <v>49</v>
@@ -2162,7 +2270,7 @@
         <v>0.2106</v>
       </c>
       <c r="AH14">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI14">
         <v>0.9652</v>
@@ -2177,7 +2285,7 @@
         <v>50</v>
       </c>
       <c r="AM14">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
@@ -2197,7 +2305,7 @@
         <v>-123</v>
       </c>
       <c r="F15">
-        <v>4.06</v>
+        <v>4.42</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2206,7 +2314,7 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>3.9</v>
+        <v>4.42</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
@@ -2257,16 +2365,16 @@
         <v>4.18</v>
       </c>
       <c r="AB15">
-        <v>1.0689</v>
+        <v>1.1753</v>
       </c>
       <c r="AC15" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="AD15">
-        <v>0.2341</v>
+        <v>0.2582</v>
       </c>
       <c r="AE15">
-        <v>0.265</v>
+        <v>0.2534</v>
       </c>
       <c r="AF15">
         <v>9</v>
@@ -2275,22 +2383,22 @@
         <v>0.2383</v>
       </c>
       <c r="AH15">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI15">
-        <v>0.9949</v>
+        <v>1.0256</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AL15" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AM15">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
@@ -2310,7 +2418,7 @@
         <v>-105</v>
       </c>
       <c r="F16">
-        <v>4.34</v>
+        <v>4.65</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2319,7 +2427,7 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.18</v>
+        <v>4.65</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
@@ -2370,16 +2478,16 @@
         <v>4.45</v>
       </c>
       <c r="AB16">
-        <v>0.9875</v>
+        <v>1.0505</v>
       </c>
       <c r="AC16" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="AD16">
-        <v>0.2162</v>
+        <v>0.2308</v>
       </c>
       <c r="AE16">
-        <v>0.2394</v>
+        <v>0.2581</v>
       </c>
       <c r="AF16">
         <v>9</v>
@@ -2388,22 +2496,22 @@
         <v>0.2463</v>
       </c>
       <c r="AH16">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI16">
-        <v>1.0041</v>
+        <v>1.0504</v>
       </c>
       <c r="AJ16" t="b">
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AL16" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AM16">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
@@ -2423,7 +2531,7 @@
         <v>-137</v>
       </c>
       <c r="F17">
-        <v>7.97</v>
+        <v>8.44</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2432,10 +2540,10 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>7.97</v>
+        <v>8.83</v>
       </c>
       <c r="L17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M17" t="s">
         <v>76</v>
@@ -2483,16 +2591,16 @@
         <v>4.08</v>
       </c>
       <c r="AB17">
-        <v>1.1636</v>
+        <v>1.2366</v>
       </c>
       <c r="AC17" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="AD17">
-        <v>0.2548</v>
+        <v>0.2717</v>
       </c>
       <c r="AE17">
-        <v>0.2676</v>
+        <v>0.2781</v>
       </c>
       <c r="AF17">
         <v>9</v>
@@ -2501,22 +2609,22 @@
         <v>0.2549</v>
       </c>
       <c r="AH17">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI17">
-        <v>1.0408</v>
+        <v>1.0843</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AL17" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.25">
@@ -2526,14 +2634,8 @@
       <c r="B18" t="s">
         <v>78</v>
       </c>
-      <c r="C18">
-        <v>5.5</v>
-      </c>
-      <c r="D18">
-        <v>-146</v>
-      </c>
-      <c r="E18">
-        <v>125</v>
+      <c r="F18">
+        <v>6.73</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2541,32 +2643,92 @@
       <c r="J18" t="s">
         <v>45</v>
       </c>
+      <c r="K18">
+        <v>7.12</v>
+      </c>
       <c r="L18" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="M18" t="s">
         <v>79</v>
       </c>
-      <c r="N18" t="s">
-        <v>45</v>
+      <c r="N18">
+        <v>823019</v>
       </c>
       <c r="O18" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P18">
+        <v>6.2</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0.278</v>
+      </c>
+      <c r="U18">
+        <v>0.2806</v>
+      </c>
+      <c r="V18">
+        <v>5</v>
+      </c>
+      <c r="W18">
+        <v>130</v>
+      </c>
+      <c r="X18">
+        <v>0.2846</v>
+      </c>
+      <c r="Y18">
+        <v>0.394</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>4.18</v>
+      </c>
+      <c r="AB18">
+        <v>1.0452</v>
       </c>
       <c r="AC18" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="AD18">
+        <v>0.2296</v>
+      </c>
+      <c r="AE18">
+        <v>0.1905</v>
+      </c>
+      <c r="AF18">
+        <v>9</v>
+      </c>
+      <c r="AG18">
+        <v>0.1805</v>
+      </c>
+      <c r="AH18">
+        <v>0.2197</v>
+      </c>
+      <c r="AI18">
+        <v>0.9303</v>
+      </c>
+      <c r="AJ18" t="b">
+        <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AL18" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="AM18">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
@@ -2586,7 +2748,7 @@
         <v>-115</v>
       </c>
       <c r="F19">
-        <v>3.47</v>
+        <v>3.18</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2595,7 +2757,7 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
@@ -2646,10 +2808,10 @@
         <v>4.17</v>
       </c>
       <c r="AB19">
-        <v>0.8509</v>
+        <v>0.8481</v>
       </c>
       <c r="AC19" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="AD19">
         <v>0.1863</v>
@@ -2664,22 +2826,22 @@
         <v>0.2267</v>
       </c>
       <c r="AH19">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI19">
-        <v>0.9637</v>
+        <v>0.9274</v>
       </c>
       <c r="AJ19" t="b">
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AL19" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AM19">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
@@ -2699,7 +2861,7 @@
         <v>-145</v>
       </c>
       <c r="F20">
-        <v>3.58</v>
+        <v>3.41</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2708,7 +2870,7 @@
         <v>45</v>
       </c>
       <c r="K20">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="L20" t="s">
         <v>46</v>
@@ -2759,10 +2921,10 @@
         <v>4.56</v>
       </c>
       <c r="AB20">
-        <v>1.0363</v>
+        <v>1.033</v>
       </c>
       <c r="AC20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD20">
         <v>0.2269</v>
@@ -2777,7 +2939,7 @@
         <v>0.2197</v>
       </c>
       <c r="AH20">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI20">
         <v>1.0152</v>
@@ -2786,13 +2948,13 @@
         <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AL20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AM20">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.25">
@@ -2803,13 +2965,16 @@
         <v>83</v>
       </c>
       <c r="C21">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D21">
-        <v>-148</v>
+        <v>-130</v>
       </c>
       <c r="E21">
-        <v>120</v>
+        <v>107</v>
+      </c>
+      <c r="F21">
+        <v>2.47</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -2817,32 +2982,92 @@
       <c r="J21" t="s">
         <v>45</v>
       </c>
+      <c r="K21">
+        <v>2.47</v>
+      </c>
       <c r="L21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>82</v>
-      </c>
-      <c r="N21" t="s">
-        <v>45</v>
+        <v>84</v>
+      </c>
+      <c r="N21">
+        <v>825046</v>
       </c>
       <c r="O21" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P21">
+        <v>5.4</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
       </c>
       <c r="S21">
         <v>6</v>
       </c>
+      <c r="T21">
+        <v>0.1353</v>
+      </c>
+      <c r="U21">
+        <v>0.1331</v>
+      </c>
+      <c r="V21">
+        <v>5</v>
+      </c>
+      <c r="W21">
+        <v>116</v>
+      </c>
+      <c r="X21">
+        <v>0.1293</v>
+      </c>
+      <c r="Y21">
+        <v>0.367</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>4.19</v>
+      </c>
+      <c r="AB21">
+        <v>0.8647</v>
+      </c>
       <c r="AC21" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="AD21">
+        <v>0.19</v>
+      </c>
+      <c r="AE21">
+        <v>0.1889</v>
+      </c>
+      <c r="AF21">
+        <v>9</v>
+      </c>
+      <c r="AG21">
+        <v>0.2003</v>
+      </c>
+      <c r="AH21">
+        <v>0.2197</v>
+      </c>
+      <c r="AI21">
+        <v>0.9517</v>
+      </c>
+      <c r="AJ21" t="b">
+        <v>1</v>
       </c>
       <c r="AK21" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AL21" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.25">
@@ -2850,19 +3075,19 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D22">
-        <v>-130</v>
+        <v>106</v>
       </c>
       <c r="E22">
-        <v>107</v>
+        <v>-125</v>
       </c>
       <c r="F22">
-        <v>2.45</v>
+        <v>3.66</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
@@ -2871,13 +3096,13 @@
         <v>45</v>
       </c>
       <c r="K22">
-        <v>2.29</v>
+        <v>3.66</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
       </c>
       <c r="M22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N22">
         <v>825046</v>
@@ -2886,7 +3111,7 @@
         <v>48</v>
       </c>
       <c r="P22">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -2898,64 +3123,64 @@
         <v>6</v>
       </c>
       <c r="T22">
-        <v>0.1353</v>
+        <v>0.1721</v>
       </c>
       <c r="U22">
-        <v>0.1331</v>
+        <v>0.1697</v>
       </c>
       <c r="V22">
         <v>5</v>
       </c>
       <c r="W22">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="X22">
-        <v>0.1293</v>
+        <v>0.1651</v>
       </c>
       <c r="Y22">
-        <v>0.367</v>
+        <v>0.353</v>
       </c>
       <c r="Z22" t="b">
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>4.19</v>
+        <v>4.41</v>
       </c>
       <c r="AB22">
-        <v>0.8059</v>
+        <v>1.0488</v>
       </c>
       <c r="AC22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD22">
-        <v>0.1765</v>
+        <v>0.2304</v>
       </c>
       <c r="AE22">
-        <v>0.1756</v>
+        <v>0.2281</v>
       </c>
       <c r="AF22">
         <v>9</v>
       </c>
       <c r="AG22">
-        <v>0.2003</v>
+        <v>0.2504</v>
       </c>
       <c r="AH22">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI22">
-        <v>0.9452</v>
+        <v>1.0109</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
       </c>
       <c r="AK22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AL22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AM22">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.25">
@@ -2966,16 +3191,16 @@
         <v>86</v>
       </c>
       <c r="C23">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D23">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="E23">
-        <v>-125</v>
+        <v>-143</v>
       </c>
       <c r="F23">
-        <v>3.83</v>
+        <v>2.67</v>
       </c>
       <c r="H23" t="s">
         <v>45</v>
@@ -2984,22 +3209,22 @@
         <v>45</v>
       </c>
       <c r="K23">
-        <v>3.67</v>
+        <v>2.67</v>
       </c>
       <c r="L23" t="s">
         <v>46</v>
       </c>
       <c r="M23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N23">
-        <v>825046</v>
+        <v>824970</v>
       </c>
       <c r="O23" t="s">
         <v>48</v>
       </c>
       <c r="P23">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -3011,64 +3236,64 @@
         <v>6</v>
       </c>
       <c r="T23">
-        <v>0.1721</v>
+        <v>0.1407</v>
       </c>
       <c r="U23">
-        <v>0.1697</v>
+        <v>0.129</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="X23">
-        <v>0.1651</v>
+        <v>0.1081</v>
       </c>
       <c r="Y23">
-        <v>0.353</v>
+        <v>0.357</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>4.41</v>
+        <v>4.02</v>
       </c>
       <c r="AB23">
-        <v>1.0522</v>
+        <v>0.8979</v>
       </c>
       <c r="AC23" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="AD23">
-        <v>0.2304</v>
+        <v>0.1973</v>
       </c>
       <c r="AE23">
-        <v>0.2281</v>
+        <v>0.1912</v>
       </c>
       <c r="AF23">
         <v>9</v>
       </c>
       <c r="AG23">
-        <v>0.2504</v>
+        <v>0.2179</v>
       </c>
       <c r="AH23">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI23">
-        <v>1.0109</v>
+        <v>0.9786</v>
       </c>
       <c r="AJ23" t="b">
         <v>1</v>
       </c>
       <c r="AK23" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AL23" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AM23">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.25">
@@ -3076,19 +3301,19 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24">
         <v>3.5</v>
       </c>
       <c r="D24">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="E24">
-        <v>-143</v>
+        <v>-125</v>
       </c>
       <c r="F24">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="H24" t="s">
         <v>45</v>
@@ -3097,13 +3322,13 @@
         <v>45</v>
       </c>
       <c r="K24">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="L24" t="s">
         <v>46</v>
       </c>
       <c r="M24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N24">
         <v>824970</v>
@@ -3112,7 +3337,7 @@
         <v>48</v>
       </c>
       <c r="P24">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -3124,64 +3349,64 @@
         <v>6</v>
       </c>
       <c r="T24">
-        <v>0.1407</v>
+        <v>0.2449</v>
       </c>
       <c r="U24">
-        <v>0.129</v>
+        <v>0.2561</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W24">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="X24">
-        <v>0.1081</v>
+        <v>0.3095</v>
       </c>
       <c r="Y24">
-        <v>0.357</v>
+        <v>0.174</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>4.02</v>
+        <v>4.32</v>
       </c>
       <c r="AB24">
-        <v>1.1852</v>
+        <v>0.8136</v>
       </c>
       <c r="AC24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD24">
-        <v>0.2595</v>
+        <v>0.1787</v>
       </c>
       <c r="AE24">
-        <v>0.2292</v>
+        <v>0.1753</v>
       </c>
       <c r="AF24">
         <v>9</v>
       </c>
       <c r="AG24">
-        <v>0.2179</v>
+        <v>0.1929</v>
       </c>
       <c r="AH24">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI24">
-        <v>1.0198</v>
+        <v>0.8983</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AL24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AM24">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.25">
@@ -3192,16 +3417,16 @@
         <v>89</v>
       </c>
       <c r="C25">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D25">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E25">
-        <v>-125</v>
+        <v>-143</v>
       </c>
       <c r="F25">
-        <v>3.95</v>
+        <v>4.81</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3210,22 +3435,22 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>3.79</v>
+        <v>4.81</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N25">
-        <v>824970</v>
+        <v>823264</v>
       </c>
       <c r="O25" t="s">
         <v>48</v>
       </c>
       <c r="P25">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -3237,64 +3462,64 @@
         <v>6</v>
       </c>
       <c r="T25">
-        <v>0.2449</v>
+        <v>0.3109</v>
       </c>
       <c r="U25">
-        <v>0.2561</v>
+        <v>0.3213</v>
       </c>
       <c r="V25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="X25">
-        <v>0.3095</v>
+        <v>0.3444</v>
       </c>
       <c r="Y25">
-        <v>0.174</v>
+        <v>0.31</v>
       </c>
       <c r="Z25" t="b">
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>4.32</v>
+        <v>4.03</v>
       </c>
       <c r="AB25">
-        <v>0.8163</v>
+        <v>0.7446</v>
       </c>
       <c r="AC25" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="AD25">
-        <v>0.1787</v>
+        <v>0.1636</v>
       </c>
       <c r="AE25">
-        <v>0.1753</v>
+        <v>0.182</v>
       </c>
       <c r="AF25">
         <v>9</v>
       </c>
       <c r="AG25">
-        <v>0.1929</v>
+        <v>0.2175</v>
       </c>
       <c r="AH25">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI25">
-        <v>0.8983</v>
+        <v>1.0142</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
       </c>
       <c r="AK25" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AL25" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AM25">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:43" x14ac:dyDescent="0.25">
@@ -3302,19 +3527,19 @@
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C26">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D26">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E26">
-        <v>-143</v>
+        <v>-150</v>
       </c>
       <c r="F26">
-        <v>4.66</v>
+        <v>4.05</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -3323,13 +3548,13 @@
         <v>45</v>
       </c>
       <c r="K26">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="L26" t="s">
         <v>46</v>
       </c>
       <c r="M26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N26">
         <v>823264</v>
@@ -3338,7 +3563,7 @@
         <v>48</v>
       </c>
       <c r="P26">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -3350,64 +3575,64 @@
         <v>6</v>
       </c>
       <c r="T26">
-        <v>0.3109</v>
+        <v>0.2008</v>
       </c>
       <c r="U26">
-        <v>0.3213</v>
+        <v>0.1851</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
       <c r="W26">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="X26">
-        <v>0.3444</v>
+        <v>0.1531</v>
       </c>
       <c r="Y26">
-        <v>0.31</v>
+        <v>0.329</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>4.03</v>
+        <v>4.37</v>
       </c>
       <c r="AB26">
-        <v>0.7134</v>
+        <v>1.0602</v>
       </c>
       <c r="AC26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD26">
-        <v>0.1562</v>
+        <v>0.2329</v>
       </c>
       <c r="AE26">
-        <v>0.1742</v>
+        <v>0.237</v>
       </c>
       <c r="AF26">
         <v>9</v>
       </c>
       <c r="AG26">
-        <v>0.2175</v>
+        <v>0.2141</v>
       </c>
       <c r="AH26">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI26">
-        <v>0.9905</v>
+        <v>1.004</v>
       </c>
       <c r="AJ26" t="b">
         <v>1</v>
       </c>
       <c r="AK26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AL26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AM26">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.25">
@@ -3418,16 +3643,16 @@
         <v>92</v>
       </c>
       <c r="C27">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D27">
-        <v>122</v>
+        <v>-143</v>
       </c>
       <c r="E27">
-        <v>-150</v>
+        <v>115</v>
       </c>
       <c r="F27">
-        <v>4.23</v>
+        <v>5.46</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3436,22 +3661,22 @@
         <v>45</v>
       </c>
       <c r="K27">
-        <v>4.07</v>
+        <v>5.46</v>
       </c>
       <c r="L27" t="s">
         <v>46</v>
       </c>
       <c r="M27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N27">
-        <v>823264</v>
+        <v>823186</v>
       </c>
       <c r="O27" t="s">
         <v>48</v>
       </c>
       <c r="P27">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -3463,64 +3688,64 @@
         <v>6</v>
       </c>
       <c r="T27">
-        <v>0.2008</v>
+        <v>0.2561</v>
       </c>
       <c r="U27">
-        <v>0.1851</v>
+        <v>0.2491</v>
       </c>
       <c r="V27">
         <v>5</v>
       </c>
       <c r="W27">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="X27">
-        <v>0.1531</v>
+        <v>0.2373</v>
       </c>
       <c r="Y27">
-        <v>0.329</v>
+        <v>0.371</v>
       </c>
       <c r="Z27" t="b">
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>4.37</v>
+        <v>4.19</v>
       </c>
       <c r="AB27">
-        <v>1.0636</v>
+        <v>0.9861</v>
       </c>
       <c r="AC27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD27">
-        <v>0.2329</v>
+        <v>0.2166</v>
       </c>
       <c r="AE27">
-        <v>0.237</v>
+        <v>0.2222</v>
       </c>
       <c r="AF27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG27">
-        <v>0.2141</v>
+        <v>0.2019</v>
       </c>
       <c r="AH27">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI27">
-        <v>1.004</v>
+        <v>0.9933</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
       </c>
       <c r="AK27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AL27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AM27">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
@@ -3528,7 +3753,7 @@
         <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28">
         <v>3.5</v>
@@ -3540,7 +3765,7 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>3.95</v>
+        <v>3.77</v>
       </c>
       <c r="H28" t="s">
         <v>45</v>
@@ -3549,13 +3774,13 @@
         <v>45</v>
       </c>
       <c r="K28">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="L28" t="s">
         <v>46</v>
       </c>
       <c r="M28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N28">
         <v>823186</v>
@@ -3600,10 +3825,10 @@
         <v>4.7</v>
       </c>
       <c r="AB28">
-        <v>0.9662</v>
+        <v>0.9631</v>
       </c>
       <c r="AC28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD28">
         <v>0.2116</v>
@@ -3618,7 +3843,7 @@
         <v>0.2071</v>
       </c>
       <c r="AH28">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI28">
         <v>0.9797</v>
@@ -3627,13 +3852,13 @@
         <v>1</v>
       </c>
       <c r="AK28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AL28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AM28">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.25">
@@ -3644,16 +3869,16 @@
         <v>96</v>
       </c>
       <c r="C29">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D29">
-        <v>-143</v>
+        <v>111</v>
       </c>
       <c r="E29">
-        <v>115</v>
+        <v>-128</v>
       </c>
       <c r="F29">
-        <v>5.63</v>
+        <v>6.19</v>
       </c>
       <c r="H29" t="s">
         <v>45</v>
@@ -3662,22 +3887,22 @@
         <v>45</v>
       </c>
       <c r="K29">
-        <v>5.47</v>
+        <v>6.19</v>
       </c>
       <c r="L29" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="M29" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N29">
-        <v>823186</v>
+        <v>823917</v>
       </c>
       <c r="O29" t="s">
         <v>48</v>
       </c>
       <c r="P29">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
@@ -3689,64 +3914,64 @@
         <v>6</v>
       </c>
       <c r="T29">
-        <v>0.2561</v>
+        <v>0.1915</v>
       </c>
       <c r="U29">
-        <v>0.2491</v>
+        <v>0.1847</v>
       </c>
       <c r="V29">
         <v>5</v>
       </c>
       <c r="W29">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X29">
-        <v>0.2373</v>
+        <v>0.1736</v>
       </c>
       <c r="Y29">
-        <v>0.371</v>
+        <v>0.377</v>
       </c>
       <c r="Z29" t="b">
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="AB29">
-        <v>0.9893</v>
+        <v>1.318</v>
       </c>
       <c r="AC29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD29">
-        <v>0.2166</v>
+        <v>0.2895</v>
       </c>
       <c r="AE29">
-        <v>0.2222</v>
+        <v>0.2205</v>
       </c>
       <c r="AF29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG29">
-        <v>0.2019</v>
+        <v>0.207</v>
       </c>
       <c r="AH29">
-        <v>0.219</v>
+        <v>0.2197</v>
       </c>
       <c r="AI29">
-        <v>0.9933</v>
+        <v>0.9998</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
       </c>
       <c r="AK29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AL29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AM29">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
@@ -3754,16 +3979,16 @@
         <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30">
         <v>6.5</v>
       </c>
       <c r="D30">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="E30">
-        <v>-154</v>
+        <v>-125</v>
       </c>
       <c r="H30" t="s">
         <v>45</v>
@@ -3775,7 +4000,7 @@
         <v>45</v>
       </c>
       <c r="M30" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="N30" t="s">
         <v>45</v>
@@ -3807,16 +4032,13 @@
         <v>99</v>
       </c>
       <c r="C31">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D31">
-        <v>111</v>
+        <v>-131</v>
       </c>
       <c r="E31">
-        <v>-128</v>
-      </c>
-      <c r="F31">
-        <v>6.21</v>
+        <v>106</v>
       </c>
       <c r="H31" t="s">
         <v>45</v>
@@ -3824,92 +4046,32 @@
       <c r="J31" t="s">
         <v>45</v>
       </c>
-      <c r="K31">
-        <v>6.21</v>
-      </c>
       <c r="L31" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="M31" t="s">
-        <v>98</v>
-      </c>
-      <c r="N31">
-        <v>823917</v>
+        <v>70</v>
+      </c>
+      <c r="N31" t="s">
+        <v>45</v>
       </c>
       <c r="O31" t="s">
-        <v>48</v>
-      </c>
-      <c r="P31">
-        <v>6.3</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>0</v>
-      </c>
-      <c r="R31" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S31">
-        <v>6</v>
-      </c>
-      <c r="T31">
-        <v>0.1915</v>
-      </c>
-      <c r="U31">
-        <v>0.1847</v>
-      </c>
-      <c r="V31">
         <v>5</v>
       </c>
-      <c r="W31">
-        <v>121</v>
-      </c>
-      <c r="X31">
-        <v>0.1736</v>
-      </c>
-      <c r="Y31">
-        <v>0.377</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>4.06</v>
-      </c>
-      <c r="AB31">
-        <v>1.3222</v>
-      </c>
       <c r="AC31" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD31">
-        <v>0.2895</v>
-      </c>
-      <c r="AE31">
-        <v>0.2205</v>
-      </c>
-      <c r="AF31">
-        <v>9</v>
-      </c>
-      <c r="AG31">
-        <v>0.207</v>
-      </c>
-      <c r="AH31">
-        <v>0.219</v>
-      </c>
-      <c r="AI31">
-        <v>0.9998</v>
-      </c>
-      <c r="AJ31" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>45</v>
       </c>
       <c r="AK31" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AL31" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.25">
@@ -3919,8 +4081,14 @@
       <c r="B32" t="s">
         <v>100</v>
       </c>
-      <c r="F32">
-        <v>6.37</v>
+      <c r="C32">
+        <v>5.5</v>
+      </c>
+      <c r="D32">
+        <v>-146</v>
+      </c>
+      <c r="E32">
+        <v>125</v>
       </c>
       <c r="H32" t="s">
         <v>45</v>
@@ -3928,92 +4096,32 @@
       <c r="J32" t="s">
         <v>45</v>
       </c>
-      <c r="K32">
-        <v>6.37</v>
-      </c>
       <c r="L32" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="M32" t="s">
-        <v>54</v>
-      </c>
-      <c r="N32">
-        <v>823832</v>
+        <v>79</v>
+      </c>
+      <c r="N32" t="s">
+        <v>45</v>
       </c>
       <c r="O32" t="s">
-        <v>48</v>
-      </c>
-      <c r="P32">
-        <v>5.5</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>0</v>
-      </c>
-      <c r="R32" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0.2707</v>
-      </c>
-      <c r="U32">
-        <v>0.2659</v>
-      </c>
-      <c r="V32">
-        <v>5</v>
-      </c>
-      <c r="W32">
-        <v>124</v>
-      </c>
-      <c r="X32">
-        <v>0.2581</v>
-      </c>
-      <c r="Y32">
-        <v>0.383</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>4.08</v>
-      </c>
-      <c r="AB32">
-        <v>1.0153</v>
+        <v>6</v>
       </c>
       <c r="AC32" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD32">
-        <v>0.2223</v>
-      </c>
-      <c r="AE32">
-        <v>0.2583</v>
-      </c>
-      <c r="AF32">
-        <v>9</v>
-      </c>
-      <c r="AG32">
-        <v>0.2359</v>
-      </c>
-      <c r="AH32">
-        <v>0.219</v>
-      </c>
-      <c r="AI32">
-        <v>1.0563</v>
-      </c>
-      <c r="AJ32" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>45</v>
       </c>
       <c r="AK32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AL32" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
@@ -4023,101 +4131,47 @@
       <c r="B33" t="s">
         <v>101</v>
       </c>
-      <c r="F33">
+      <c r="C33">
         <v>4.5</v>
       </c>
+      <c r="D33">
+        <v>-148</v>
+      </c>
+      <c r="E33">
+        <v>120</v>
+      </c>
       <c r="H33" t="s">
         <v>45</v>
       </c>
       <c r="J33" t="s">
         <v>45</v>
       </c>
-      <c r="K33">
-        <v>4.34</v>
-      </c>
       <c r="L33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M33" t="s">
-        <v>70</v>
-      </c>
-      <c r="N33">
-        <v>824886</v>
+        <v>82</v>
+      </c>
+      <c r="N33" t="s">
+        <v>45</v>
       </c>
       <c r="O33" t="s">
-        <v>48</v>
-      </c>
-      <c r="P33">
-        <v>5.1</v>
-      </c>
-      <c r="Q33" t="b">
-        <v>0</v>
-      </c>
-      <c r="R33" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0.1916</v>
-      </c>
-      <c r="U33">
-        <v>0.1882</v>
-      </c>
-      <c r="V33">
-        <v>5</v>
-      </c>
-      <c r="W33">
-        <v>94</v>
-      </c>
-      <c r="X33">
-        <v>0.1809</v>
-      </c>
-      <c r="Y33">
-        <v>0.32</v>
-      </c>
-      <c r="Z33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>4.06</v>
-      </c>
-      <c r="AB33">
-        <v>1.1574</v>
+        <v>6</v>
       </c>
       <c r="AC33" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD33">
-        <v>0.2534</v>
-      </c>
-      <c r="AE33">
-        <v>0.2541</v>
-      </c>
-      <c r="AF33">
-        <v>8</v>
-      </c>
-      <c r="AG33">
-        <v>0.2315</v>
-      </c>
-      <c r="AH33">
-        <v>0.219</v>
-      </c>
-      <c r="AI33">
-        <v>0.9722</v>
-      </c>
-      <c r="AJ33" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>45</v>
       </c>
       <c r="AK33" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AL33" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM33">
-        <v>0.16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.25">
@@ -4127,8 +4181,14 @@
       <c r="B34" t="s">
         <v>102</v>
       </c>
-      <c r="F34">
-        <v>6.56</v>
+      <c r="C34">
+        <v>6.5</v>
+      </c>
+      <c r="D34">
+        <v>126</v>
+      </c>
+      <c r="E34">
+        <v>-154</v>
       </c>
       <c r="H34" t="s">
         <v>45</v>
@@ -4136,92 +4196,32 @@
       <c r="J34" t="s">
         <v>45</v>
       </c>
-      <c r="K34">
-        <v>6.56</v>
-      </c>
       <c r="L34" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="M34" t="s">
-        <v>79</v>
-      </c>
-      <c r="N34">
-        <v>823019</v>
+        <v>97</v>
+      </c>
+      <c r="N34" t="s">
+        <v>45</v>
       </c>
       <c r="O34" t="s">
-        <v>48</v>
-      </c>
-      <c r="P34">
-        <v>6.2</v>
-      </c>
-      <c r="Q34" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0.278</v>
-      </c>
-      <c r="U34">
-        <v>0.2806</v>
-      </c>
-      <c r="V34">
-        <v>5</v>
-      </c>
-      <c r="W34">
-        <v>130</v>
-      </c>
-      <c r="X34">
-        <v>0.2846</v>
-      </c>
-      <c r="Y34">
-        <v>0.394</v>
-      </c>
-      <c r="Z34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>4.18</v>
-      </c>
-      <c r="AB34">
-        <v>0.9164</v>
+        <v>6</v>
       </c>
       <c r="AC34" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD34">
-        <v>0.2007</v>
-      </c>
-      <c r="AE34">
-        <v>0.1844</v>
-      </c>
-      <c r="AF34">
-        <v>8</v>
-      </c>
-      <c r="AG34">
-        <v>0.1805</v>
-      </c>
-      <c r="AH34">
-        <v>0.219</v>
-      </c>
-      <c r="AI34">
-        <v>0.9783</v>
-      </c>
-      <c r="AJ34" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>45</v>
       </c>
       <c r="AK34" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AL34" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM34">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-11.xlsx
+++ b/data/k-props/2026-08-11.xlsx
@@ -1,17 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CD2360-FB80-4418-8FC9-8B0FACF1EDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="K-Props" state="visible" r:id="rId4"/>
+    <sheet name="K-Props" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'K-Props'!$A$1:$AQ$29</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="98">
   <si>
     <t>date</t>
   </si>
@@ -305,37 +325,27 @@
   </si>
   <si>
     <t>Kansas City Royals @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Eury Perez</t>
-  </si>
-  <si>
-    <t>Martin Perez</t>
-  </si>
-  <si>
-    <t>Cristopher Sanchez</t>
-  </si>
-  <si>
-    <t>Cody Bradford</t>
-  </si>
-  <si>
-    <t>Blake Snell</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -358,9 +368,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,11 +711,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ34"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AQ29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="43" width="16" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="43" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -853,8 +867,8 @@
       <c r="E2">
         <v>-108</v>
       </c>
-      <c r="F2">
-        <v>4.14</v>
+      <c r="F2" s="3">
+        <v>4.32271997077207</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -862,8 +876,8 @@
       <c r="J2" t="s">
         <v>45</v>
       </c>
-      <c r="K2">
-        <v>4.14</v>
+      <c r="K2" s="3">
+        <v>4.32271997077207</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -878,7 +892,7 @@
         <v>48</v>
       </c>
       <c r="P2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -889,11 +903,11 @@
       <c r="S2">
         <v>5</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="2">
         <v>0.1968</v>
       </c>
-      <c r="U2">
-        <v>0.1987</v>
+      <c r="U2" s="2">
+        <v>0.19868160000000001</v>
       </c>
       <c r="V2">
         <v>5</v>
@@ -901,11 +915,11 @@
       <c r="W2">
         <v>129</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="2">
         <v>0.2016</v>
       </c>
-      <c r="Y2">
-        <v>0.392</v>
+      <c r="Y2" s="2">
+        <v>0.39200000000000002</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -913,29 +927,29 @@
       <c r="AA2">
         <v>4.05</v>
       </c>
-      <c r="AB2">
-        <v>0.9307</v>
+      <c r="AB2" s="2">
+        <v>0.93081474738279468</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
       </c>
-      <c r="AD2">
-        <v>0.2045</v>
-      </c>
-      <c r="AE2">
-        <v>0.2052</v>
+      <c r="AD2" s="2">
+        <v>0.20449999999999999</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>0.20519999999999999</v>
       </c>
       <c r="AF2">
         <v>9</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="2">
         <v>0.2261</v>
       </c>
-      <c r="AH2">
-        <v>0.2197</v>
-      </c>
-      <c r="AI2">
-        <v>0.9619</v>
+      <c r="AH2" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI2" s="2">
+        <v>0.96189999999999998</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -966,8 +980,8 @@
       <c r="E3">
         <v>-150</v>
       </c>
-      <c r="F3">
-        <v>2.75</v>
+      <c r="F3" s="3">
+        <v>2.7518828149661534</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -975,8 +989,8 @@
       <c r="J3" t="s">
         <v>45</v>
       </c>
-      <c r="K3">
-        <v>2.75</v>
+      <c r="K3" s="3">
+        <v>2.7518828149661534</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -1002,11 +1016,11 @@
       <c r="S3">
         <v>5</v>
       </c>
-      <c r="T3">
-        <v>0.2699</v>
-      </c>
-      <c r="U3">
-        <v>0.2715</v>
+      <c r="T3" s="2">
+        <v>0.26989999999999997</v>
+      </c>
+      <c r="U3" s="2">
+        <v>0.27152839999999995</v>
       </c>
       <c r="V3">
         <v>3</v>
@@ -1014,11 +1028,11 @@
       <c r="W3">
         <v>43</v>
       </c>
-      <c r="X3">
-        <v>0.2791</v>
-      </c>
-      <c r="Y3">
-        <v>0.177</v>
+      <c r="X3" s="2">
+        <v>0.27910000000000001</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>0.17699999999999999</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
@@ -1026,28 +1040,28 @@
       <c r="AA3">
         <v>4.29</v>
       </c>
-      <c r="AB3">
-        <v>0.8947</v>
+      <c r="AB3" s="2">
+        <v>0.8948566226672735</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
       </c>
-      <c r="AD3">
+      <c r="AD3" s="2">
         <v>0.1966</v>
       </c>
-      <c r="AE3">
-        <v>0.1965</v>
+      <c r="AE3" s="2">
+        <v>0.19650000000000001</v>
       </c>
       <c r="AF3">
         <v>9</v>
       </c>
-      <c r="AG3">
-        <v>0.2176</v>
-      </c>
-      <c r="AH3">
-        <v>0.2197</v>
-      </c>
-      <c r="AI3">
+      <c r="AG3" s="2">
+        <v>0.21759999999999999</v>
+      </c>
+      <c r="AH3" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI3" s="2">
         <v>0.88</v>
       </c>
       <c r="AJ3" t="b">
@@ -1079,8 +1093,8 @@
       <c r="E4">
         <v>120</v>
       </c>
-      <c r="F4">
-        <v>6.74</v>
+      <c r="F4" s="3">
+        <v>6.2326396568100346</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1088,8 +1102,8 @@
       <c r="J4" t="s">
         <v>45</v>
       </c>
-      <c r="K4">
-        <v>7.13</v>
+      <c r="K4" s="3">
+        <v>7.0321335456251965</v>
       </c>
       <c r="L4" t="s">
         <v>54</v>
@@ -1104,7 +1118,7 @@
         <v>48</v>
       </c>
       <c r="P4">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -1115,11 +1129,11 @@
       <c r="S4">
         <v>6</v>
       </c>
-      <c r="T4">
-        <v>0.3045</v>
-      </c>
-      <c r="U4">
-        <v>0.3202</v>
+      <c r="T4" s="2">
+        <v>0.30449999999999999</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0.32018829999999998</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -1127,41 +1141,41 @@
       <c r="W4">
         <v>112</v>
       </c>
-      <c r="X4">
-        <v>0.3482</v>
-      </c>
-      <c r="Y4">
-        <v>0.359</v>
+      <c r="X4" s="2">
+        <v>0.34820000000000001</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0.35899999999999999</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>4.1</v>
-      </c>
-      <c r="AB4">
-        <v>1.1017</v>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>1.1015020482476103</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
       </c>
-      <c r="AD4">
-        <v>0.242</v>
-      </c>
-      <c r="AE4">
-        <v>0.2322</v>
+      <c r="AD4" s="2">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>0.23219999999999999</v>
       </c>
       <c r="AF4">
         <v>9</v>
       </c>
-      <c r="AG4">
-        <v>0.2096</v>
-      </c>
-      <c r="AH4">
-        <v>0.2197</v>
-      </c>
-      <c r="AI4">
-        <v>0.9124</v>
+      <c r="AG4" s="2">
+        <v>0.20960000000000001</v>
+      </c>
+      <c r="AH4" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI4" s="2">
+        <v>0.91239999999999999</v>
       </c>
       <c r="AJ4" t="b">
         <v>1</v>
@@ -1173,7 +1187,7 @@
         <v>50</v>
       </c>
       <c r="AM4">
-        <v>-0.39</v>
+        <v>-0.79949388881516192</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
@@ -1183,8 +1197,17 @@
       <c r="B5" t="s">
         <v>56</v>
       </c>
-      <c r="F5">
-        <v>6.35</v>
+      <c r="C5">
+        <v>6.5</v>
+      </c>
+      <c r="D5">
+        <v>102</v>
+      </c>
+      <c r="E5">
+        <v>-125</v>
+      </c>
+      <c r="F5" s="3">
+        <v>6.57379419719115</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1192,8 +1215,8 @@
       <c r="J5" t="s">
         <v>45</v>
       </c>
-      <c r="K5">
-        <v>6.35</v>
+      <c r="K5" s="3">
+        <v>6.57379419719115</v>
       </c>
       <c r="L5" t="s">
         <v>57</v>
@@ -1208,7 +1231,7 @@
         <v>48</v>
       </c>
       <c r="P5">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1219,11 +1242,11 @@
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="2">
         <v>0.2707</v>
       </c>
-      <c r="U5">
-        <v>0.2659</v>
+      <c r="U5" s="2">
+        <v>0.2658742</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1231,11 +1254,11 @@
       <c r="W5">
         <v>124</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="2">
         <v>0.2581</v>
       </c>
-      <c r="Y5">
-        <v>0.383</v>
+      <c r="Y5" s="2">
+        <v>0.38300000000000001</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
@@ -1243,28 +1266,28 @@
       <c r="AA5">
         <v>4.08</v>
       </c>
-      <c r="AB5">
-        <v>1.012</v>
+      <c r="AB5" s="2">
+        <v>1.0118343195266273</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="2">
         <v>0.2223</v>
       </c>
-      <c r="AE5">
-        <v>0.2583</v>
+      <c r="AE5" s="2">
+        <v>0.25829999999999997</v>
       </c>
       <c r="AF5">
         <v>9</v>
       </c>
-      <c r="AG5">
+      <c r="AG5" s="2">
         <v>0.2359</v>
       </c>
-      <c r="AH5">
-        <v>0.2197</v>
-      </c>
-      <c r="AI5">
+      <c r="AH5" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI5" s="2">
         <v>1.0563</v>
       </c>
       <c r="AJ5" t="b">
@@ -1296,8 +1319,8 @@
       <c r="E6">
         <v>-143</v>
       </c>
-      <c r="F6">
-        <v>4.88</v>
+      <c r="F6" s="3">
+        <v>4.7977947870519975</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1305,8 +1328,8 @@
       <c r="J6" t="s">
         <v>45</v>
       </c>
-      <c r="K6">
-        <v>4.88</v>
+      <c r="K6" s="3">
+        <v>4.7977947870519975</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
@@ -1321,7 +1344,7 @@
         <v>48</v>
       </c>
       <c r="P6">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1332,11 +1355,11 @@
       <c r="S6">
         <v>5</v>
       </c>
-      <c r="T6">
-        <v>0.2345</v>
-      </c>
-      <c r="U6">
-        <v>0.2261</v>
+      <c r="T6" s="2">
+        <v>0.23449999999999999</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0.22611539999999997</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1344,40 +1367,40 @@
       <c r="W6">
         <v>118</v>
       </c>
-      <c r="X6">
-        <v>0.2119</v>
-      </c>
-      <c r="Y6">
+      <c r="X6" s="2">
+        <v>0.21190000000000001</v>
+      </c>
+      <c r="Y6" s="2">
         <v>0.371</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>4.02</v>
-      </c>
-      <c r="AB6">
-        <v>0.9016</v>
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0.90168411470186616</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
       </c>
-      <c r="AD6">
+      <c r="AD6" s="2">
         <v>0.1981</v>
       </c>
-      <c r="AE6">
-        <v>0.2224</v>
+      <c r="AE6" s="2">
+        <v>0.22239999999999999</v>
       </c>
       <c r="AF6">
         <v>9</v>
       </c>
-      <c r="AG6">
-        <v>0.2352</v>
-      </c>
-      <c r="AH6">
-        <v>0.2197</v>
-      </c>
-      <c r="AI6">
+      <c r="AG6" s="2">
+        <v>0.23519999999999999</v>
+      </c>
+      <c r="AH6" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI6" s="2">
         <v>1.0324</v>
       </c>
       <c r="AJ6" t="b">
@@ -1409,8 +1432,8 @@
       <c r="E7">
         <v>-155</v>
       </c>
-      <c r="F7">
-        <v>4.7</v>
+      <c r="F7" s="3">
+        <v>4.9216952510201191</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1418,8 +1441,8 @@
       <c r="J7" t="s">
         <v>45</v>
       </c>
-      <c r="K7">
-        <v>4.7</v>
+      <c r="K7" s="3">
+        <v>4.9216952510201191</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
@@ -1434,7 +1457,7 @@
         <v>48</v>
       </c>
       <c r="P7">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1445,11 +1468,11 @@
       <c r="S7">
         <v>5</v>
       </c>
-      <c r="T7">
-        <v>0.2313</v>
-      </c>
-      <c r="U7">
-        <v>0.2304</v>
+      <c r="T7" s="2">
+        <v>0.23130000000000001</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0.23035500000000003</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1457,10 +1480,10 @@
       <c r="W7">
         <v>92</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="2">
         <v>0.2283</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="2">
         <v>0.315</v>
       </c>
       <c r="Z7" t="b">
@@ -1469,29 +1492,29 @@
       <c r="AA7">
         <v>4.32</v>
       </c>
-      <c r="AB7">
-        <v>1.0179</v>
+      <c r="AB7" s="2">
+        <v>1.0177514792899407</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
       </c>
-      <c r="AD7">
-        <v>0.2236</v>
-      </c>
-      <c r="AE7">
-        <v>0.2226</v>
+      <c r="AD7" s="2">
+        <v>0.22359999999999999</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>0.22259999999999999</v>
       </c>
       <c r="AF7">
         <v>9</v>
       </c>
-      <c r="AG7">
+      <c r="AG7" s="2">
         <v>0.218</v>
       </c>
-      <c r="AH7">
-        <v>0.2197</v>
-      </c>
-      <c r="AI7">
-        <v>0.9719</v>
+      <c r="AH7" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI7" s="2">
+        <v>0.97189999999999999</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
@@ -1522,8 +1545,8 @@
       <c r="E8">
         <v>-134</v>
       </c>
-      <c r="F8">
-        <v>6.84</v>
+      <c r="F8" s="3">
+        <v>6.2982708605325701</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1531,11 +1554,11 @@
       <c r="J8" t="s">
         <v>45</v>
       </c>
-      <c r="K8">
-        <v>6.84</v>
+      <c r="K8" s="3">
+        <v>7.097764749347732</v>
       </c>
       <c r="L8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M8" t="s">
         <v>62</v>
@@ -1547,7 +1570,7 @@
         <v>48</v>
       </c>
       <c r="P8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1558,11 +1581,11 @@
       <c r="S8">
         <v>6</v>
       </c>
-      <c r="T8">
-        <v>0.2428</v>
-      </c>
-      <c r="U8">
-        <v>0.2425</v>
+      <c r="T8" s="2">
+        <v>0.24279999999999999</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.24245529999999998</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1570,40 +1593,40 @@
       <c r="W8">
         <v>124</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="2">
         <v>0.2419</v>
       </c>
-      <c r="Y8">
-        <v>0.383</v>
+      <c r="Y8" s="2">
+        <v>0.38300000000000001</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>4.11</v>
-      </c>
-      <c r="AB8">
-        <v>1.1664</v>
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>1.1661356395084204</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
       </c>
-      <c r="AD8">
-        <v>0.2562</v>
-      </c>
-      <c r="AE8">
+      <c r="AD8" s="2">
+        <v>0.25619999999999998</v>
+      </c>
+      <c r="AE8" s="2">
         <v>0.2601</v>
       </c>
       <c r="AF8">
         <v>9</v>
       </c>
-      <c r="AG8">
-        <v>0.2439</v>
-      </c>
-      <c r="AH8">
-        <v>0.2197</v>
-      </c>
-      <c r="AI8">
+      <c r="AG8" s="2">
+        <v>0.24390000000000001</v>
+      </c>
+      <c r="AH8" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI8" s="2">
         <v>1.018</v>
       </c>
       <c r="AJ8" t="b">
@@ -1616,7 +1639,7 @@
         <v>50</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>-0.79949388881516192</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
@@ -1635,8 +1658,8 @@
       <c r="E9">
         <v>-145</v>
       </c>
-      <c r="F9">
-        <v>5.83</v>
+      <c r="F9" s="3">
+        <v>6.016514650860266</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1644,11 +1667,11 @@
       <c r="J9" t="s">
         <v>45</v>
       </c>
-      <c r="K9">
-        <v>5.83</v>
+      <c r="K9" s="3">
+        <v>6.016514650860266</v>
       </c>
       <c r="L9" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="M9" t="s">
         <v>62</v>
@@ -1660,7 +1683,7 @@
         <v>48</v>
       </c>
       <c r="P9">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -1671,11 +1694,11 @@
       <c r="S9">
         <v>5</v>
       </c>
-      <c r="T9">
-        <v>0.2624</v>
-      </c>
-      <c r="U9">
-        <v>0.2539</v>
+      <c r="T9" s="2">
+        <v>0.26240000000000002</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0.25387609999999999</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1683,11 +1706,11 @@
       <c r="W9">
         <v>117</v>
       </c>
-      <c r="X9">
-        <v>0.2393</v>
-      </c>
-      <c r="Y9">
-        <v>0.369</v>
+      <c r="X9" s="2">
+        <v>0.23930000000000001</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0.36899999999999999</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
@@ -1695,29 +1718,29 @@
       <c r="AA9">
         <v>4.16</v>
       </c>
-      <c r="AB9">
-        <v>1.0387</v>
+      <c r="AB9" s="2">
+        <v>1.0386891215293581</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
       </c>
-      <c r="AD9">
-        <v>0.2282</v>
-      </c>
-      <c r="AE9">
+      <c r="AD9" s="2">
+        <v>0.22819999999999999</v>
+      </c>
+      <c r="AE9" s="2">
         <v>0.2152</v>
       </c>
       <c r="AF9">
         <v>9</v>
       </c>
-      <c r="AG9">
-        <v>0.2371</v>
-      </c>
-      <c r="AH9">
-        <v>0.2197</v>
-      </c>
-      <c r="AI9">
-        <v>0.9673</v>
+      <c r="AG9" s="2">
+        <v>0.23710000000000001</v>
+      </c>
+      <c r="AH9" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI9" s="2">
+        <v>0.96730000000000005</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
@@ -1748,8 +1771,8 @@
       <c r="E10">
         <v>-134</v>
       </c>
-      <c r="F10">
-        <v>2.82</v>
+      <c r="F10" s="3">
+        <v>2.940972737369139</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1757,8 +1780,8 @@
       <c r="J10" t="s">
         <v>45</v>
       </c>
-      <c r="K10">
-        <v>2.82</v>
+      <c r="K10" s="3">
+        <v>2.940972737369139</v>
       </c>
       <c r="L10" t="s">
         <v>46</v>
@@ -1773,7 +1796,7 @@
         <v>48</v>
       </c>
       <c r="P10">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1784,11 +1807,11 @@
       <c r="S10">
         <v>6</v>
       </c>
-      <c r="T10">
-        <v>0.2294</v>
-      </c>
-      <c r="U10">
-        <v>0.2294</v>
+      <c r="T10" s="2">
+        <v>0.22939999999999999</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0.22939999999999999</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1796,11 +1819,11 @@
       <c r="W10">
         <v>109</v>
       </c>
-      <c r="X10">
-        <v>0.2294</v>
-      </c>
-      <c r="Y10">
-        <v>0.353</v>
+      <c r="X10" s="2">
+        <v>0.22939999999999999</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0.35299999999999998</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
@@ -1808,28 +1831,28 @@
       <c r="AA10">
         <v>4.54</v>
       </c>
-      <c r="AB10">
-        <v>0.6417</v>
+      <c r="AB10" s="2">
+        <v>0.64178425125170679</v>
       </c>
       <c r="AC10" t="s">
         <v>49</v>
       </c>
-      <c r="AD10">
-        <v>0.141</v>
-      </c>
-      <c r="AE10">
+      <c r="AD10" s="2">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="AE10" s="2">
         <v>0.1474</v>
       </c>
       <c r="AF10">
         <v>9</v>
       </c>
-      <c r="AG10">
-        <v>0.2164</v>
-      </c>
-      <c r="AH10">
-        <v>0.2197</v>
-      </c>
-      <c r="AI10">
+      <c r="AG10" s="2">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI10" s="2">
         <v>0.88</v>
       </c>
       <c r="AJ10" t="b">
@@ -1861,8 +1884,8 @@
       <c r="E11">
         <v>124</v>
       </c>
-      <c r="F11">
-        <v>6.99</v>
+      <c r="F11" s="3">
+        <v>6.5667615684368714</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1870,8 +1893,8 @@
       <c r="J11" t="s">
         <v>45</v>
       </c>
-      <c r="K11">
-        <v>7.38</v>
+      <c r="K11" s="3">
+        <v>7.3662554572520333</v>
       </c>
       <c r="L11" t="s">
         <v>54</v>
@@ -1897,11 +1920,11 @@
       <c r="S11">
         <v>6</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="2">
         <v>0.3644</v>
       </c>
-      <c r="U11">
-        <v>0.3611</v>
+      <c r="U11" s="2">
+        <v>0.36109659999999999</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1909,11 +1932,11 @@
       <c r="W11">
         <v>132</v>
       </c>
-      <c r="X11">
-        <v>0.3561</v>
-      </c>
-      <c r="Y11">
-        <v>0.398</v>
+      <c r="X11" s="2">
+        <v>0.35610000000000003</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0.39800000000000002</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
@@ -1921,29 +1944,29 @@
       <c r="AA11">
         <v>4</v>
       </c>
-      <c r="AB11">
-        <v>0.8574</v>
+      <c r="AB11" s="2">
+        <v>0.85753299954483386</v>
       </c>
       <c r="AC11" t="s">
         <v>67</v>
       </c>
-      <c r="AD11">
-        <v>0.1884</v>
-      </c>
-      <c r="AE11">
-        <v>0.1881</v>
+      <c r="AD11" s="2">
+        <v>0.18840000000000001</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>0.18809999999999999</v>
       </c>
       <c r="AF11">
         <v>8</v>
       </c>
-      <c r="AG11">
+      <c r="AG11" s="2">
         <v>0.2185</v>
       </c>
-      <c r="AH11">
-        <v>0.2197</v>
-      </c>
-      <c r="AI11">
-        <v>0.9912</v>
+      <c r="AH11" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI11" s="2">
+        <v>0.99119999999999997</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
@@ -1955,7 +1978,7 @@
         <v>68</v>
       </c>
       <c r="AM11">
-        <v>-0.39</v>
+        <v>-0.79949388881516192</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
@@ -1974,8 +1997,8 @@
       <c r="E12">
         <v>122</v>
       </c>
-      <c r="F12">
-        <v>6.61</v>
+      <c r="F12" s="3">
+        <v>6.9827469327026659</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1983,11 +2006,11 @@
       <c r="J12" t="s">
         <v>45</v>
       </c>
-      <c r="K12">
-        <v>7</v>
+      <c r="K12" s="3">
+        <v>6.9827469327026659</v>
       </c>
       <c r="L12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M12" t="s">
         <v>70</v>
@@ -1999,7 +2022,7 @@
         <v>48</v>
       </c>
       <c r="P12">
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -2010,11 +2033,11 @@
       <c r="S12">
         <v>6</v>
       </c>
-      <c r="T12">
-        <v>0.2847</v>
-      </c>
-      <c r="U12">
-        <v>0.2912</v>
+      <c r="T12" s="2">
+        <v>0.28470000000000001</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0.29124030000000001</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -2022,41 +2045,41 @@
       <c r="W12">
         <v>126</v>
       </c>
-      <c r="X12">
-        <v>0.3016</v>
-      </c>
-      <c r="Y12">
-        <v>0.387</v>
+      <c r="X12" s="2">
+        <v>0.30159999999999998</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0.38700000000000001</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>4.19</v>
-      </c>
-      <c r="AB12">
-        <v>1.0081</v>
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>1.0081929904415112</v>
       </c>
       <c r="AC12" t="s">
         <v>49</v>
       </c>
-      <c r="AD12">
+      <c r="AD12" s="2">
         <v>0.2215</v>
       </c>
-      <c r="AE12">
+      <c r="AE12" s="2">
         <v>0.2152</v>
       </c>
       <c r="AF12">
         <v>9</v>
       </c>
-      <c r="AG12">
-        <v>0.2179</v>
-      </c>
-      <c r="AH12">
-        <v>0.2197</v>
-      </c>
-      <c r="AI12">
-        <v>1.001</v>
+      <c r="AG12" s="2">
+        <v>0.21790000000000001</v>
+      </c>
+      <c r="AH12" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI12" s="2">
+        <v>1.0009999999999999</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
@@ -2068,7 +2091,7 @@
         <v>50</v>
       </c>
       <c r="AM12">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
@@ -2078,8 +2101,17 @@
       <c r="B13" t="s">
         <v>71</v>
       </c>
-      <c r="F13">
-        <v>5.04</v>
+      <c r="C13">
+        <v>3.5</v>
+      </c>
+      <c r="D13">
+        <v>-131</v>
+      </c>
+      <c r="E13">
+        <v>106</v>
+      </c>
+      <c r="F13" s="3">
+        <v>5.3140287173599789</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2087,8 +2119,8 @@
       <c r="J13" t="s">
         <v>45</v>
       </c>
-      <c r="K13">
-        <v>5.04</v>
+      <c r="K13" s="3">
+        <v>5.3140287173599789</v>
       </c>
       <c r="L13" t="s">
         <v>46</v>
@@ -2103,7 +2135,7 @@
         <v>48</v>
       </c>
       <c r="P13">
-        <v>5.1</v>
+        <v>5.33</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -2114,11 +2146,11 @@
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0.1916</v>
-      </c>
-      <c r="U13">
-        <v>0.1882</v>
+      <c r="T13" s="2">
+        <v>0.19159999999999999</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0.18817599999999998</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -2126,41 +2158,41 @@
       <c r="W13">
         <v>94</v>
       </c>
-      <c r="X13">
-        <v>0.1809</v>
-      </c>
-      <c r="Y13">
+      <c r="X13" s="2">
+        <v>0.18090000000000001</v>
+      </c>
+      <c r="Y13" s="2">
         <v>0.32</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>4.06</v>
-      </c>
-      <c r="AB13">
-        <v>1.3565</v>
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>1.3563950842057351</v>
       </c>
       <c r="AC13" t="s">
         <v>49</v>
       </c>
-      <c r="AD13">
-        <v>0.298</v>
-      </c>
-      <c r="AE13">
-        <v>0.2803</v>
+      <c r="AD13" s="2">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="AE13" s="2">
+        <v>0.28029999999999999</v>
       </c>
       <c r="AF13">
         <v>9</v>
       </c>
-      <c r="AG13">
-        <v>0.2315</v>
-      </c>
-      <c r="AH13">
-        <v>0.2197</v>
-      </c>
-      <c r="AI13">
-        <v>0.9621</v>
+      <c r="AG13" s="2">
+        <v>0.23150000000000001</v>
+      </c>
+      <c r="AH13" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI13" s="2">
+        <v>0.96209999999999996</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
@@ -2191,8 +2223,8 @@
       <c r="E14">
         <v>-152</v>
       </c>
-      <c r="F14">
-        <v>4.43</v>
+      <c r="F14" s="3">
+        <v>4.4259036792464013</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2200,8 +2232,8 @@
       <c r="J14" t="s">
         <v>45</v>
       </c>
-      <c r="K14">
-        <v>4.43</v>
+      <c r="K14" s="3">
+        <v>4.4259036792464013</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
@@ -2216,7 +2248,7 @@
         <v>48</v>
       </c>
       <c r="P14">
-        <v>5.7</v>
+        <v>5.67</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
@@ -2227,11 +2259,11 @@
       <c r="S14">
         <v>6</v>
       </c>
-      <c r="T14">
-        <v>0.1939</v>
-      </c>
-      <c r="U14">
-        <v>0.2037</v>
+      <c r="T14" s="2">
+        <v>0.19389999999999999</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0.20365359999999999</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -2239,11 +2271,11 @@
       <c r="W14">
         <v>123</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="2">
         <v>0.2195</v>
       </c>
-      <c r="Y14">
-        <v>0.381</v>
+      <c r="Y14" s="2">
+        <v>0.38100000000000001</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
@@ -2251,29 +2283,29 @@
       <c r="AA14">
         <v>4.26</v>
       </c>
-      <c r="AB14">
-        <v>0.9324</v>
+      <c r="AB14" s="2">
+        <v>0.93218024578971326</v>
       </c>
       <c r="AC14" t="s">
         <v>49</v>
       </c>
-      <c r="AD14">
-        <v>0.2048</v>
-      </c>
-      <c r="AE14">
+      <c r="AD14" s="2">
+        <v>0.20480000000000001</v>
+      </c>
+      <c r="AE14" s="2">
         <v>0.1903</v>
       </c>
       <c r="AF14">
         <v>9</v>
       </c>
-      <c r="AG14">
-        <v>0.2106</v>
-      </c>
-      <c r="AH14">
-        <v>0.2197</v>
-      </c>
-      <c r="AI14">
-        <v>0.9652</v>
+      <c r="AG14" s="2">
+        <v>0.21060000000000001</v>
+      </c>
+      <c r="AH14" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI14" s="2">
+        <v>0.96519999999999995</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
@@ -2304,8 +2336,8 @@
       <c r="E15">
         <v>-123</v>
       </c>
-      <c r="F15">
-        <v>4.42</v>
+      <c r="F15" s="3">
+        <v>4.5817181071463251</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2313,8 +2345,8 @@
       <c r="J15" t="s">
         <v>45</v>
       </c>
-      <c r="K15">
-        <v>4.42</v>
+      <c r="K15" s="3">
+        <v>4.5817181071463251</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
@@ -2329,7 +2361,7 @@
         <v>48</v>
       </c>
       <c r="P15">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -2340,11 +2372,11 @@
       <c r="S15">
         <v>6</v>
       </c>
-      <c r="T15">
-        <v>0.162</v>
-      </c>
-      <c r="U15">
-        <v>0.1604</v>
+      <c r="T15" s="2">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0.16038540000000001</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -2352,11 +2384,11 @@
       <c r="W15">
         <v>108</v>
       </c>
-      <c r="X15">
-        <v>0.1574</v>
-      </c>
-      <c r="Y15">
-        <v>0.351</v>
+      <c r="X15" s="2">
+        <v>0.15740000000000001</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0.35099999999999998</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
@@ -2364,29 +2396,29 @@
       <c r="AA15">
         <v>4.18</v>
       </c>
-      <c r="AB15">
-        <v>1.1753</v>
+      <c r="AB15" s="2">
+        <v>1.1752389622212107</v>
       </c>
       <c r="AC15" t="s">
         <v>49</v>
       </c>
-      <c r="AD15">
-        <v>0.2582</v>
-      </c>
-      <c r="AE15">
-        <v>0.2534</v>
+      <c r="AD15" s="2">
+        <v>0.25819999999999999</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>0.25340000000000001</v>
       </c>
       <c r="AF15">
         <v>9</v>
       </c>
-      <c r="AG15">
-        <v>0.2383</v>
-      </c>
-      <c r="AH15">
-        <v>0.2197</v>
-      </c>
-      <c r="AI15">
-        <v>1.0256</v>
+      <c r="AG15" s="2">
+        <v>0.23830000000000001</v>
+      </c>
+      <c r="AH15" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI15" s="2">
+        <v>1.0256000000000001</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
@@ -2417,8 +2449,8 @@
       <c r="E16">
         <v>-105</v>
       </c>
-      <c r="F16">
-        <v>4.65</v>
+      <c r="F16" s="3">
+        <v>4.7452582968046775</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2426,8 +2458,8 @@
       <c r="J16" t="s">
         <v>45</v>
       </c>
-      <c r="K16">
-        <v>4.65</v>
+      <c r="K16" s="3">
+        <v>4.7452582968046775</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
@@ -2442,7 +2474,7 @@
         <v>48</v>
       </c>
       <c r="P16">
-        <v>5.2</v>
+        <v>5.33</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -2453,11 +2485,11 @@
       <c r="S16">
         <v>6</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="2">
         <v>0.1792</v>
       </c>
-      <c r="U16">
-        <v>0.1813</v>
+      <c r="U16" s="2">
+        <v>0.18130599999999999</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -2465,11 +2497,11 @@
       <c r="W16">
         <v>108</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="2">
         <v>0.1852</v>
       </c>
-      <c r="Y16">
-        <v>0.351</v>
+      <c r="Y16" s="2">
+        <v>0.35099999999999998</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
@@ -2477,28 +2509,28 @@
       <c r="AA16">
         <v>4.45</v>
       </c>
-      <c r="AB16">
-        <v>1.0505</v>
+      <c r="AB16" s="2">
+        <v>1.0505234410559854</v>
       </c>
       <c r="AC16" t="s">
         <v>49</v>
       </c>
-      <c r="AD16">
-        <v>0.2308</v>
-      </c>
-      <c r="AE16">
+      <c r="AD16" s="2">
+        <v>0.23080000000000001</v>
+      </c>
+      <c r="AE16" s="2">
         <v>0.2581</v>
       </c>
       <c r="AF16">
         <v>9</v>
       </c>
-      <c r="AG16">
-        <v>0.2463</v>
-      </c>
-      <c r="AH16">
-        <v>0.2197</v>
-      </c>
-      <c r="AI16">
+      <c r="AG16" s="2">
+        <v>0.24629999999999999</v>
+      </c>
+      <c r="AH16" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI16" s="2">
         <v>1.0504</v>
       </c>
       <c r="AJ16" t="b">
@@ -2514,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -2530,8 +2562,8 @@
       <c r="E17">
         <v>-137</v>
       </c>
-      <c r="F17">
-        <v>8.44</v>
+      <c r="F17" s="3">
+        <v>8.3738685535713202</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2539,8 +2571,8 @@
       <c r="J17" t="s">
         <v>45</v>
       </c>
-      <c r="K17">
-        <v>8.83</v>
+      <c r="K17" s="3">
+        <v>9.1733624423864821</v>
       </c>
       <c r="L17" t="s">
         <v>54</v>
@@ -2555,7 +2587,7 @@
         <v>48</v>
       </c>
       <c r="P17">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
@@ -2566,11 +2598,11 @@
       <c r="S17">
         <v>6</v>
       </c>
-      <c r="T17">
-        <v>0.2743</v>
-      </c>
-      <c r="U17">
-        <v>0.2957</v>
+      <c r="T17" s="2">
+        <v>0.27429999999999999</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0.29571700000000001</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2578,11 +2610,11 @@
       <c r="W17">
         <v>114</v>
       </c>
-      <c r="X17">
-        <v>0.3333</v>
-      </c>
-      <c r="Y17">
-        <v>0.363</v>
+      <c r="X17" s="2">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>0.36299999999999999</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
@@ -2590,28 +2622,28 @@
       <c r="AA17">
         <v>4.08</v>
       </c>
-      <c r="AB17">
-        <v>1.2366</v>
+      <c r="AB17" s="2">
+        <v>1.2366863905325443</v>
       </c>
       <c r="AC17" t="s">
         <v>49</v>
       </c>
-      <c r="AD17">
+      <c r="AD17" s="2">
         <v>0.2717</v>
       </c>
-      <c r="AE17">
-        <v>0.2781</v>
+      <c r="AE17" s="2">
+        <v>0.27810000000000001</v>
       </c>
       <c r="AF17">
         <v>9</v>
       </c>
-      <c r="AG17">
-        <v>0.2549</v>
-      </c>
-      <c r="AH17">
-        <v>0.2197</v>
-      </c>
-      <c r="AI17">
+      <c r="AG17" s="2">
+        <v>0.25490000000000002</v>
+      </c>
+      <c r="AH17" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI17" s="2">
         <v>1.0843</v>
       </c>
       <c r="AJ17" t="b">
@@ -2624,18 +2656,27 @@
         <v>50</v>
       </c>
       <c r="AM17">
-        <v>-0.39</v>
+        <v>-0.79949388881516192</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
       <c r="B18" t="s">
         <v>78</v>
       </c>
-      <c r="F18">
-        <v>6.73</v>
+      <c r="C18">
+        <v>5.5</v>
+      </c>
+      <c r="D18">
+        <v>-146</v>
+      </c>
+      <c r="E18">
+        <v>125</v>
+      </c>
+      <c r="F18" s="3">
+        <v>6.4187761525971183</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2643,8 +2684,8 @@
       <c r="J18" t="s">
         <v>45</v>
       </c>
-      <c r="K18">
-        <v>7.12</v>
+      <c r="K18" s="3">
+        <v>7.2182700414122802</v>
       </c>
       <c r="L18" t="s">
         <v>54</v>
@@ -2659,7 +2700,7 @@
         <v>48</v>
       </c>
       <c r="P18">
-        <v>6.2</v>
+        <v>6.33</v>
       </c>
       <c r="Q18" t="b">
         <v>0</v>
@@ -2670,11 +2711,11 @@
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0.278</v>
-      </c>
-      <c r="U18">
-        <v>0.2806</v>
+      <c r="T18" s="2">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0.28060040000000003</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2682,11 +2723,11 @@
       <c r="W18">
         <v>130</v>
       </c>
-      <c r="X18">
-        <v>0.2846</v>
-      </c>
-      <c r="Y18">
-        <v>0.394</v>
+      <c r="X18" s="2">
+        <v>0.28460000000000002</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0.39400000000000002</v>
       </c>
       <c r="Z18" t="b">
         <v>0</v>
@@ -2694,29 +2735,29 @@
       <c r="AA18">
         <v>4.18</v>
       </c>
-      <c r="AB18">
-        <v>1.0452</v>
+      <c r="AB18" s="2">
+        <v>1.0450614474283113</v>
       </c>
       <c r="AC18" t="s">
         <v>49</v>
       </c>
-      <c r="AD18">
+      <c r="AD18" s="2">
         <v>0.2296</v>
       </c>
-      <c r="AE18">
+      <c r="AE18" s="2">
         <v>0.1905</v>
       </c>
       <c r="AF18">
         <v>9</v>
       </c>
-      <c r="AG18">
-        <v>0.1805</v>
-      </c>
-      <c r="AH18">
-        <v>0.2197</v>
-      </c>
-      <c r="AI18">
-        <v>0.9303</v>
+      <c r="AG18" s="2">
+        <v>0.18049999999999999</v>
+      </c>
+      <c r="AH18" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI18" s="2">
+        <v>0.93030000000000002</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
@@ -2728,10 +2769,10 @@
         <v>50</v>
       </c>
       <c r="AM18">
-        <v>-0.39</v>
+        <v>-0.79949388881516192</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -2747,8 +2788,8 @@
       <c r="E19">
         <v>-115</v>
       </c>
-      <c r="F19">
-        <v>3.18</v>
+      <c r="F19" s="3">
+        <v>3.1955738963089537</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2756,8 +2797,8 @@
       <c r="J19" t="s">
         <v>45</v>
       </c>
-      <c r="K19">
-        <v>3.18</v>
+      <c r="K19" s="3">
+        <v>3.1955738963089537</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
@@ -2772,7 +2813,7 @@
         <v>48</v>
       </c>
       <c r="P19">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -2783,11 +2824,11 @@
       <c r="S19">
         <v>6</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="2">
         <v>0.1741</v>
       </c>
-      <c r="U19">
-        <v>0.1718</v>
+      <c r="U19" s="2">
+        <v>0.17186200000000001</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2795,10 +2836,10 @@
       <c r="W19">
         <v>119</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="2">
         <v>0.1681</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="2">
         <v>0.373</v>
       </c>
       <c r="Z19" t="b">
@@ -2807,28 +2848,28 @@
       <c r="AA19">
         <v>4.17</v>
       </c>
-      <c r="AB19">
-        <v>0.8481</v>
+      <c r="AB19" s="2">
+        <v>0.84797451069640417</v>
       </c>
       <c r="AC19" t="s">
         <v>49</v>
       </c>
-      <c r="AD19">
-        <v>0.1863</v>
-      </c>
-      <c r="AE19">
-        <v>0.1899</v>
+      <c r="AD19" s="2">
+        <v>0.18629999999999999</v>
+      </c>
+      <c r="AE19" s="2">
+        <v>0.18990000000000001</v>
       </c>
       <c r="AF19">
         <v>9</v>
       </c>
-      <c r="AG19">
-        <v>0.2267</v>
-      </c>
-      <c r="AH19">
-        <v>0.2197</v>
-      </c>
-      <c r="AI19">
+      <c r="AG19" s="2">
+        <v>0.22670000000000001</v>
+      </c>
+      <c r="AH19" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI19" s="2">
         <v>0.9274</v>
       </c>
       <c r="AJ19" t="b">
@@ -2844,7 +2885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -2860,8 +2901,8 @@
       <c r="E20">
         <v>-145</v>
       </c>
-      <c r="F20">
-        <v>3.41</v>
+      <c r="F20" s="3">
+        <v>3.4906961396014924</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2869,8 +2910,8 @@
       <c r="J20" t="s">
         <v>45</v>
       </c>
-      <c r="K20">
-        <v>3.41</v>
+      <c r="K20" s="3">
+        <v>3.4906961396014924</v>
       </c>
       <c r="L20" t="s">
         <v>46</v>
@@ -2885,7 +2926,7 @@
         <v>48</v>
       </c>
       <c r="P20">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
@@ -2896,11 +2937,11 @@
       <c r="S20">
         <v>6</v>
       </c>
-      <c r="T20">
-        <v>0.1645</v>
-      </c>
-      <c r="U20">
-        <v>0.1563</v>
+      <c r="T20" s="2">
+        <v>0.16450000000000001</v>
+      </c>
+      <c r="U20" s="2">
+        <v>0.15634150000000002</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2908,41 +2949,41 @@
       <c r="W20">
         <v>100</v>
       </c>
-      <c r="X20">
-        <v>0.14</v>
-      </c>
-      <c r="Y20">
-        <v>0.333</v>
+      <c r="X20" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0.33300000000000002</v>
       </c>
       <c r="Z20" t="b">
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>4.56</v>
-      </c>
-      <c r="AB20">
-        <v>1.033</v>
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>1.0327719617660445</v>
       </c>
       <c r="AC20" t="s">
         <v>67</v>
       </c>
-      <c r="AD20">
-        <v>0.2269</v>
-      </c>
-      <c r="AE20">
-        <v>0.2406</v>
+      <c r="AD20" s="2">
+        <v>0.22689999999999999</v>
+      </c>
+      <c r="AE20" s="2">
+        <v>0.24060000000000001</v>
       </c>
       <c r="AF20">
         <v>9</v>
       </c>
-      <c r="AG20">
-        <v>0.2197</v>
-      </c>
-      <c r="AH20">
-        <v>0.2197</v>
-      </c>
-      <c r="AI20">
-        <v>1.0152</v>
+      <c r="AG20" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AH20" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI20" s="2">
+        <v>1.0152000000000001</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
@@ -2957,7 +2998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -2973,8 +3014,8 @@
       <c r="E21">
         <v>107</v>
       </c>
-      <c r="F21">
-        <v>2.47</v>
+      <c r="F21" s="3">
+        <v>2.4464501732311597</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -2982,8 +3023,8 @@
       <c r="J21" t="s">
         <v>45</v>
       </c>
-      <c r="K21">
-        <v>2.47</v>
+      <c r="K21" s="3">
+        <v>2.4464501732311597</v>
       </c>
       <c r="L21" t="s">
         <v>46</v>
@@ -2998,7 +3039,7 @@
         <v>48</v>
       </c>
       <c r="P21">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -3009,11 +3050,11 @@
       <c r="S21">
         <v>6</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="2">
         <v>0.1353</v>
       </c>
-      <c r="U21">
-        <v>0.1331</v>
+      <c r="U21" s="2">
+        <v>0.13309799999999999</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -3021,41 +3062,41 @@
       <c r="W21">
         <v>116</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="2">
         <v>0.1293</v>
       </c>
-      <c r="Y21">
-        <v>0.367</v>
+      <c r="Y21" s="2">
+        <v>0.36699999999999999</v>
       </c>
       <c r="Z21" t="b">
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>4.19</v>
-      </c>
-      <c r="AB21">
-        <v>0.8647</v>
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="AB21" s="2">
+        <v>0.86481565771506597</v>
       </c>
       <c r="AC21" t="s">
         <v>49</v>
       </c>
-      <c r="AD21">
+      <c r="AD21" s="2">
         <v>0.19</v>
       </c>
-      <c r="AE21">
-        <v>0.1889</v>
+      <c r="AE21" s="2">
+        <v>0.18890000000000001</v>
       </c>
       <c r="AF21">
         <v>9</v>
       </c>
-      <c r="AG21">
-        <v>0.2003</v>
-      </c>
-      <c r="AH21">
-        <v>0.2197</v>
-      </c>
-      <c r="AI21">
-        <v>0.9517</v>
+      <c r="AG21" s="2">
+        <v>0.20030000000000001</v>
+      </c>
+      <c r="AH21" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI21" s="2">
+        <v>0.95169999999999999</v>
       </c>
       <c r="AJ21" t="b">
         <v>1</v>
@@ -3070,7 +3111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -3086,8 +3127,8 @@
       <c r="E22">
         <v>-125</v>
       </c>
-      <c r="F22">
-        <v>3.66</v>
+      <c r="F22" s="3">
+        <v>3.7035327227961359</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
@@ -3095,8 +3136,8 @@
       <c r="J22" t="s">
         <v>45</v>
       </c>
-      <c r="K22">
-        <v>3.66</v>
+      <c r="K22" s="3">
+        <v>3.7035327227961359</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
@@ -3111,7 +3152,7 @@
         <v>48</v>
       </c>
       <c r="P22">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -3122,11 +3163,11 @@
       <c r="S22">
         <v>6</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="2">
         <v>0.1721</v>
       </c>
-      <c r="U22">
-        <v>0.1697</v>
+      <c r="U22" s="2">
+        <v>0.169629</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -3134,11 +3175,11 @@
       <c r="W22">
         <v>109</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="2">
         <v>0.1651</v>
       </c>
-      <c r="Y22">
-        <v>0.353</v>
+      <c r="Y22" s="2">
+        <v>0.35299999999999998</v>
       </c>
       <c r="Z22" t="b">
         <v>0</v>
@@ -3146,29 +3187,29 @@
       <c r="AA22">
         <v>4.41</v>
       </c>
-      <c r="AB22">
-        <v>1.0488</v>
+      <c r="AB22" s="2">
+        <v>1.0487027765134274</v>
       </c>
       <c r="AC22" t="s">
         <v>67</v>
       </c>
-      <c r="AD22">
-        <v>0.2304</v>
-      </c>
-      <c r="AE22">
+      <c r="AD22" s="2">
+        <v>0.23039999999999999</v>
+      </c>
+      <c r="AE22" s="2">
         <v>0.2281</v>
       </c>
       <c r="AF22">
         <v>9</v>
       </c>
-      <c r="AG22">
-        <v>0.2504</v>
-      </c>
-      <c r="AH22">
-        <v>0.2197</v>
-      </c>
-      <c r="AI22">
-        <v>1.0109</v>
+      <c r="AG22" s="2">
+        <v>0.25040000000000001</v>
+      </c>
+      <c r="AH22" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI22" s="2">
+        <v>1.0108999999999999</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
@@ -3183,7 +3224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -3199,8 +3240,8 @@
       <c r="E23">
         <v>-143</v>
       </c>
-      <c r="F23">
-        <v>2.67</v>
+      <c r="F23" s="3">
+        <v>2.7357553743400658</v>
       </c>
       <c r="H23" t="s">
         <v>45</v>
@@ -3208,8 +3249,8 @@
       <c r="J23" t="s">
         <v>45</v>
       </c>
-      <c r="K23">
-        <v>2.67</v>
+      <c r="K23" s="3">
+        <v>2.7357553743400658</v>
       </c>
       <c r="L23" t="s">
         <v>46</v>
@@ -3224,7 +3265,7 @@
         <v>48</v>
       </c>
       <c r="P23">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -3235,11 +3276,11 @@
       <c r="S23">
         <v>6</v>
       </c>
-      <c r="T23">
-        <v>0.1407</v>
-      </c>
-      <c r="U23">
-        <v>0.129</v>
+      <c r="T23" s="2">
+        <v>0.14069999999999999</v>
+      </c>
+      <c r="U23" s="2">
+        <v>0.1290618</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -3247,41 +3288,41 @@
       <c r="W23">
         <v>111</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="2">
         <v>0.1081</v>
       </c>
-      <c r="Y23">
-        <v>0.357</v>
+      <c r="Y23" s="2">
+        <v>0.35699999999999998</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>4.02</v>
-      </c>
-      <c r="AB23">
-        <v>0.8979</v>
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="AB23" s="2">
+        <v>0.89804278561675011</v>
       </c>
       <c r="AC23" t="s">
         <v>49</v>
       </c>
-      <c r="AD23">
+      <c r="AD23" s="2">
         <v>0.1973</v>
       </c>
-      <c r="AE23">
-        <v>0.1912</v>
+      <c r="AE23" s="2">
+        <v>0.19120000000000001</v>
       </c>
       <c r="AF23">
         <v>9</v>
       </c>
-      <c r="AG23">
-        <v>0.2179</v>
-      </c>
-      <c r="AH23">
-        <v>0.2197</v>
-      </c>
-      <c r="AI23">
-        <v>0.9786</v>
+      <c r="AG23" s="2">
+        <v>0.21790000000000001</v>
+      </c>
+      <c r="AH23" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI23" s="2">
+        <v>0.97860000000000003</v>
       </c>
       <c r="AJ23" t="b">
         <v>1</v>
@@ -3296,7 +3337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -3312,8 +3353,8 @@
       <c r="E24">
         <v>-125</v>
       </c>
-      <c r="F24">
-        <v>3.78</v>
+      <c r="F24" s="3">
+        <v>3.7756750149571054</v>
       </c>
       <c r="H24" t="s">
         <v>45</v>
@@ -3321,8 +3362,8 @@
       <c r="J24" t="s">
         <v>45</v>
       </c>
-      <c r="K24">
-        <v>3.78</v>
+      <c r="K24" s="3">
+        <v>3.7756750149571054</v>
       </c>
       <c r="L24" t="s">
         <v>46</v>
@@ -3337,7 +3378,7 @@
         <v>48</v>
       </c>
       <c r="P24">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -3348,11 +3389,11 @@
       <c r="S24">
         <v>6</v>
       </c>
-      <c r="T24">
-        <v>0.2449</v>
-      </c>
-      <c r="U24">
-        <v>0.2561</v>
+      <c r="T24" s="2">
+        <v>0.24490000000000001</v>
+      </c>
+      <c r="U24" s="2">
+        <v>0.25614040000000005</v>
       </c>
       <c r="V24">
         <v>2</v>
@@ -3360,11 +3401,11 @@
       <c r="W24">
         <v>42</v>
       </c>
-      <c r="X24">
+      <c r="X24" s="2">
         <v>0.3095</v>
       </c>
-      <c r="Y24">
-        <v>0.174</v>
+      <c r="Y24" s="2">
+        <v>0.17399999999999999</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
@@ -3372,29 +3413,29 @@
       <c r="AA24">
         <v>4.32</v>
       </c>
-      <c r="AB24">
-        <v>0.8136</v>
+      <c r="AB24" s="2">
+        <v>0.81338188438780157</v>
       </c>
       <c r="AC24" t="s">
         <v>67</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" s="2">
         <v>0.1787</v>
       </c>
-      <c r="AE24">
-        <v>0.1753</v>
+      <c r="AE24" s="2">
+        <v>0.17530000000000001</v>
       </c>
       <c r="AF24">
         <v>9</v>
       </c>
-      <c r="AG24">
-        <v>0.1929</v>
-      </c>
-      <c r="AH24">
-        <v>0.2197</v>
-      </c>
-      <c r="AI24">
-        <v>0.8983</v>
+      <c r="AG24" s="2">
+        <v>0.19289999999999999</v>
+      </c>
+      <c r="AH24" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI24" s="2">
+        <v>0.89829999999999999</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
@@ -3409,7 +3450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -3425,8 +3466,8 @@
       <c r="E25">
         <v>-143</v>
       </c>
-      <c r="F25">
-        <v>4.81</v>
+      <c r="F25" s="3">
+        <v>4.8892511771751472</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3434,8 +3475,8 @@
       <c r="J25" t="s">
         <v>45</v>
       </c>
-      <c r="K25">
-        <v>4.81</v>
+      <c r="K25" s="3">
+        <v>4.8892511771751472</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
@@ -3450,7 +3491,7 @@
         <v>48</v>
       </c>
       <c r="P25">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -3461,11 +3502,11 @@
       <c r="S25">
         <v>6</v>
       </c>
-      <c r="T25">
-        <v>0.3109</v>
-      </c>
-      <c r="U25">
-        <v>0.3213</v>
+      <c r="T25" s="2">
+        <v>0.31090000000000001</v>
+      </c>
+      <c r="U25" s="2">
+        <v>0.32128499999999999</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -3473,10 +3514,10 @@
       <c r="W25">
         <v>90</v>
       </c>
-      <c r="X25">
-        <v>0.3444</v>
-      </c>
-      <c r="Y25">
+      <c r="X25" s="2">
+        <v>0.34439999999999998</v>
+      </c>
+      <c r="Y25" s="2">
         <v>0.31</v>
       </c>
       <c r="Z25" t="b">
@@ -3485,28 +3526,28 @@
       <c r="AA25">
         <v>4.03</v>
       </c>
-      <c r="AB25">
-        <v>0.7446</v>
+      <c r="AB25" s="2">
+        <v>0.7446517979062357</v>
       </c>
       <c r="AC25" t="s">
         <v>49</v>
       </c>
-      <c r="AD25">
+      <c r="AD25" s="2">
         <v>0.1636</v>
       </c>
-      <c r="AE25">
+      <c r="AE25" s="2">
         <v>0.182</v>
       </c>
       <c r="AF25">
         <v>9</v>
       </c>
-      <c r="AG25">
+      <c r="AG25" s="2">
         <v>0.2175</v>
       </c>
-      <c r="AH25">
-        <v>0.2197</v>
-      </c>
-      <c r="AI25">
+      <c r="AH25" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI25" s="2">
         <v>1.0142</v>
       </c>
       <c r="AJ25" t="b">
@@ -3522,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -3538,8 +3579,8 @@
       <c r="E26">
         <v>-150</v>
       </c>
-      <c r="F26">
-        <v>4.05</v>
+      <c r="F26" s="3">
+        <v>4.0206252933735032</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -3547,8 +3588,8 @@
       <c r="J26" t="s">
         <v>45</v>
       </c>
-      <c r="K26">
-        <v>4.05</v>
+      <c r="K26" s="3">
+        <v>4.0206252933735032</v>
       </c>
       <c r="L26" t="s">
         <v>46</v>
@@ -3563,7 +3604,7 @@
         <v>48</v>
       </c>
       <c r="P26">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -3574,11 +3615,11 @@
       <c r="S26">
         <v>6</v>
       </c>
-      <c r="T26">
-        <v>0.2008</v>
-      </c>
-      <c r="U26">
-        <v>0.1851</v>
+      <c r="T26" s="2">
+        <v>0.20080000000000001</v>
+      </c>
+      <c r="U26" s="2">
+        <v>0.18510670000000001</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -3586,11 +3627,11 @@
       <c r="W26">
         <v>98</v>
       </c>
-      <c r="X26">
-        <v>0.1531</v>
-      </c>
-      <c r="Y26">
-        <v>0.329</v>
+      <c r="X26" s="2">
+        <v>0.15310000000000001</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>0.32900000000000001</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
@@ -3598,28 +3639,28 @@
       <c r="AA26">
         <v>4.37</v>
       </c>
-      <c r="AB26">
-        <v>1.0602</v>
+      <c r="AB26" s="2">
+        <v>1.0600819299044151</v>
       </c>
       <c r="AC26" t="s">
         <v>67</v>
       </c>
-      <c r="AD26">
+      <c r="AD26" s="2">
         <v>0.2329</v>
       </c>
-      <c r="AE26">
-        <v>0.237</v>
+      <c r="AE26" s="2">
+        <v>0.23699999999999999</v>
       </c>
       <c r="AF26">
         <v>9</v>
       </c>
-      <c r="AG26">
-        <v>0.2141</v>
-      </c>
-      <c r="AH26">
-        <v>0.2197</v>
-      </c>
-      <c r="AI26">
+      <c r="AG26" s="2">
+        <v>0.21410000000000001</v>
+      </c>
+      <c r="AH26" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI26" s="2">
         <v>1.004</v>
       </c>
       <c r="AJ26" t="b">
@@ -3635,7 +3676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -3651,8 +3692,8 @@
       <c r="E27">
         <v>115</v>
       </c>
-      <c r="F27">
-        <v>5.46</v>
+      <c r="F27" s="3">
+        <v>5.4483841794852701</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3660,8 +3701,8 @@
       <c r="J27" t="s">
         <v>45</v>
       </c>
-      <c r="K27">
-        <v>5.46</v>
+      <c r="K27" s="3">
+        <v>5.4483841794852701</v>
       </c>
       <c r="L27" t="s">
         <v>46</v>
@@ -3676,7 +3717,7 @@
         <v>48</v>
       </c>
       <c r="P27">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -3687,11 +3728,11 @@
       <c r="S27">
         <v>6</v>
       </c>
-      <c r="T27">
-        <v>0.2561</v>
-      </c>
-      <c r="U27">
-        <v>0.2491</v>
+      <c r="T27" s="2">
+        <v>0.25609999999999999</v>
+      </c>
+      <c r="U27" s="2">
+        <v>0.24912519999999999</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -3699,41 +3740,41 @@
       <c r="W27">
         <v>118</v>
       </c>
-      <c r="X27">
-        <v>0.2373</v>
-      </c>
-      <c r="Y27">
+      <c r="X27" s="2">
+        <v>0.23730000000000001</v>
+      </c>
+      <c r="Y27" s="2">
         <v>0.371</v>
       </c>
       <c r="Z27" t="b">
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>4.19</v>
-      </c>
-      <c r="AB27">
-        <v>0.9861</v>
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="AB27" s="2">
+        <v>0.98588984979517513</v>
       </c>
       <c r="AC27" t="s">
         <v>67</v>
       </c>
-      <c r="AD27">
-        <v>0.2166</v>
-      </c>
-      <c r="AE27">
-        <v>0.2222</v>
+      <c r="AD27" s="2">
+        <v>0.21659999999999999</v>
+      </c>
+      <c r="AE27" s="2">
+        <v>0.22220000000000001</v>
       </c>
       <c r="AF27">
         <v>7</v>
       </c>
-      <c r="AG27">
+      <c r="AG27" s="2">
         <v>0.2019</v>
       </c>
-      <c r="AH27">
-        <v>0.2197</v>
-      </c>
-      <c r="AI27">
-        <v>0.9933</v>
+      <c r="AH27" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI27" s="2">
+        <v>0.99329999999999996</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
@@ -3748,7 +3789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -3764,8 +3805,8 @@
       <c r="E28">
         <v>100</v>
       </c>
-      <c r="F28">
-        <v>3.77</v>
+      <c r="F28" s="3">
+        <v>3.9453763143192533</v>
       </c>
       <c r="H28" t="s">
         <v>45</v>
@@ -3773,8 +3814,8 @@
       <c r="J28" t="s">
         <v>45</v>
       </c>
-      <c r="K28">
-        <v>3.77</v>
+      <c r="K28" s="3">
+        <v>3.9453763143192533</v>
       </c>
       <c r="L28" t="s">
         <v>46</v>
@@ -3789,7 +3830,7 @@
         <v>95</v>
       </c>
       <c r="P28">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
@@ -3800,10 +3841,10 @@
       <c r="S28">
         <v>5</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="2">
         <v>0.1905</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="2">
         <v>0.1905</v>
       </c>
       <c r="V28">
@@ -3812,11 +3853,11 @@
       <c r="W28">
         <v>105</v>
       </c>
-      <c r="X28">
+      <c r="X28" s="2">
         <v>0.1905</v>
       </c>
-      <c r="Y28">
-        <v>0.344</v>
+      <c r="Y28" s="2">
+        <v>0.34399999999999997</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
@@ -3824,29 +3865,29 @@
       <c r="AA28">
         <v>4.7</v>
       </c>
-      <c r="AB28">
-        <v>0.9631</v>
+      <c r="AB28" s="2">
+        <v>0.96313154301319981</v>
       </c>
       <c r="AC28" t="s">
         <v>67</v>
       </c>
-      <c r="AD28">
-        <v>0.2116</v>
-      </c>
-      <c r="AE28">
-        <v>0.2017</v>
+      <c r="AD28" s="2">
+        <v>0.21160000000000001</v>
+      </c>
+      <c r="AE28" s="2">
+        <v>0.20169999999999999</v>
       </c>
       <c r="AF28">
         <v>8</v>
       </c>
-      <c r="AG28">
-        <v>0.2071</v>
-      </c>
-      <c r="AH28">
-        <v>0.2197</v>
-      </c>
-      <c r="AI28">
-        <v>0.9797</v>
+      <c r="AG28" s="2">
+        <v>0.20710000000000001</v>
+      </c>
+      <c r="AH28" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI28" s="2">
+        <v>0.97970000000000002</v>
       </c>
       <c r="AJ28" t="b">
         <v>1</v>
@@ -3861,7 +3902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -3877,8 +3918,8 @@
       <c r="E29">
         <v>-128</v>
       </c>
-      <c r="F29">
-        <v>6.19</v>
+      <c r="F29" s="3">
+        <v>6.2553243045008804</v>
       </c>
       <c r="H29" t="s">
         <v>45</v>
@@ -3886,8 +3927,8 @@
       <c r="J29" t="s">
         <v>45</v>
       </c>
-      <c r="K29">
-        <v>6.19</v>
+      <c r="K29" s="3">
+        <v>6.2553243045008804</v>
       </c>
       <c r="L29" t="s">
         <v>57</v>
@@ -3902,7 +3943,7 @@
         <v>48</v>
       </c>
       <c r="P29">
-        <v>6.3</v>
+        <v>6.33</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
@@ -3913,11 +3954,11 @@
       <c r="S29">
         <v>6</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="2">
         <v>0.1915</v>
       </c>
-      <c r="U29">
-        <v>0.1847</v>
+      <c r="U29" s="2">
+        <v>0.18475170000000002</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -3925,41 +3966,41 @@
       <c r="W29">
         <v>121</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="2">
         <v>0.1736</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" s="2">
         <v>0.377</v>
       </c>
       <c r="Z29" t="b">
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>4.06</v>
-      </c>
-      <c r="AB29">
-        <v>1.318</v>
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="AB29" s="2">
+        <v>1.3177059626763767</v>
       </c>
       <c r="AC29" t="s">
         <v>67</v>
       </c>
-      <c r="AD29">
-        <v>0.2895</v>
-      </c>
-      <c r="AE29">
+      <c r="AD29" s="2">
+        <v>0.28949999999999998</v>
+      </c>
+      <c r="AE29" s="2">
         <v>0.2205</v>
       </c>
       <c r="AF29">
         <v>9</v>
       </c>
-      <c r="AG29">
-        <v>0.207</v>
-      </c>
-      <c r="AH29">
-        <v>0.2197</v>
-      </c>
-      <c r="AI29">
-        <v>0.9998</v>
+      <c r="AG29" s="2">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="AH29" s="2">
+        <v>0.21970000000000001</v>
+      </c>
+      <c r="AI29" s="2">
+        <v>0.99980000000000002</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
@@ -3974,258 +4015,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30">
-        <v>6.5</v>
-      </c>
-      <c r="D30">
-        <v>102</v>
-      </c>
-      <c r="E30">
-        <v>-125</v>
-      </c>
-      <c r="H30" t="s">
-        <v>45</v>
-      </c>
-      <c r="J30" t="s">
-        <v>45</v>
-      </c>
-      <c r="L30" t="s">
-        <v>45</v>
-      </c>
-      <c r="M30" t="s">
-        <v>55</v>
-      </c>
-      <c r="N30" t="s">
-        <v>45</v>
-      </c>
-      <c r="O30" t="s">
-        <v>45</v>
-      </c>
-      <c r="S30">
-        <v>6</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>45</v>
-      </c>
-      <c r="AK30" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31">
-        <v>3.5</v>
-      </c>
-      <c r="D31">
-        <v>-131</v>
-      </c>
-      <c r="E31">
-        <v>106</v>
-      </c>
-      <c r="H31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J31" t="s">
-        <v>45</v>
-      </c>
-      <c r="L31" t="s">
-        <v>45</v>
-      </c>
-      <c r="M31" t="s">
-        <v>70</v>
-      </c>
-      <c r="N31" t="s">
-        <v>45</v>
-      </c>
-      <c r="O31" t="s">
-        <v>45</v>
-      </c>
-      <c r="S31">
-        <v>5</v>
-      </c>
-      <c r="AC31" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>45</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32">
-        <v>5.5</v>
-      </c>
-      <c r="D32">
-        <v>-146</v>
-      </c>
-      <c r="E32">
-        <v>125</v>
-      </c>
-      <c r="H32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J32" t="s">
-        <v>45</v>
-      </c>
-      <c r="L32" t="s">
-        <v>45</v>
-      </c>
-      <c r="M32" t="s">
-        <v>79</v>
-      </c>
-      <c r="N32" t="s">
-        <v>45</v>
-      </c>
-      <c r="O32" t="s">
-        <v>45</v>
-      </c>
-      <c r="S32">
-        <v>6</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>45</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33">
-        <v>4.5</v>
-      </c>
-      <c r="D33">
-        <v>-148</v>
-      </c>
-      <c r="E33">
-        <v>120</v>
-      </c>
-      <c r="H33" t="s">
-        <v>45</v>
-      </c>
-      <c r="J33" t="s">
-        <v>45</v>
-      </c>
-      <c r="L33" t="s">
-        <v>45</v>
-      </c>
-      <c r="M33" t="s">
-        <v>82</v>
-      </c>
-      <c r="N33" t="s">
-        <v>45</v>
-      </c>
-      <c r="O33" t="s">
-        <v>45</v>
-      </c>
-      <c r="S33">
-        <v>6</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>45</v>
-      </c>
-      <c r="AK33" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34">
-        <v>6.5</v>
-      </c>
-      <c r="D34">
-        <v>126</v>
-      </c>
-      <c r="E34">
-        <v>-154</v>
-      </c>
-      <c r="H34" t="s">
-        <v>45</v>
-      </c>
-      <c r="J34" t="s">
-        <v>45</v>
-      </c>
-      <c r="L34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M34" t="s">
-        <v>97</v>
-      </c>
-      <c r="N34" t="s">
-        <v>45</v>
-      </c>
-      <c r="O34" t="s">
-        <v>45</v>
-      </c>
-      <c r="S34">
-        <v>6</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>45</v>
-      </c>
-      <c r="AK34" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL34" t="s">
-        <v>45</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:AQ29" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/data/k-props/2026-08-11.xlsx
+++ b/data/k-props/2026-08-11.xlsx
@@ -1,37 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CD2360-FB80-4418-8FC9-8B0FACF1EDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="K-Props" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="K-Props" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'K-Props'!$A$1:$AQ$29</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="103">
   <si>
     <t>date</t>
   </si>
@@ -234,63 +214,63 @@
     <t>Dylan Cease</t>
   </si>
   <si>
+    <t>Nolan McLean</t>
+  </si>
+  <si>
+    <t>New York Mets @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Bailey Ober</t>
+  </si>
+  <si>
+    <t>Nick Lodolo</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Andre Pallante</t>
+  </si>
+  <si>
+    <t>Ryan Johnson</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
   </si>
   <si>
-    <t>Nolan McLean</t>
-  </si>
-  <si>
-    <t>New York Mets @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Martín Pérez</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Bailey Ober</t>
-  </si>
-  <si>
-    <t>Nick Lodolo</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Andre Pallante</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Tomoyuki Sugano</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
     <t>Nick Martinez</t>
   </si>
   <si>
@@ -325,27 +305,37 @@
   </si>
   <si>
     <t>Kansas City Royals @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Eury Perez</t>
+  </si>
+  <si>
+    <t>Martin Perez</t>
+  </si>
+  <si>
+    <t>Cristopher Sanchez</t>
+  </si>
+  <si>
+    <t>Cody Bradford</t>
+  </si>
+  <si>
+    <t>Blake Snell</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.000"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -368,11 +358,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -711,13 +699,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AQ34"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="43" width="16" customWidth="1"/>
+    <col min="1" max="43" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -867,8 +853,8 @@
       <c r="E2">
         <v>-108</v>
       </c>
-      <c r="F2" s="3">
-        <v>4.32271997077207</v>
+      <c r="F2">
+        <v>4.01</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -876,8 +862,8 @@
       <c r="J2" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="3">
-        <v>4.32271997077207</v>
+      <c r="K2">
+        <v>4.01</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -892,7 +878,7 @@
         <v>48</v>
       </c>
       <c r="P2">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -903,11 +889,11 @@
       <c r="S2">
         <v>5</v>
       </c>
-      <c r="T2" s="2">
-        <v>0.1968</v>
-      </c>
-      <c r="U2" s="2">
-        <v>0.19868160000000001</v>
+      <c r="T2">
+        <v>0.1964</v>
+      </c>
+      <c r="U2">
+        <v>0.1984</v>
       </c>
       <c r="V2">
         <v>5</v>
@@ -915,11 +901,11 @@
       <c r="W2">
         <v>129</v>
       </c>
-      <c r="X2" s="2">
+      <c r="X2">
         <v>0.2016</v>
       </c>
-      <c r="Y2" s="2">
-        <v>0.39200000000000002</v>
+      <c r="Y2">
+        <v>0.392</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -927,29 +913,29 @@
       <c r="AA2">
         <v>4.05</v>
       </c>
-      <c r="AB2" s="2">
-        <v>0.93081474738279468</v>
+      <c r="AB2">
+        <v>0.9378</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
       </c>
-      <c r="AD2" s="2">
-        <v>0.20449999999999999</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>0.20519999999999999</v>
+      <c r="AD2">
+        <v>0.2045</v>
+      </c>
+      <c r="AE2">
+        <v>0.2052</v>
       </c>
       <c r="AF2">
         <v>9</v>
       </c>
-      <c r="AG2" s="2">
+      <c r="AG2">
         <v>0.2261</v>
       </c>
-      <c r="AH2" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI2" s="2">
-        <v>0.96189999999999998</v>
+      <c r="AH2">
+        <v>0.218</v>
+      </c>
+      <c r="AI2">
+        <v>0.9619</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -980,8 +966,8 @@
       <c r="E3">
         <v>-150</v>
       </c>
-      <c r="F3" s="3">
-        <v>2.7518828149661534</v>
+      <c r="F3">
+        <v>2.77</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -989,8 +975,8 @@
       <c r="J3" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="3">
-        <v>2.7518828149661534</v>
+      <c r="K3">
+        <v>2.77</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -1016,23 +1002,23 @@
       <c r="S3">
         <v>5</v>
       </c>
-      <c r="T3" s="2">
-        <v>0.26989999999999997</v>
-      </c>
-      <c r="U3" s="2">
-        <v>0.27152839999999995</v>
+      <c r="T3">
+        <v>0.2696</v>
+      </c>
+      <c r="U3">
+        <v>0.271</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W3">
-        <v>43</v>
-      </c>
-      <c r="X3" s="2">
-        <v>0.27910000000000001</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>0.17699999999999999</v>
+        <v>47</v>
+      </c>
+      <c r="X3">
+        <v>0.2766</v>
+      </c>
+      <c r="Y3">
+        <v>0.19</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
@@ -1040,28 +1026,28 @@
       <c r="AA3">
         <v>4.29</v>
       </c>
-      <c r="AB3" s="2">
-        <v>0.8948566226672735</v>
+      <c r="AB3">
+        <v>0.9016</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
       </c>
-      <c r="AD3" s="2">
+      <c r="AD3">
         <v>0.1966</v>
       </c>
-      <c r="AE3" s="2">
-        <v>0.19650000000000001</v>
+      <c r="AE3">
+        <v>0.1965</v>
       </c>
       <c r="AF3">
         <v>9</v>
       </c>
-      <c r="AG3" s="2">
-        <v>0.21759999999999999</v>
-      </c>
-      <c r="AH3" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI3" s="2">
+      <c r="AG3">
+        <v>0.2176</v>
+      </c>
+      <c r="AH3">
+        <v>0.218</v>
+      </c>
+      <c r="AI3">
         <v>0.88</v>
       </c>
       <c r="AJ3" t="b">
@@ -1093,8 +1079,8 @@
       <c r="E4">
         <v>120</v>
       </c>
-      <c r="F4" s="3">
-        <v>6.2326396568100346</v>
+      <c r="F4">
+        <v>6.8</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1102,8 +1088,8 @@
       <c r="J4" t="s">
         <v>45</v>
       </c>
-      <c r="K4" s="3">
-        <v>7.0321335456251965</v>
+      <c r="K4">
+        <v>7.19</v>
       </c>
       <c r="L4" t="s">
         <v>54</v>
@@ -1118,7 +1104,7 @@
         <v>48</v>
       </c>
       <c r="P4">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -1129,11 +1115,11 @@
       <c r="S4">
         <v>6</v>
       </c>
-      <c r="T4" s="2">
-        <v>0.30449999999999999</v>
-      </c>
-      <c r="U4" s="2">
-        <v>0.32018829999999998</v>
+      <c r="T4">
+        <v>0.3045</v>
+      </c>
+      <c r="U4">
+        <v>0.3202</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -1141,41 +1127,41 @@
       <c r="W4">
         <v>112</v>
       </c>
-      <c r="X4" s="2">
-        <v>0.34820000000000001</v>
-      </c>
-      <c r="Y4" s="2">
-        <v>0.35899999999999999</v>
+      <c r="X4">
+        <v>0.3482</v>
+      </c>
+      <c r="Y4">
+        <v>0.359</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AB4" s="2">
-        <v>1.1015020482476103</v>
+        <v>4.1</v>
+      </c>
+      <c r="AB4">
+        <v>1.1102</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
       </c>
-      <c r="AD4" s="2">
-        <v>0.24199999999999999</v>
-      </c>
-      <c r="AE4" s="2">
-        <v>0.23219999999999999</v>
+      <c r="AD4">
+        <v>0.242</v>
+      </c>
+      <c r="AE4">
+        <v>0.2322</v>
       </c>
       <c r="AF4">
         <v>9</v>
       </c>
-      <c r="AG4" s="2">
-        <v>0.20960000000000001</v>
-      </c>
-      <c r="AH4" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI4" s="2">
-        <v>0.91239999999999999</v>
+      <c r="AG4">
+        <v>0.2096</v>
+      </c>
+      <c r="AH4">
+        <v>0.218</v>
+      </c>
+      <c r="AI4">
+        <v>0.9124</v>
       </c>
       <c r="AJ4" t="b">
         <v>1</v>
@@ -1187,7 +1173,7 @@
         <v>50</v>
       </c>
       <c r="AM4">
-        <v>-0.79949388881516192</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
@@ -1197,17 +1183,8 @@
       <c r="B5" t="s">
         <v>56</v>
       </c>
-      <c r="C5">
-        <v>6.5</v>
-      </c>
-      <c r="D5">
-        <v>102</v>
-      </c>
-      <c r="E5">
-        <v>-125</v>
-      </c>
-      <c r="F5" s="3">
-        <v>6.57379419719115</v>
+      <c r="F5">
+        <v>6.39</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1215,8 +1192,8 @@
       <c r="J5" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="3">
-        <v>6.57379419719115</v>
+      <c r="K5">
+        <v>6.39</v>
       </c>
       <c r="L5" t="s">
         <v>57</v>
@@ -1231,7 +1208,7 @@
         <v>48</v>
       </c>
       <c r="P5">
-        <v>5.67</v>
+        <v>5.3</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1242,52 +1219,52 @@
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5" s="2">
-        <v>0.2707</v>
-      </c>
-      <c r="U5" s="2">
-        <v>0.2658742</v>
+      <c r="T5">
+        <v>0.2756</v>
+      </c>
+      <c r="U5">
+        <v>0.277</v>
       </c>
       <c r="V5">
         <v>5</v>
       </c>
       <c r="W5">
-        <v>124</v>
-      </c>
-      <c r="X5" s="2">
-        <v>0.2581</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>0.38300000000000001</v>
+        <v>100</v>
+      </c>
+      <c r="X5">
+        <v>0.28</v>
+      </c>
+      <c r="Y5">
+        <v>0.333</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>4.08</v>
-      </c>
-      <c r="AB5" s="2">
-        <v>1.0118343195266273</v>
+        <v>4.07</v>
+      </c>
+      <c r="AB5">
+        <v>1.0197</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
       </c>
-      <c r="AD5" s="2">
+      <c r="AD5">
         <v>0.2223</v>
       </c>
-      <c r="AE5" s="2">
-        <v>0.25829999999999997</v>
+      <c r="AE5">
+        <v>0.2583</v>
       </c>
       <c r="AF5">
         <v>9</v>
       </c>
-      <c r="AG5" s="2">
+      <c r="AG5">
         <v>0.2359</v>
       </c>
-      <c r="AH5" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI5" s="2">
+      <c r="AH5">
+        <v>0.218</v>
+      </c>
+      <c r="AI5">
         <v>1.0563</v>
       </c>
       <c r="AJ5" t="b">
@@ -1319,8 +1296,8 @@
       <c r="E6">
         <v>-143</v>
       </c>
-      <c r="F6" s="3">
-        <v>4.7977947870519975</v>
+      <c r="F6">
+        <v>4.91</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1328,8 +1305,8 @@
       <c r="J6" t="s">
         <v>45</v>
       </c>
-      <c r="K6" s="3">
-        <v>4.7977947870519975</v>
+      <c r="K6">
+        <v>4.91</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
@@ -1344,7 +1321,7 @@
         <v>48</v>
       </c>
       <c r="P6">
-        <v>5.67</v>
+        <v>5.8</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1355,11 +1332,11 @@
       <c r="S6">
         <v>5</v>
       </c>
-      <c r="T6" s="2">
-        <v>0.23449999999999999</v>
-      </c>
-      <c r="U6" s="2">
-        <v>0.22611539999999997</v>
+      <c r="T6">
+        <v>0.2345</v>
+      </c>
+      <c r="U6">
+        <v>0.2261</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1367,40 +1344,40 @@
       <c r="W6">
         <v>118</v>
       </c>
-      <c r="X6" s="2">
-        <v>0.21190000000000001</v>
-      </c>
-      <c r="Y6" s="2">
+      <c r="X6">
+        <v>0.2119</v>
+      </c>
+      <c r="Y6">
         <v>0.371</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="AB6" s="2">
-        <v>0.90168411470186616</v>
+        <v>4.02</v>
+      </c>
+      <c r="AB6">
+        <v>0.9085</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
       </c>
-      <c r="AD6" s="2">
+      <c r="AD6">
         <v>0.1981</v>
       </c>
-      <c r="AE6" s="2">
-        <v>0.22239999999999999</v>
+      <c r="AE6">
+        <v>0.2224</v>
       </c>
       <c r="AF6">
         <v>9</v>
       </c>
-      <c r="AG6" s="2">
-        <v>0.23519999999999999</v>
-      </c>
-      <c r="AH6" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI6" s="2">
+      <c r="AG6">
+        <v>0.2352</v>
+      </c>
+      <c r="AH6">
+        <v>0.218</v>
+      </c>
+      <c r="AI6">
         <v>1.0324</v>
       </c>
       <c r="AJ6" t="b">
@@ -1432,8 +1409,8 @@
       <c r="E7">
         <v>-155</v>
       </c>
-      <c r="F7" s="3">
-        <v>4.9216952510201191</v>
+      <c r="F7">
+        <v>4.73</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1441,8 +1418,8 @@
       <c r="J7" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="3">
-        <v>4.9216952510201191</v>
+      <c r="K7">
+        <v>4.73</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
@@ -1457,7 +1434,7 @@
         <v>48</v>
       </c>
       <c r="P7">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1468,11 +1445,11 @@
       <c r="S7">
         <v>5</v>
       </c>
-      <c r="T7" s="2">
-        <v>0.23130000000000001</v>
-      </c>
-      <c r="U7" s="2">
-        <v>0.23035500000000003</v>
+      <c r="T7">
+        <v>0.2313</v>
+      </c>
+      <c r="U7">
+        <v>0.2304</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1480,10 +1457,10 @@
       <c r="W7">
         <v>92</v>
       </c>
-      <c r="X7" s="2">
+      <c r="X7">
         <v>0.2283</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y7">
         <v>0.315</v>
       </c>
       <c r="Z7" t="b">
@@ -1492,29 +1469,29 @@
       <c r="AA7">
         <v>4.32</v>
       </c>
-      <c r="AB7" s="2">
-        <v>1.0177514792899407</v>
+      <c r="AB7">
+        <v>1.0257</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
       </c>
-      <c r="AD7" s="2">
-        <v>0.22359999999999999</v>
-      </c>
-      <c r="AE7" s="2">
-        <v>0.22259999999999999</v>
+      <c r="AD7">
+        <v>0.2236</v>
+      </c>
+      <c r="AE7">
+        <v>0.2226</v>
       </c>
       <c r="AF7">
         <v>9</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AG7">
         <v>0.218</v>
       </c>
-      <c r="AH7" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI7" s="2">
-        <v>0.97189999999999999</v>
+      <c r="AH7">
+        <v>0.218</v>
+      </c>
+      <c r="AI7">
+        <v>0.9719</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
@@ -1545,8 +1522,8 @@
       <c r="E8">
         <v>-134</v>
       </c>
-      <c r="F8" s="3">
-        <v>6.2982708605325701</v>
+      <c r="F8">
+        <v>6.9</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1554,11 +1531,11 @@
       <c r="J8" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="3">
-        <v>7.097764749347732</v>
+      <c r="K8">
+        <v>6.9</v>
       </c>
       <c r="L8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M8" t="s">
         <v>62</v>
@@ -1570,7 +1547,7 @@
         <v>48</v>
       </c>
       <c r="P8">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1581,11 +1558,11 @@
       <c r="S8">
         <v>6</v>
       </c>
-      <c r="T8" s="2">
-        <v>0.24279999999999999</v>
-      </c>
-      <c r="U8" s="2">
-        <v>0.24245529999999998</v>
+      <c r="T8">
+        <v>0.2428</v>
+      </c>
+      <c r="U8">
+        <v>0.2425</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1593,40 +1570,40 @@
       <c r="W8">
         <v>124</v>
       </c>
-      <c r="X8" s="2">
+      <c r="X8">
         <v>0.2419</v>
       </c>
-      <c r="Y8" s="2">
-        <v>0.38300000000000001</v>
+      <c r="Y8">
+        <v>0.383</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="AB8" s="2">
-        <v>1.1661356395084204</v>
+        <v>4.11</v>
+      </c>
+      <c r="AB8">
+        <v>1.1753</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
       </c>
-      <c r="AD8" s="2">
-        <v>0.25619999999999998</v>
-      </c>
-      <c r="AE8" s="2">
+      <c r="AD8">
+        <v>0.2562</v>
+      </c>
+      <c r="AE8">
         <v>0.2601</v>
       </c>
       <c r="AF8">
         <v>9</v>
       </c>
-      <c r="AG8" s="2">
-        <v>0.24390000000000001</v>
-      </c>
-      <c r="AH8" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI8" s="2">
+      <c r="AG8">
+        <v>0.2439</v>
+      </c>
+      <c r="AH8">
+        <v>0.218</v>
+      </c>
+      <c r="AI8">
         <v>1.018</v>
       </c>
       <c r="AJ8" t="b">
@@ -1639,7 +1616,7 @@
         <v>50</v>
       </c>
       <c r="AM8">
-        <v>-0.79949388881516192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
@@ -1658,8 +1635,8 @@
       <c r="E9">
         <v>-145</v>
       </c>
-      <c r="F9" s="3">
-        <v>6.016514650860266</v>
+      <c r="F9">
+        <v>5.88</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1667,11 +1644,11 @@
       <c r="J9" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="3">
-        <v>6.016514650860266</v>
+      <c r="K9">
+        <v>5.88</v>
       </c>
       <c r="L9" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="M9" t="s">
         <v>62</v>
@@ -1683,7 +1660,7 @@
         <v>48</v>
       </c>
       <c r="P9">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -1694,11 +1671,11 @@
       <c r="S9">
         <v>5</v>
       </c>
-      <c r="T9" s="2">
-        <v>0.26240000000000002</v>
-      </c>
-      <c r="U9" s="2">
-        <v>0.25387609999999999</v>
+      <c r="T9">
+        <v>0.2624</v>
+      </c>
+      <c r="U9">
+        <v>0.2539</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1706,11 +1683,11 @@
       <c r="W9">
         <v>117</v>
       </c>
-      <c r="X9" s="2">
-        <v>0.23930000000000001</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>0.36899999999999999</v>
+      <c r="X9">
+        <v>0.2393</v>
+      </c>
+      <c r="Y9">
+        <v>0.369</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
@@ -1718,29 +1695,29 @@
       <c r="AA9">
         <v>4.16</v>
       </c>
-      <c r="AB9" s="2">
-        <v>1.0386891215293581</v>
+      <c r="AB9">
+        <v>1.0466</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
       </c>
-      <c r="AD9" s="2">
-        <v>0.22819999999999999</v>
-      </c>
-      <c r="AE9" s="2">
+      <c r="AD9">
+        <v>0.2282</v>
+      </c>
+      <c r="AE9">
         <v>0.2152</v>
       </c>
       <c r="AF9">
         <v>9</v>
       </c>
-      <c r="AG9" s="2">
-        <v>0.23710000000000001</v>
-      </c>
-      <c r="AH9" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI9" s="2">
-        <v>0.96730000000000005</v>
+      <c r="AG9">
+        <v>0.2371</v>
+      </c>
+      <c r="AH9">
+        <v>0.218</v>
+      </c>
+      <c r="AI9">
+        <v>0.9673</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
@@ -1771,8 +1748,8 @@
       <c r="E10">
         <v>-134</v>
       </c>
-      <c r="F10" s="3">
-        <v>2.940972737369139</v>
+      <c r="F10">
+        <v>2.85</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1780,8 +1757,8 @@
       <c r="J10" t="s">
         <v>45</v>
       </c>
-      <c r="K10" s="3">
-        <v>2.940972737369139</v>
+      <c r="K10">
+        <v>2.85</v>
       </c>
       <c r="L10" t="s">
         <v>46</v>
@@ -1796,7 +1773,7 @@
         <v>48</v>
       </c>
       <c r="P10">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1807,11 +1784,11 @@
       <c r="S10">
         <v>6</v>
       </c>
-      <c r="T10" s="2">
-        <v>0.22939999999999999</v>
-      </c>
-      <c r="U10" s="2">
-        <v>0.22939999999999999</v>
+      <c r="T10">
+        <v>0.2294</v>
+      </c>
+      <c r="U10">
+        <v>0.2294</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1819,11 +1796,11 @@
       <c r="W10">
         <v>109</v>
       </c>
-      <c r="X10" s="2">
-        <v>0.22939999999999999</v>
-      </c>
-      <c r="Y10" s="2">
-        <v>0.35299999999999998</v>
+      <c r="X10">
+        <v>0.2294</v>
+      </c>
+      <c r="Y10">
+        <v>0.353</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
@@ -1831,28 +1808,28 @@
       <c r="AA10">
         <v>4.54</v>
       </c>
-      <c r="AB10" s="2">
-        <v>0.64178425125170679</v>
+      <c r="AB10">
+        <v>0.6466</v>
       </c>
       <c r="AC10" t="s">
         <v>49</v>
       </c>
-      <c r="AD10" s="2">
-        <v>0.14099999999999999</v>
-      </c>
-      <c r="AE10" s="2">
+      <c r="AD10">
+        <v>0.141</v>
+      </c>
+      <c r="AE10">
         <v>0.1474</v>
       </c>
       <c r="AF10">
         <v>9</v>
       </c>
-      <c r="AG10" s="2">
-        <v>0.21640000000000001</v>
-      </c>
-      <c r="AH10" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI10" s="2">
+      <c r="AG10">
+        <v>0.2164</v>
+      </c>
+      <c r="AH10">
+        <v>0.218</v>
+      </c>
+      <c r="AI10">
         <v>0.88</v>
       </c>
       <c r="AJ10" t="b">
@@ -1884,8 +1861,8 @@
       <c r="E11">
         <v>124</v>
       </c>
-      <c r="F11" s="3">
-        <v>6.5667615684368714</v>
+      <c r="F11">
+        <v>6.8</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1893,11 +1870,11 @@
       <c r="J11" t="s">
         <v>45</v>
       </c>
-      <c r="K11" s="3">
-        <v>7.3662554572520333</v>
+      <c r="K11">
+        <v>6.8</v>
       </c>
       <c r="L11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M11" t="s">
         <v>65</v>
@@ -1920,11 +1897,11 @@
       <c r="S11">
         <v>6</v>
       </c>
-      <c r="T11" s="2">
+      <c r="T11">
         <v>0.3644</v>
       </c>
-      <c r="U11" s="2">
-        <v>0.36109659999999999</v>
+      <c r="U11">
+        <v>0.3611</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1932,11 +1909,11 @@
       <c r="W11">
         <v>132</v>
       </c>
-      <c r="X11" s="2">
-        <v>0.35610000000000003</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>0.39800000000000002</v>
+      <c r="X11">
+        <v>0.3561</v>
+      </c>
+      <c r="Y11">
+        <v>0.398</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
@@ -1944,41 +1921,41 @@
       <c r="AA11">
         <v>4</v>
       </c>
-      <c r="AB11" s="2">
-        <v>0.85753299954483386</v>
+      <c r="AB11">
+        <v>0.8064</v>
       </c>
       <c r="AC11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD11" s="2">
-        <v>0.18840000000000001</v>
-      </c>
-      <c r="AE11" s="2">
-        <v>0.18809999999999999</v>
+        <v>49</v>
+      </c>
+      <c r="AD11">
+        <v>0.1758</v>
+      </c>
+      <c r="AE11">
+        <v>0.1864</v>
       </c>
       <c r="AF11">
-        <v>8</v>
-      </c>
-      <c r="AG11" s="2">
+        <v>9</v>
+      </c>
+      <c r="AG11">
         <v>0.2185</v>
       </c>
-      <c r="AH11" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI11" s="2">
-        <v>0.99119999999999997</v>
+      <c r="AH11">
+        <v>0.218</v>
+      </c>
+      <c r="AI11">
+        <v>0.9709</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AL11" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AM11">
-        <v>-0.79949388881516192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
@@ -1986,7 +1963,7 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>5.5</v>
@@ -1997,8 +1974,8 @@
       <c r="E12">
         <v>122</v>
       </c>
-      <c r="F12" s="3">
-        <v>6.9827469327026659</v>
+      <c r="F12">
+        <v>6.67</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -2006,14 +1983,14 @@
       <c r="J12" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="3">
-        <v>6.9827469327026659</v>
+      <c r="K12">
+        <v>7.06</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N12">
         <v>824886</v>
@@ -2022,7 +1999,7 @@
         <v>48</v>
       </c>
       <c r="P12">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -2033,11 +2010,11 @@
       <c r="S12">
         <v>6</v>
       </c>
-      <c r="T12" s="2">
-        <v>0.28470000000000001</v>
-      </c>
-      <c r="U12" s="2">
-        <v>0.29124030000000001</v>
+      <c r="T12">
+        <v>0.2847</v>
+      </c>
+      <c r="U12">
+        <v>0.2912</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -2045,41 +2022,41 @@
       <c r="W12">
         <v>126</v>
       </c>
-      <c r="X12" s="2">
-        <v>0.30159999999999998</v>
-      </c>
-      <c r="Y12" s="2">
-        <v>0.38700000000000001</v>
+      <c r="X12">
+        <v>0.3016</v>
+      </c>
+      <c r="Y12">
+        <v>0.387</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="AB12" s="2">
-        <v>1.0081929904415112</v>
+        <v>4.19</v>
+      </c>
+      <c r="AB12">
+        <v>1.0158</v>
       </c>
       <c r="AC12" t="s">
         <v>49</v>
       </c>
-      <c r="AD12" s="2">
+      <c r="AD12">
         <v>0.2215</v>
       </c>
-      <c r="AE12" s="2">
+      <c r="AE12">
         <v>0.2152</v>
       </c>
       <c r="AF12">
         <v>9</v>
       </c>
-      <c r="AG12" s="2">
-        <v>0.21790000000000001</v>
-      </c>
-      <c r="AH12" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI12" s="2">
-        <v>1.0009999999999999</v>
+      <c r="AG12">
+        <v>0.2179</v>
+      </c>
+      <c r="AH12">
+        <v>0.218</v>
+      </c>
+      <c r="AI12">
+        <v>1.001</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
@@ -2091,7 +2068,7 @@
         <v>50</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
@@ -2099,19 +2076,10 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13">
-        <v>3.5</v>
-      </c>
-      <c r="D13">
-        <v>-131</v>
-      </c>
-      <c r="E13">
-        <v>106</v>
-      </c>
-      <c r="F13" s="3">
-        <v>5.3140287173599789</v>
+        <v>69</v>
+      </c>
+      <c r="F13">
+        <v>5.08</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2119,14 +2087,14 @@
       <c r="J13" t="s">
         <v>45</v>
       </c>
-      <c r="K13" s="3">
-        <v>5.3140287173599789</v>
+      <c r="K13">
+        <v>5.08</v>
       </c>
       <c r="L13" t="s">
         <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N13">
         <v>824886</v>
@@ -2135,7 +2103,7 @@
         <v>48</v>
       </c>
       <c r="P13">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -2146,11 +2114,11 @@
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13" s="2">
-        <v>0.19159999999999999</v>
-      </c>
-      <c r="U13" s="2">
-        <v>0.18817599999999998</v>
+      <c r="T13">
+        <v>0.1916</v>
+      </c>
+      <c r="U13">
+        <v>0.1882</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -2158,41 +2126,41 @@
       <c r="W13">
         <v>94</v>
       </c>
-      <c r="X13" s="2">
-        <v>0.18090000000000001</v>
-      </c>
-      <c r="Y13" s="2">
+      <c r="X13">
+        <v>0.1809</v>
+      </c>
+      <c r="Y13">
         <v>0.32</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="AB13" s="2">
-        <v>1.3563950842057351</v>
+        <v>4.06</v>
+      </c>
+      <c r="AB13">
+        <v>1.3669</v>
       </c>
       <c r="AC13" t="s">
         <v>49</v>
       </c>
-      <c r="AD13" s="2">
-        <v>0.29799999999999999</v>
-      </c>
-      <c r="AE13" s="2">
-        <v>0.28029999999999999</v>
+      <c r="AD13">
+        <v>0.298</v>
+      </c>
+      <c r="AE13">
+        <v>0.2803</v>
       </c>
       <c r="AF13">
         <v>9</v>
       </c>
-      <c r="AG13" s="2">
-        <v>0.23150000000000001</v>
-      </c>
-      <c r="AH13" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI13" s="2">
-        <v>0.96209999999999996</v>
+      <c r="AG13">
+        <v>0.2315</v>
+      </c>
+      <c r="AH13">
+        <v>0.218</v>
+      </c>
+      <c r="AI13">
+        <v>0.9621</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
@@ -2212,7 +2180,7 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C14">
         <v>4.5</v>
@@ -2223,8 +2191,8 @@
       <c r="E14">
         <v>-152</v>
       </c>
-      <c r="F14" s="3">
-        <v>4.4259036792464013</v>
+      <c r="F14">
+        <v>4.46</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2232,14 +2200,14 @@
       <c r="J14" t="s">
         <v>45</v>
       </c>
-      <c r="K14" s="3">
-        <v>4.4259036792464013</v>
+      <c r="K14">
+        <v>4.46</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N14">
         <v>823673</v>
@@ -2248,7 +2216,7 @@
         <v>48</v>
       </c>
       <c r="P14">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
@@ -2259,11 +2227,11 @@
       <c r="S14">
         <v>6</v>
       </c>
-      <c r="T14" s="2">
-        <v>0.19389999999999999</v>
-      </c>
-      <c r="U14" s="2">
-        <v>0.20365359999999999</v>
+      <c r="T14">
+        <v>0.1939</v>
+      </c>
+      <c r="U14">
+        <v>0.2037</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -2271,11 +2239,11 @@
       <c r="W14">
         <v>123</v>
       </c>
-      <c r="X14" s="2">
+      <c r="X14">
         <v>0.2195</v>
       </c>
-      <c r="Y14" s="2">
-        <v>0.38100000000000001</v>
+      <c r="Y14">
+        <v>0.381</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
@@ -2283,29 +2251,29 @@
       <c r="AA14">
         <v>4.26</v>
       </c>
-      <c r="AB14" s="2">
-        <v>0.93218024578971326</v>
+      <c r="AB14">
+        <v>0.9395</v>
       </c>
       <c r="AC14" t="s">
         <v>49</v>
       </c>
-      <c r="AD14" s="2">
-        <v>0.20480000000000001</v>
-      </c>
-      <c r="AE14" s="2">
+      <c r="AD14">
+        <v>0.2048</v>
+      </c>
+      <c r="AE14">
         <v>0.1903</v>
       </c>
       <c r="AF14">
         <v>9</v>
       </c>
-      <c r="AG14" s="2">
-        <v>0.21060000000000001</v>
-      </c>
-      <c r="AH14" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI14" s="2">
-        <v>0.96519999999999995</v>
+      <c r="AG14">
+        <v>0.2106</v>
+      </c>
+      <c r="AH14">
+        <v>0.218</v>
+      </c>
+      <c r="AI14">
+        <v>0.9652</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
@@ -2325,7 +2293,7 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2336,8 +2304,8 @@
       <c r="E15">
         <v>-123</v>
       </c>
-      <c r="F15" s="3">
-        <v>4.5817181071463251</v>
+      <c r="F15">
+        <v>4.46</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2345,14 +2313,14 @@
       <c r="J15" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="3">
-        <v>4.5817181071463251</v>
+      <c r="K15">
+        <v>4.46</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N15">
         <v>823673</v>
@@ -2361,7 +2329,7 @@
         <v>48</v>
       </c>
       <c r="P15">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -2372,11 +2340,11 @@
       <c r="S15">
         <v>6</v>
       </c>
-      <c r="T15" s="2">
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="U15" s="2">
-        <v>0.16038540000000001</v>
+      <c r="T15">
+        <v>0.162</v>
+      </c>
+      <c r="U15">
+        <v>0.1604</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -2384,11 +2352,11 @@
       <c r="W15">
         <v>108</v>
       </c>
-      <c r="X15" s="2">
-        <v>0.15740000000000001</v>
-      </c>
-      <c r="Y15" s="2">
-        <v>0.35099999999999998</v>
+      <c r="X15">
+        <v>0.1574</v>
+      </c>
+      <c r="Y15">
+        <v>0.351</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
@@ -2396,29 +2364,29 @@
       <c r="AA15">
         <v>4.18</v>
       </c>
-      <c r="AB15" s="2">
-        <v>1.1752389622212107</v>
+      <c r="AB15">
+        <v>1.1843</v>
       </c>
       <c r="AC15" t="s">
         <v>49</v>
       </c>
-      <c r="AD15" s="2">
-        <v>0.25819999999999999</v>
-      </c>
-      <c r="AE15" s="2">
-        <v>0.25340000000000001</v>
+      <c r="AD15">
+        <v>0.2582</v>
+      </c>
+      <c r="AE15">
+        <v>0.2534</v>
       </c>
       <c r="AF15">
         <v>9</v>
       </c>
-      <c r="AG15" s="2">
-        <v>0.23830000000000001</v>
-      </c>
-      <c r="AH15" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI15" s="2">
-        <v>1.0256000000000001</v>
+      <c r="AG15">
+        <v>0.2383</v>
+      </c>
+      <c r="AH15">
+        <v>0.218</v>
+      </c>
+      <c r="AI15">
+        <v>1.0256</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
@@ -2438,7 +2406,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2449,8 +2417,8 @@
       <c r="E16">
         <v>-105</v>
       </c>
-      <c r="F16" s="3">
-        <v>4.7452582968046775</v>
+      <c r="F16">
+        <v>4.69</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2458,14 +2426,14 @@
       <c r="J16" t="s">
         <v>45</v>
       </c>
-      <c r="K16" s="3">
-        <v>4.7452582968046775</v>
+      <c r="K16">
+        <v>4.69</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N16">
         <v>824563</v>
@@ -2474,7 +2442,7 @@
         <v>48</v>
       </c>
       <c r="P16">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -2485,11 +2453,11 @@
       <c r="S16">
         <v>6</v>
       </c>
-      <c r="T16" s="2">
+      <c r="T16">
         <v>0.1792</v>
       </c>
-      <c r="U16" s="2">
-        <v>0.18130599999999999</v>
+      <c r="U16">
+        <v>0.1813</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -2497,11 +2465,11 @@
       <c r="W16">
         <v>108</v>
       </c>
-      <c r="X16" s="2">
+      <c r="X16">
         <v>0.1852</v>
       </c>
-      <c r="Y16" s="2">
-        <v>0.35099999999999998</v>
+      <c r="Y16">
+        <v>0.351</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
@@ -2509,28 +2477,28 @@
       <c r="AA16">
         <v>4.45</v>
       </c>
-      <c r="AB16" s="2">
-        <v>1.0505234410559854</v>
+      <c r="AB16">
+        <v>1.0586</v>
       </c>
       <c r="AC16" t="s">
         <v>49</v>
       </c>
-      <c r="AD16" s="2">
-        <v>0.23080000000000001</v>
-      </c>
-      <c r="AE16" s="2">
+      <c r="AD16">
+        <v>0.2308</v>
+      </c>
+      <c r="AE16">
         <v>0.2581</v>
       </c>
       <c r="AF16">
         <v>9</v>
       </c>
-      <c r="AG16" s="2">
-        <v>0.24629999999999999</v>
-      </c>
-      <c r="AH16" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI16" s="2">
+      <c r="AG16">
+        <v>0.2463</v>
+      </c>
+      <c r="AH16">
+        <v>0.218</v>
+      </c>
+      <c r="AI16">
         <v>1.0504</v>
       </c>
       <c r="AJ16" t="b">
@@ -2546,12 +2514,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>7.5</v>
@@ -2562,8 +2530,8 @@
       <c r="E17">
         <v>-137</v>
       </c>
-      <c r="F17" s="3">
-        <v>8.3738685535713202</v>
+      <c r="F17">
+        <v>8.51</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2571,14 +2539,14 @@
       <c r="J17" t="s">
         <v>45</v>
       </c>
-      <c r="K17" s="3">
-        <v>9.1733624423864821</v>
+      <c r="K17">
+        <v>8.9</v>
       </c>
       <c r="L17" t="s">
         <v>54</v>
       </c>
       <c r="M17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N17">
         <v>824563</v>
@@ -2587,7 +2555,7 @@
         <v>48</v>
       </c>
       <c r="P17">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
@@ -2598,11 +2566,11 @@
       <c r="S17">
         <v>6</v>
       </c>
-      <c r="T17" s="2">
-        <v>0.27429999999999999</v>
-      </c>
-      <c r="U17" s="2">
-        <v>0.29571700000000001</v>
+      <c r="T17">
+        <v>0.2743</v>
+      </c>
+      <c r="U17">
+        <v>0.2957</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2610,11 +2578,11 @@
       <c r="W17">
         <v>114</v>
       </c>
-      <c r="X17" s="2">
-        <v>0.33329999999999999</v>
-      </c>
-      <c r="Y17" s="2">
-        <v>0.36299999999999999</v>
+      <c r="X17">
+        <v>0.3333</v>
+      </c>
+      <c r="Y17">
+        <v>0.363</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
@@ -2622,28 +2590,28 @@
       <c r="AA17">
         <v>4.08</v>
       </c>
-      <c r="AB17" s="2">
-        <v>1.2366863905325443</v>
+      <c r="AB17">
+        <v>1.2461</v>
       </c>
       <c r="AC17" t="s">
         <v>49</v>
       </c>
-      <c r="AD17" s="2">
+      <c r="AD17">
         <v>0.2717</v>
       </c>
-      <c r="AE17" s="2">
-        <v>0.27810000000000001</v>
+      <c r="AE17">
+        <v>0.2781</v>
       </c>
       <c r="AF17">
         <v>9</v>
       </c>
-      <c r="AG17" s="2">
-        <v>0.25490000000000002</v>
-      </c>
-      <c r="AH17" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI17" s="2">
+      <c r="AG17">
+        <v>0.2549</v>
+      </c>
+      <c r="AH17">
+        <v>0.218</v>
+      </c>
+      <c r="AI17">
         <v>1.0843</v>
       </c>
       <c r="AJ17" t="b">
@@ -2656,27 +2624,18 @@
         <v>50</v>
       </c>
       <c r="AM17">
-        <v>-0.79949388881516192</v>
+        <v>-0.39</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18">
-        <v>5.5</v>
-      </c>
-      <c r="D18">
-        <v>-146</v>
-      </c>
-      <c r="E18">
-        <v>125</v>
-      </c>
-      <c r="F18" s="3">
-        <v>6.4187761525971183</v>
+        <v>76</v>
+      </c>
+      <c r="F18">
+        <v>6.78</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2684,14 +2643,14 @@
       <c r="J18" t="s">
         <v>45</v>
       </c>
-      <c r="K18" s="3">
-        <v>7.2182700414122802</v>
+      <c r="K18">
+        <v>7.17</v>
       </c>
       <c r="L18" t="s">
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N18">
         <v>823019</v>
@@ -2700,7 +2659,7 @@
         <v>48</v>
       </c>
       <c r="P18">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="Q18" t="b">
         <v>0</v>
@@ -2711,11 +2670,11 @@
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18" s="2">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="U18" s="2">
-        <v>0.28060040000000003</v>
+      <c r="T18">
+        <v>0.278</v>
+      </c>
+      <c r="U18">
+        <v>0.2806</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2723,11 +2682,11 @@
       <c r="W18">
         <v>130</v>
       </c>
-      <c r="X18" s="2">
-        <v>0.28460000000000002</v>
-      </c>
-      <c r="Y18" s="2">
-        <v>0.39400000000000002</v>
+      <c r="X18">
+        <v>0.2846</v>
+      </c>
+      <c r="Y18">
+        <v>0.394</v>
       </c>
       <c r="Z18" t="b">
         <v>0</v>
@@ -2735,29 +2694,29 @@
       <c r="AA18">
         <v>4.18</v>
       </c>
-      <c r="AB18" s="2">
-        <v>1.0450614474283113</v>
+      <c r="AB18">
+        <v>1.0532</v>
       </c>
       <c r="AC18" t="s">
         <v>49</v>
       </c>
-      <c r="AD18" s="2">
+      <c r="AD18">
         <v>0.2296</v>
       </c>
-      <c r="AE18" s="2">
+      <c r="AE18">
         <v>0.1905</v>
       </c>
       <c r="AF18">
         <v>9</v>
       </c>
-      <c r="AG18" s="2">
-        <v>0.18049999999999999</v>
-      </c>
-      <c r="AH18" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI18" s="2">
-        <v>0.93030000000000002</v>
+      <c r="AG18">
+        <v>0.1805</v>
+      </c>
+      <c r="AH18">
+        <v>0.218</v>
+      </c>
+      <c r="AI18">
+        <v>0.9303</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
@@ -2769,15 +2728,15 @@
         <v>50</v>
       </c>
       <c r="AM18">
-        <v>-0.79949388881516192</v>
+        <v>-0.39</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>3.5</v>
@@ -2788,8 +2747,8 @@
       <c r="E19">
         <v>-115</v>
       </c>
-      <c r="F19" s="3">
-        <v>3.1955738963089537</v>
+      <c r="F19">
+        <v>3.2</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2797,14 +2756,14 @@
       <c r="J19" t="s">
         <v>45</v>
       </c>
-      <c r="K19" s="3">
-        <v>3.1955738963089537</v>
+      <c r="K19">
+        <v>3.2</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N19">
         <v>823019</v>
@@ -2813,7 +2772,7 @@
         <v>48</v>
       </c>
       <c r="P19">
-        <v>5.67</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -2824,11 +2783,11 @@
       <c r="S19">
         <v>6</v>
       </c>
-      <c r="T19" s="2">
+      <c r="T19">
         <v>0.1741</v>
       </c>
-      <c r="U19" s="2">
-        <v>0.17186200000000001</v>
+      <c r="U19">
+        <v>0.1718</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2836,10 +2795,10 @@
       <c r="W19">
         <v>119</v>
       </c>
-      <c r="X19" s="2">
+      <c r="X19">
         <v>0.1681</v>
       </c>
-      <c r="Y19" s="2">
+      <c r="Y19">
         <v>0.373</v>
       </c>
       <c r="Z19" t="b">
@@ -2848,28 +2807,28 @@
       <c r="AA19">
         <v>4.17</v>
       </c>
-      <c r="AB19" s="2">
-        <v>0.84797451069640417</v>
+      <c r="AB19">
+        <v>0.8546</v>
       </c>
       <c r="AC19" t="s">
         <v>49</v>
       </c>
-      <c r="AD19" s="2">
-        <v>0.18629999999999999</v>
-      </c>
-      <c r="AE19" s="2">
-        <v>0.18990000000000001</v>
+      <c r="AD19">
+        <v>0.1863</v>
+      </c>
+      <c r="AE19">
+        <v>0.1899</v>
       </c>
       <c r="AF19">
         <v>9</v>
       </c>
-      <c r="AG19" s="2">
-        <v>0.22670000000000001</v>
-      </c>
-      <c r="AH19" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI19" s="2">
+      <c r="AG19">
+        <v>0.2267</v>
+      </c>
+      <c r="AH19">
+        <v>0.218</v>
+      </c>
+      <c r="AI19">
         <v>0.9274</v>
       </c>
       <c r="AJ19" t="b">
@@ -2885,12 +2844,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C20">
         <v>4.5</v>
@@ -2901,8 +2860,8 @@
       <c r="E20">
         <v>-145</v>
       </c>
-      <c r="F20" s="3">
-        <v>3.4906961396014924</v>
+      <c r="F20">
+        <v>3.82</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2910,14 +2869,14 @@
       <c r="J20" t="s">
         <v>45</v>
       </c>
-      <c r="K20" s="3">
-        <v>3.4906961396014924</v>
+      <c r="K20">
+        <v>3.82</v>
       </c>
       <c r="L20" t="s">
         <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N20">
         <v>823997</v>
@@ -2926,7 +2885,7 @@
         <v>48</v>
       </c>
       <c r="P20">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
@@ -2937,11 +2896,11 @@
       <c r="S20">
         <v>6</v>
       </c>
-      <c r="T20" s="2">
-        <v>0.16450000000000001</v>
-      </c>
-      <c r="U20" s="2">
-        <v>0.15634150000000002</v>
+      <c r="T20">
+        <v>0.1645</v>
+      </c>
+      <c r="U20">
+        <v>0.1563</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2949,61 +2908,61 @@
       <c r="W20">
         <v>100</v>
       </c>
-      <c r="X20" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Y20" s="2">
-        <v>0.33300000000000002</v>
+      <c r="X20">
+        <v>0.14</v>
+      </c>
+      <c r="Y20">
+        <v>0.333</v>
       </c>
       <c r="Z20" t="b">
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="AB20" s="2">
-        <v>1.0327719617660445</v>
+        <v>4.56</v>
+      </c>
+      <c r="AB20">
+        <v>1.1142</v>
       </c>
       <c r="AC20" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD20" s="2">
-        <v>0.22689999999999999</v>
-      </c>
-      <c r="AE20" s="2">
-        <v>0.24060000000000001</v>
+        <v>49</v>
+      </c>
+      <c r="AD20">
+        <v>0.2429</v>
+      </c>
+      <c r="AE20">
+        <v>0.2412</v>
       </c>
       <c r="AF20">
         <v>9</v>
       </c>
-      <c r="AG20" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AH20" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI20" s="2">
-        <v>1.0152000000000001</v>
+      <c r="AG20">
+        <v>0.2197</v>
+      </c>
+      <c r="AH20">
+        <v>0.218</v>
+      </c>
+      <c r="AI20">
+        <v>1.0537</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AL20" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AM20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <v>2.5</v>
@@ -3014,8 +2973,8 @@
       <c r="E21">
         <v>107</v>
       </c>
-      <c r="F21" s="3">
-        <v>2.4464501732311597</v>
+      <c r="F21">
+        <v>2.49</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -3023,14 +2982,14 @@
       <c r="J21" t="s">
         <v>45</v>
       </c>
-      <c r="K21" s="3">
-        <v>2.4464501732311597</v>
+      <c r="K21">
+        <v>2.49</v>
       </c>
       <c r="L21" t="s">
         <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N21">
         <v>825046</v>
@@ -3039,7 +2998,7 @@
         <v>48</v>
       </c>
       <c r="P21">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -3050,11 +3009,11 @@
       <c r="S21">
         <v>6</v>
       </c>
-      <c r="T21" s="2">
+      <c r="T21">
         <v>0.1353</v>
       </c>
-      <c r="U21" s="2">
-        <v>0.13309799999999999</v>
+      <c r="U21">
+        <v>0.1331</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -3062,41 +3021,41 @@
       <c r="W21">
         <v>116</v>
       </c>
-      <c r="X21" s="2">
+      <c r="X21">
         <v>0.1293</v>
       </c>
-      <c r="Y21" s="2">
-        <v>0.36699999999999999</v>
+      <c r="Y21">
+        <v>0.367</v>
       </c>
       <c r="Z21" t="b">
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="AB21" s="2">
-        <v>0.86481565771506597</v>
+        <v>4.19</v>
+      </c>
+      <c r="AB21">
+        <v>0.8713</v>
       </c>
       <c r="AC21" t="s">
         <v>49</v>
       </c>
-      <c r="AD21" s="2">
+      <c r="AD21">
         <v>0.19</v>
       </c>
-      <c r="AE21" s="2">
-        <v>0.18890000000000001</v>
+      <c r="AE21">
+        <v>0.1889</v>
       </c>
       <c r="AF21">
         <v>9</v>
       </c>
-      <c r="AG21" s="2">
-        <v>0.20030000000000001</v>
-      </c>
-      <c r="AH21" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI21" s="2">
-        <v>0.95169999999999999</v>
+      <c r="AG21">
+        <v>0.2003</v>
+      </c>
+      <c r="AH21">
+        <v>0.218</v>
+      </c>
+      <c r="AI21">
+        <v>0.9517</v>
       </c>
       <c r="AJ21" t="b">
         <v>1</v>
@@ -3111,12 +3070,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C22">
         <v>4.5</v>
@@ -3127,8 +3086,8 @@
       <c r="E22">
         <v>-125</v>
       </c>
-      <c r="F22" s="3">
-        <v>3.7035327227961359</v>
+      <c r="F22">
+        <v>3.69</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
@@ -3136,14 +3095,14 @@
       <c r="J22" t="s">
         <v>45</v>
       </c>
-      <c r="K22" s="3">
-        <v>3.7035327227961359</v>
+      <c r="K22">
+        <v>3.69</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
       </c>
       <c r="M22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N22">
         <v>825046</v>
@@ -3152,7 +3111,7 @@
         <v>48</v>
       </c>
       <c r="P22">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -3163,11 +3122,11 @@
       <c r="S22">
         <v>6</v>
       </c>
-      <c r="T22" s="2">
+      <c r="T22">
         <v>0.1721</v>
       </c>
-      <c r="U22" s="2">
-        <v>0.169629</v>
+      <c r="U22">
+        <v>0.1697</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -3175,11 +3134,11 @@
       <c r="W22">
         <v>109</v>
       </c>
-      <c r="X22" s="2">
+      <c r="X22">
         <v>0.1651</v>
       </c>
-      <c r="Y22" s="2">
-        <v>0.35299999999999998</v>
+      <c r="Y22">
+        <v>0.353</v>
       </c>
       <c r="Z22" t="b">
         <v>0</v>
@@ -3187,44 +3146,44 @@
       <c r="AA22">
         <v>4.41</v>
       </c>
-      <c r="AB22" s="2">
-        <v>1.0487027765134274</v>
+      <c r="AB22">
+        <v>1.0568</v>
       </c>
       <c r="AC22" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD22" s="2">
-        <v>0.23039999999999999</v>
-      </c>
-      <c r="AE22" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD22">
+        <v>0.2304</v>
+      </c>
+      <c r="AE22">
         <v>0.2281</v>
       </c>
       <c r="AF22">
         <v>9</v>
       </c>
-      <c r="AG22" s="2">
-        <v>0.25040000000000001</v>
-      </c>
-      <c r="AH22" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI22" s="2">
-        <v>1.0108999999999999</v>
+      <c r="AG22">
+        <v>0.2504</v>
+      </c>
+      <c r="AH22">
+        <v>0.218</v>
+      </c>
+      <c r="AI22">
+        <v>1.0109</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
       </c>
       <c r="AK22" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="AL22" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="AM22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -3240,8 +3199,8 @@
       <c r="E23">
         <v>-143</v>
       </c>
-      <c r="F23" s="3">
-        <v>2.7357553743400658</v>
+      <c r="F23">
+        <v>2.7</v>
       </c>
       <c r="H23" t="s">
         <v>45</v>
@@ -3249,8 +3208,8 @@
       <c r="J23" t="s">
         <v>45</v>
       </c>
-      <c r="K23" s="3">
-        <v>2.7357553743400658</v>
+      <c r="K23">
+        <v>2.7</v>
       </c>
       <c r="L23" t="s">
         <v>46</v>
@@ -3265,7 +3224,7 @@
         <v>48</v>
       </c>
       <c r="P23">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -3276,11 +3235,11 @@
       <c r="S23">
         <v>6</v>
       </c>
-      <c r="T23" s="2">
-        <v>0.14069999999999999</v>
-      </c>
-      <c r="U23" s="2">
-        <v>0.1290618</v>
+      <c r="T23">
+        <v>0.1407</v>
+      </c>
+      <c r="U23">
+        <v>0.129</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -3288,41 +3247,41 @@
       <c r="W23">
         <v>111</v>
       </c>
-      <c r="X23" s="2">
+      <c r="X23">
         <v>0.1081</v>
       </c>
-      <c r="Y23" s="2">
-        <v>0.35699999999999998</v>
+      <c r="Y23">
+        <v>0.357</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="AB23" s="2">
-        <v>0.89804278561675011</v>
+        <v>4.02</v>
+      </c>
+      <c r="AB23">
+        <v>0.9048</v>
       </c>
       <c r="AC23" t="s">
         <v>49</v>
       </c>
-      <c r="AD23" s="2">
+      <c r="AD23">
         <v>0.1973</v>
       </c>
-      <c r="AE23" s="2">
-        <v>0.19120000000000001</v>
+      <c r="AE23">
+        <v>0.1912</v>
       </c>
       <c r="AF23">
         <v>9</v>
       </c>
-      <c r="AG23" s="2">
-        <v>0.21790000000000001</v>
-      </c>
-      <c r="AH23" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI23" s="2">
-        <v>0.97860000000000003</v>
+      <c r="AG23">
+        <v>0.2179</v>
+      </c>
+      <c r="AH23">
+        <v>0.218</v>
+      </c>
+      <c r="AI23">
+        <v>0.9786</v>
       </c>
       <c r="AJ23" t="b">
         <v>1</v>
@@ -3337,7 +3296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -3353,8 +3312,8 @@
       <c r="E24">
         <v>-125</v>
       </c>
-      <c r="F24" s="3">
-        <v>3.7756750149571054</v>
+      <c r="F24">
+        <v>3.81</v>
       </c>
       <c r="H24" t="s">
         <v>45</v>
@@ -3362,8 +3321,8 @@
       <c r="J24" t="s">
         <v>45</v>
       </c>
-      <c r="K24" s="3">
-        <v>3.7756750149571054</v>
+      <c r="K24">
+        <v>3.81</v>
       </c>
       <c r="L24" t="s">
         <v>46</v>
@@ -3378,7 +3337,7 @@
         <v>48</v>
       </c>
       <c r="P24">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -3389,11 +3348,11 @@
       <c r="S24">
         <v>6</v>
       </c>
-      <c r="T24" s="2">
-        <v>0.24490000000000001</v>
-      </c>
-      <c r="U24" s="2">
-        <v>0.25614040000000005</v>
+      <c r="T24">
+        <v>0.2449</v>
+      </c>
+      <c r="U24">
+        <v>0.2561</v>
       </c>
       <c r="V24">
         <v>2</v>
@@ -3401,11 +3360,11 @@
       <c r="W24">
         <v>42</v>
       </c>
-      <c r="X24" s="2">
+      <c r="X24">
         <v>0.3095</v>
       </c>
-      <c r="Y24" s="2">
-        <v>0.17399999999999999</v>
+      <c r="Y24">
+        <v>0.174</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
@@ -3413,44 +3372,44 @@
       <c r="AA24">
         <v>4.32</v>
       </c>
-      <c r="AB24" s="2">
-        <v>0.81338188438780157</v>
+      <c r="AB24">
+        <v>0.8199</v>
       </c>
       <c r="AC24" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD24" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD24">
         <v>0.1787</v>
       </c>
-      <c r="AE24" s="2">
-        <v>0.17530000000000001</v>
+      <c r="AE24">
+        <v>0.1753</v>
       </c>
       <c r="AF24">
         <v>9</v>
       </c>
-      <c r="AG24" s="2">
-        <v>0.19289999999999999</v>
-      </c>
-      <c r="AH24" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI24" s="2">
-        <v>0.89829999999999999</v>
+      <c r="AG24">
+        <v>0.1929</v>
+      </c>
+      <c r="AH24">
+        <v>0.218</v>
+      </c>
+      <c r="AI24">
+        <v>0.8983</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="AL24" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="AM24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -3466,8 +3425,8 @@
       <c r="E25">
         <v>-143</v>
       </c>
-      <c r="F25" s="3">
-        <v>4.8892511771751472</v>
+      <c r="F25">
+        <v>4.85</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3475,8 +3434,8 @@
       <c r="J25" t="s">
         <v>45</v>
       </c>
-      <c r="K25" s="3">
-        <v>4.8892511771751472</v>
+      <c r="K25">
+        <v>4.85</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
@@ -3491,7 +3450,7 @@
         <v>48</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -3502,11 +3461,11 @@
       <c r="S25">
         <v>6</v>
       </c>
-      <c r="T25" s="2">
-        <v>0.31090000000000001</v>
-      </c>
-      <c r="U25" s="2">
-        <v>0.32128499999999999</v>
+      <c r="T25">
+        <v>0.3109</v>
+      </c>
+      <c r="U25">
+        <v>0.3213</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -3514,10 +3473,10 @@
       <c r="W25">
         <v>90</v>
       </c>
-      <c r="X25" s="2">
-        <v>0.34439999999999998</v>
-      </c>
-      <c r="Y25" s="2">
+      <c r="X25">
+        <v>0.3444</v>
+      </c>
+      <c r="Y25">
         <v>0.31</v>
       </c>
       <c r="Z25" t="b">
@@ -3526,28 +3485,28 @@
       <c r="AA25">
         <v>4.03</v>
       </c>
-      <c r="AB25" s="2">
-        <v>0.7446517979062357</v>
+      <c r="AB25">
+        <v>0.7503</v>
       </c>
       <c r="AC25" t="s">
         <v>49</v>
       </c>
-      <c r="AD25" s="2">
+      <c r="AD25">
         <v>0.1636</v>
       </c>
-      <c r="AE25" s="2">
+      <c r="AE25">
         <v>0.182</v>
       </c>
       <c r="AF25">
         <v>9</v>
       </c>
-      <c r="AG25" s="2">
+      <c r="AG25">
         <v>0.2175</v>
       </c>
-      <c r="AH25" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI25" s="2">
+      <c r="AH25">
+        <v>0.218</v>
+      </c>
+      <c r="AI25">
         <v>1.0142</v>
       </c>
       <c r="AJ25" t="b">
@@ -3563,7 +3522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -3579,8 +3538,8 @@
       <c r="E26">
         <v>-150</v>
       </c>
-      <c r="F26" s="3">
-        <v>4.0206252933735032</v>
+      <c r="F26">
+        <v>3.85</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -3588,8 +3547,8 @@
       <c r="J26" t="s">
         <v>45</v>
       </c>
-      <c r="K26" s="3">
-        <v>4.0206252933735032</v>
+      <c r="K26">
+        <v>3.85</v>
       </c>
       <c r="L26" t="s">
         <v>46</v>
@@ -3604,7 +3563,7 @@
         <v>48</v>
       </c>
       <c r="P26">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -3615,11 +3574,11 @@
       <c r="S26">
         <v>6</v>
       </c>
-      <c r="T26" s="2">
-        <v>0.20080000000000001</v>
-      </c>
-      <c r="U26" s="2">
-        <v>0.18510670000000001</v>
+      <c r="T26">
+        <v>0.2008</v>
+      </c>
+      <c r="U26">
+        <v>0.1851</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -3627,11 +3586,11 @@
       <c r="W26">
         <v>98</v>
       </c>
-      <c r="X26" s="2">
-        <v>0.15310000000000001</v>
-      </c>
-      <c r="Y26" s="2">
-        <v>0.32900000000000001</v>
+      <c r="X26">
+        <v>0.1531</v>
+      </c>
+      <c r="Y26">
+        <v>0.329</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
@@ -3639,44 +3598,44 @@
       <c r="AA26">
         <v>4.37</v>
       </c>
-      <c r="AB26" s="2">
-        <v>1.0600819299044151</v>
+      <c r="AB26">
+        <v>0.9576</v>
       </c>
       <c r="AC26" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD26" s="2">
-        <v>0.2329</v>
-      </c>
-      <c r="AE26" s="2">
-        <v>0.23699999999999999</v>
+        <v>49</v>
+      </c>
+      <c r="AD26">
+        <v>0.2088</v>
+      </c>
+      <c r="AE26">
+        <v>0.2358</v>
       </c>
       <c r="AF26">
         <v>9</v>
       </c>
-      <c r="AG26" s="2">
-        <v>0.21410000000000001</v>
-      </c>
-      <c r="AH26" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI26" s="2">
-        <v>1.004</v>
+      <c r="AG26">
+        <v>0.2141</v>
+      </c>
+      <c r="AH26">
+        <v>0.218</v>
+      </c>
+      <c r="AI26">
+        <v>1.0551</v>
       </c>
       <c r="AJ26" t="b">
         <v>1</v>
       </c>
       <c r="AK26" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AL26" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AM26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -3692,8 +3651,8 @@
       <c r="E27">
         <v>115</v>
       </c>
-      <c r="F27" s="3">
-        <v>5.4483841794852701</v>
+      <c r="F27">
+        <v>5.67</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3701,8 +3660,8 @@
       <c r="J27" t="s">
         <v>45</v>
       </c>
-      <c r="K27" s="3">
-        <v>5.4483841794852701</v>
+      <c r="K27">
+        <v>5.67</v>
       </c>
       <c r="L27" t="s">
         <v>46</v>
@@ -3717,7 +3676,7 @@
         <v>48</v>
       </c>
       <c r="P27">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -3728,11 +3687,11 @@
       <c r="S27">
         <v>6</v>
       </c>
-      <c r="T27" s="2">
-        <v>0.25609999999999999</v>
-      </c>
-      <c r="U27" s="2">
-        <v>0.24912519999999999</v>
+      <c r="T27">
+        <v>0.2561</v>
+      </c>
+      <c r="U27">
+        <v>0.2491</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -3740,56 +3699,56 @@
       <c r="W27">
         <v>118</v>
       </c>
-      <c r="X27" s="2">
-        <v>0.23730000000000001</v>
-      </c>
-      <c r="Y27" s="2">
+      <c r="X27">
+        <v>0.2373</v>
+      </c>
+      <c r="Y27">
         <v>0.371</v>
       </c>
       <c r="Z27" t="b">
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="AB27" s="2">
-        <v>0.98588984979517513</v>
+        <v>4.19</v>
+      </c>
+      <c r="AB27">
+        <v>1.0228</v>
       </c>
       <c r="AC27" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD27" s="2">
-        <v>0.21659999999999999</v>
-      </c>
-      <c r="AE27" s="2">
-        <v>0.22220000000000001</v>
+        <v>49</v>
+      </c>
+      <c r="AD27">
+        <v>0.223</v>
+      </c>
+      <c r="AE27">
+        <v>0.2261</v>
       </c>
       <c r="AF27">
-        <v>7</v>
-      </c>
-      <c r="AG27" s="2">
+        <v>8</v>
+      </c>
+      <c r="AG27">
         <v>0.2019</v>
       </c>
-      <c r="AH27" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI27" s="2">
-        <v>0.99329999999999996</v>
+      <c r="AH27">
+        <v>0.218</v>
+      </c>
+      <c r="AI27">
+        <v>0.9952</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
       </c>
       <c r="AK27" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AL27" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AM27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3764,8 @@
       <c r="E28">
         <v>100</v>
       </c>
-      <c r="F28" s="3">
-        <v>3.9453763143192533</v>
+      <c r="F28">
+        <v>3.8</v>
       </c>
       <c r="H28" t="s">
         <v>45</v>
@@ -3814,8 +3773,8 @@
       <c r="J28" t="s">
         <v>45</v>
       </c>
-      <c r="K28" s="3">
-        <v>3.9453763143192533</v>
+      <c r="K28">
+        <v>3.8</v>
       </c>
       <c r="L28" t="s">
         <v>46</v>
@@ -3830,7 +3789,7 @@
         <v>95</v>
       </c>
       <c r="P28">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
@@ -3841,10 +3800,10 @@
       <c r="S28">
         <v>5</v>
       </c>
-      <c r="T28" s="2">
+      <c r="T28">
         <v>0.1905</v>
       </c>
-      <c r="U28" s="2">
+      <c r="U28">
         <v>0.1905</v>
       </c>
       <c r="V28">
@@ -3853,11 +3812,11 @@
       <c r="W28">
         <v>105</v>
       </c>
-      <c r="X28" s="2">
+      <c r="X28">
         <v>0.1905</v>
       </c>
-      <c r="Y28" s="2">
-        <v>0.34399999999999997</v>
+      <c r="Y28">
+        <v>0.344</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
@@ -3865,44 +3824,44 @@
       <c r="AA28">
         <v>4.7</v>
       </c>
-      <c r="AB28" s="2">
-        <v>0.96313154301319981</v>
+      <c r="AB28">
+        <v>0.9705</v>
       </c>
       <c r="AC28" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD28" s="2">
-        <v>0.21160000000000001</v>
-      </c>
-      <c r="AE28" s="2">
-        <v>0.20169999999999999</v>
+        <v>84</v>
+      </c>
+      <c r="AD28">
+        <v>0.2116</v>
+      </c>
+      <c r="AE28">
+        <v>0.2017</v>
       </c>
       <c r="AF28">
         <v>8</v>
       </c>
-      <c r="AG28" s="2">
-        <v>0.20710000000000001</v>
-      </c>
-      <c r="AH28" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI28" s="2">
-        <v>0.97970000000000002</v>
+      <c r="AG28">
+        <v>0.2071</v>
+      </c>
+      <c r="AH28">
+        <v>0.218</v>
+      </c>
+      <c r="AI28">
+        <v>0.9797</v>
       </c>
       <c r="AJ28" t="b">
         <v>1</v>
       </c>
       <c r="AK28" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="AL28" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="AM28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -3918,8 +3877,8 @@
       <c r="E29">
         <v>-128</v>
       </c>
-      <c r="F29" s="3">
-        <v>6.2553243045008804</v>
+      <c r="F29">
+        <v>6.24</v>
       </c>
       <c r="H29" t="s">
         <v>45</v>
@@ -3927,8 +3886,8 @@
       <c r="J29" t="s">
         <v>45</v>
       </c>
-      <c r="K29" s="3">
-        <v>6.2553243045008804</v>
+      <c r="K29">
+        <v>6.24</v>
       </c>
       <c r="L29" t="s">
         <v>57</v>
@@ -3943,7 +3902,7 @@
         <v>48</v>
       </c>
       <c r="P29">
-        <v>6.33</v>
+        <v>6.3</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
@@ -3954,11 +3913,11 @@
       <c r="S29">
         <v>6</v>
       </c>
-      <c r="T29" s="2">
+      <c r="T29">
         <v>0.1915</v>
       </c>
-      <c r="U29" s="2">
-        <v>0.18475170000000002</v>
+      <c r="U29">
+        <v>0.1847</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -3966,58 +3925,307 @@
       <c r="W29">
         <v>121</v>
       </c>
-      <c r="X29" s="2">
+      <c r="X29">
         <v>0.1736</v>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y29">
         <v>0.377</v>
       </c>
       <c r="Z29" t="b">
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="AB29" s="2">
-        <v>1.3177059626763767</v>
+        <v>4.06</v>
+      </c>
+      <c r="AB29">
+        <v>1.3281</v>
       </c>
       <c r="AC29" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD29" s="2">
-        <v>0.28949999999999998</v>
-      </c>
-      <c r="AE29" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD29">
+        <v>0.2895</v>
+      </c>
+      <c r="AE29">
         <v>0.2205</v>
       </c>
       <c r="AF29">
         <v>9</v>
       </c>
-      <c r="AG29" s="2">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="AH29" s="2">
-        <v>0.21970000000000001</v>
-      </c>
-      <c r="AI29" s="2">
-        <v>0.99980000000000002</v>
+      <c r="AG29">
+        <v>0.207</v>
+      </c>
+      <c r="AH29">
+        <v>0.218</v>
+      </c>
+      <c r="AI29">
+        <v>0.9998</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
       </c>
       <c r="AK29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30">
+        <v>6.5</v>
+      </c>
+      <c r="D30">
+        <v>102</v>
+      </c>
+      <c r="E30">
+        <v>-125</v>
+      </c>
+      <c r="H30" t="s">
+        <v>45</v>
+      </c>
+      <c r="J30" t="s">
+        <v>45</v>
+      </c>
+      <c r="L30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M30" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" t="s">
+        <v>45</v>
+      </c>
+      <c r="O30" t="s">
+        <v>45</v>
+      </c>
+      <c r="S30">
+        <v>6</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31">
+        <v>3.5</v>
+      </c>
+      <c r="D31">
+        <v>-131</v>
+      </c>
+      <c r="E31">
+        <v>106</v>
+      </c>
+      <c r="H31" t="s">
+        <v>45</v>
+      </c>
+      <c r="J31" t="s">
+        <v>45</v>
+      </c>
+      <c r="L31" t="s">
+        <v>45</v>
+      </c>
+      <c r="M31" t="s">
         <v>68</v>
       </c>
-      <c r="AL29" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM29">
-        <v>0</v>
+      <c r="N31" t="s">
+        <v>45</v>
+      </c>
+      <c r="O31" t="s">
+        <v>45</v>
+      </c>
+      <c r="S31">
+        <v>5</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32">
+        <v>5.5</v>
+      </c>
+      <c r="D32">
+        <v>-146</v>
+      </c>
+      <c r="E32">
+        <v>125</v>
+      </c>
+      <c r="H32" t="s">
+        <v>45</v>
+      </c>
+      <c r="J32" t="s">
+        <v>45</v>
+      </c>
+      <c r="L32" t="s">
+        <v>45</v>
+      </c>
+      <c r="M32" t="s">
+        <v>77</v>
+      </c>
+      <c r="N32" t="s">
+        <v>45</v>
+      </c>
+      <c r="O32" t="s">
+        <v>45</v>
+      </c>
+      <c r="S32">
+        <v>6</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33">
+        <v>4.5</v>
+      </c>
+      <c r="D33">
+        <v>-148</v>
+      </c>
+      <c r="E33">
+        <v>120</v>
+      </c>
+      <c r="H33" t="s">
+        <v>45</v>
+      </c>
+      <c r="J33" t="s">
+        <v>45</v>
+      </c>
+      <c r="L33" t="s">
+        <v>45</v>
+      </c>
+      <c r="M33" t="s">
+        <v>80</v>
+      </c>
+      <c r="N33" t="s">
+        <v>45</v>
+      </c>
+      <c r="O33" t="s">
+        <v>45</v>
+      </c>
+      <c r="S33">
+        <v>6</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34">
+        <v>6.5</v>
+      </c>
+      <c r="D34">
+        <v>126</v>
+      </c>
+      <c r="E34">
+        <v>-154</v>
+      </c>
+      <c r="H34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" t="s">
+        <v>45</v>
+      </c>
+      <c r="L34" t="s">
+        <v>45</v>
+      </c>
+      <c r="M34" t="s">
+        <v>97</v>
+      </c>
+      <c r="N34" t="s">
+        <v>45</v>
+      </c>
+      <c r="O34" t="s">
+        <v>45</v>
+      </c>
+      <c r="S34">
+        <v>6</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ29" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>